--- a/out/universities.xlsx
+++ b/out/universities.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>도심에 위치</t>
+          <t>도시 — 멜버른 도심에 위치</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>도심에서 셔틀버스 20분 또는 대중교통으로 약 15-25분(추정) (도심 인접)</t>
+          <t>준도시 — 소도시 뉴캐슬 시내 (시드니에서 기차 약 2시간 10분)</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>시내에서 트램/버스 약 15-20분 (도심 인접)</t>
+          <t>준도시 — 멜버른 도심까지 트램 약 25분</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스 약 10~15분 (도심 인접)</t>
+          <t>준도시 — 퍼스 도심까지 버스 약 15분</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>시드니 중심부에서 버스/기차 약 10~15분 (도심 인접)</t>
+          <t>준도시 — 시드니 도심까지 기차 약 15분</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Gardens Point 캠퍼스는 도심에 위치, Kelvin Grove 캠퍼스는 시내에서 버스/트램 약 10-15분 (도심|도심 인접)</t>
+          <t>도시 — 브리즈번 도심에 위치</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>도심에 위치 (대표 캠퍼스 기준)</t>
+          <t>도시 — 시드니 도심에 위치</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>도시 중심(마리바브로)에서 대중교통으로 약 30-40분(추정) (교외/소도시)</t>
+          <t>준도시 — 소도시 선샤인코스트 시내 (브리즈번에서 기차 또는 버스 약 90분)</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>도심에서 버스 약 10-15분(추정) (도심 인접)</t>
+          <t>준도시 — 캔버라 도심까지 버스 약 15분</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>쿠프슈타인은 소도시로 도심에서 캠퍼스까지 도보 또는 자전거로 접근 가능(추정) (교외/소도시)</t>
+          <t>준도시 — 소도시·마을(쿠프슈타인) 소재, 인스브루크에서 기차 약 50분</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>도심에 위치</t>
+          <t>도시 — 빈 도심에 위치</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>도심에서 도보 또는 버스 약 10분 이내(도심 인접)</t>
+          <t>준도시 — 소도시 도르비른 시내 (브레겐츠에서 버스 약 50분)</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>도심에서 도보 또는 대중교통으로 약 10~15분(추정) (도심 인접)</t>
+          <t>준도시 — 소도시 인스브루크 시내 (빈에서 기차 약 5시간)</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>시내에서 도보 또는 버스 약 10분 이내(도심 인접)</t>
+          <t>준도시 — 소도시 슈타이어 시내 (린츠에서 기차 약 80분)</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>도심에서 버스/트램 약 10~15분(추정) (도심 인접)</t>
+          <t>준도시 — 브뤼셀 도심까지 지하철 약 15분</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스/트램 약 10~15분 (도심 인접)</t>
+          <t>준도시 — 브뤼셀 도심까지 지하철 약 15분</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>도심에서 도보 또는 대중교통으로 약 10~15분 (도심 인접)</t>
+          <t>도시 — 리에주 도심에 위치</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>도심에서 도보 또는 자전거 10~15분(추정) (도심 인접)</t>
+          <t>준도시 — 소도시 루벤 시내 (브뤼셀에서 기차 약 45분)</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>São Leopoldo 캠퍼스는 도심(Porto Alegre)에서 버스 약 40분(추정), Porto Alegre 캠퍼스는 도심 인접 (외곽|도심 인접)</t>
+          <t>준도시 — 소도시 상 레오폴두 시내 (포르투알레그리에서 버스 약 30분)</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>도심에서 버스/지하철 약 15~30분(추정) (도심 인접)</t>
+          <t>준도시 — 상파울루 도심까지 지하철 약 25분</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스 약 15~20분 (추정) (도심 인접)</t>
+          <t>준도시 — 캄피나스 도심까지 버스 약 25분</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>도심에서 버스 약 10~15분(추정) (도심 인접)</t>
+          <t>준도시 — 소도시 켈로나 시내 (밴쿠버에서 버스+기차 약 300분)</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>도심에 위치</t>
+          <t>도시 — 토론토 도심에 위치</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스/지하철 약 30~40분(추정) (외곽)</t>
+          <t>준도시 — 토론토 도심까지 버스 약 30분</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>도심에서 버스 약 15-20분(추정) (외곽)</t>
+          <t>도시 — 서스캐처원 도심에 위치</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>도심에 위치</t>
+          <t>도시 — 몬트리올 도심에 위치</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스 약 10-15분(추정) (도심 인접)</t>
+          <t>준도시 — 위니펙 도심까지 버스 약 15분</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>버너비 캠퍼스: 밴쿠버 시내에서 스카이트레인 약 30분 / 서리 캠퍼스: 밴쿠버 시내 버스+스카이트레인 약 45분 / 밴쿠버 캠퍼스: 도심에 위치 (외곽|도심 인접|도심)</t>
+          <t>준도시 — 버너비 도심까지 버스 약 45분</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>도심에서 버스 약 10~15분(추정) (도심 인접)</t>
+          <t>준도시 — 소도시 세인트존스 시내 (핼리팩스에서 버스+기차 약 3시간)</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2743,7 +2743,7 @@
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스/스카이트레인 약 30~40분(추정) (외곽)</t>
+          <t>준도시 — 밴쿠버 도심까지 버스 약 25분</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>도심에 위치(St. George), 도심에서 버스/지하철 약 40분(Scarborough), 도심에서 버스 약 50분(Mississauga) (도심|도심 인접|외곽|교외/소도시)</t>
+          <t>도시 — 토론토 도심에 위치</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>도심에서 버스/지하철 약 10~15분 (도심 인접)</t>
+          <t>준도시 — 몬트리올 도심까지 지하철 약 15분</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>도심에서 도보 또는 대중교통으로 약 10~15분 (도심 인접)</t>
+          <t>준도시 — 몬트리올 도심까지 지하철 약 15분</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스/지하철 약 20~30분(추정) (도심 인접)</t>
+          <t>준도시 — 베이징 도심까지 지하철 약 30분</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스/지하철 약 20~30분(추정) (도심 인접)</t>
+          <t>준도시 — 우한 도심까지 버스 약 30분</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3173,7 +3173,7 @@
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>Jinan 캠퍼스는 시내에서 버스/지하철 약 20-30분, Qingdao 캠퍼스는 도심에서 버스 약 40분(추정) (도심 인접|외곽)</t>
+          <t>준도시 — 지난 도심까지 버스 약 30분</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>도심에서 버스/지하철 약 30~40분(추정) (도심 인접)</t>
+          <t>준도시 — 베이징 도심까지 지하철 약 30분</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>베이징 도심에서 지하철/버스 약 30분(추정), 주하이 도심에서 버스 약 15분(추정) (도심 인접|외곽)</t>
+          <t>준도시 — 베이징 도심까지 지하철 약 30분</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>시내에서 지하철 약 40분(추정) (외곽)</t>
+          <t>준도시 — 상하이 도심까지 지하철 약 30분</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>도심에서 트램/버스 약 10~15분 (도심 인접)</t>
+          <t>도시 — 자그레브 도심에 위치</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>시내에서 트램/버스 약 10~15분 (도심 인접)</t>
+          <t>도시 — 브르노 도심에 위치</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>도심에 위치</t>
+          <t>도시 — 프라하 도심에 위치</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스 약 10~15분 (도심 인접)</t>
+          <t>준도시 — 소도시 오덴세 시내 (코펜하겐에서 기차 약 90분)</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>코펜하겐 도심에서 전철(지하철/S-tog) 약 20~30분 (교외/소도시)</t>
+          <t>준도시 — 소도시 린비 시내 (코펜하겐에서 기차 약 30분)</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>도심에서 버스/메트로 약 10~15분 (도심 인접)</t>
+          <t>도시 — 코펜하겐 도심에 위치</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3916,7 +3916,7 @@
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>코펜하겐 도심에서 기차 약 30분(추정) (외곽)</t>
+          <t>준도시 — 소도시 로스킬데 시내 (코펜하겐에서 기차 약 45분)</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>도심에서 대중교통으로 대략 10~30분(추정) (도심 인접|외곽|교외/소도시)</t>
+          <t>준도시 — 소도시 올보르 시내 (오르후스에서 기차 약 50분)</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스 약 30-40분(추정) (외곽)</t>
+          <t>도시 외곽 — 소도시·마을(쿰바야) 소재, 키토에서 버스 약 1시간</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>시내에서 트램/버스 약 10~15분 (도심 인접)</t>
+          <t>준도시 — 탈린 도심까지 버스 약 15분</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>라티 캠퍼스는 라티 시내에서 버스 약 10분, 라펜란타 캠퍼스는 라펜란타 시내에서 버스/도보 약 15분(추정) (외곽)</t>
+          <t>준도시 — 소도시 라티 시내 (헬싱키에서 기차 약 100분)</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>도심에서 도보 또는 버스 약 10-15분(추정) (도심 인접)</t>
+          <t>준도시 — 소도시 바사 시내 (헬싱키에서 기차 약 120분)</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4370,7 +4370,7 @@
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>도심에서 도보 또는 버스 약 10분 이내 (도심 인접)</t>
+          <t>준도시 — 소도시 로바니에미 시내 (헬싱키에서 기차 및 버스 환승 약 1020분)</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>조엔수·쿠오피오 시내에서 대중교통으로 대략 10~20분(추정) (교외/소도시)</t>
+          <t>준도시 — 소도시 요엔수 시내 (헬싱키에서 기차 약 2시간)</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>도심에 위치 (City centre campus 기준), Hervanta 캠퍼스는 도심에서 버스/트램 약 15~20분 (도심|도심 인접|외곽|교외/소도시)</t>
+          <t>도시 — 탐페레 도심에 위치</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>도심에 위치</t>
+          <t>준도시 — 소도시 카야니 시내 (오울루에서 기차 약 3시간)</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4674,7 +4674,7 @@
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>헬싱키 캠퍼스는 도심에 위치, 바사 캠퍼스는 소도시 중심가 인근 (도심 인접|교외/소도시)</t>
+          <t>도시 — 헬싱키 도심에 위치</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스 약 10분(추정) (도심 인접)</t>
+          <t>도시 — 헬싱키 도심에 위치</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>헬싱키 도심에서 기차/버스 약 15~20분 (도심 인접)</t>
+          <t>준도시 — 소도시 에스포 시내 (헬싱키에서 버스 및 기차 약 40분)</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>시내에서 트램/버스 약 10~15분 (도심 인접)</t>
+          <t>도시 — 헬싱키 도심에 위치</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스/트램 약 10~15분 (도심 인접)</t>
+          <t>준도시 — 소도시 투르쿠 시내 (헬싱키에서 기차 약 2시간)</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스/메트로 약 20-30분(추정) (도심 인접)</t>
+          <t>준도시 — 파리 도심까지 지하철 약 15분</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>파리 캠퍼스는 도심에 위치, 보르도/리용 캠퍼스는 도심 또는 도심 인접(추정) (도심|도심 인접|도심)</t>
+          <t>준도시 — 파리 도심까지 지하철 약 15분</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>시내에서 RER/메트로 약 20-30분(추정) (도심 인접)</t>
+          <t>도시 — 파리 도심에 위치</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>시내에서 트램/버스 약 10~15분(도심 인접 추정)</t>
+          <t>준도시 — 소도시 낭시 시내 (파리에서 기차 약 1시간 30분)</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>도심에서 트램/버스 약 10~15분(추정) (도심 인접)</t>
+          <t>도시 — 리옹 도심에 위치</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스/트램 약 10-15분 (도심 인접)</t>
+          <t>준도시 — 소도시 렌 시내 (렌에서 기차 약 60분)</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>리옹 도심에서 트램/버스 약 15-20분(추정) (도심 인접)</t>
+          <t>준도시 — 리옹 도심까지 지하철 약 15분</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>시내에서 트램/버스 약 10~15분 (도심 인접)</t>
+          <t>준도시 — 릴 도심까지 지하철 약 15분</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>시내에서 트램/버스 약 10~15분 (도심 인접)</t>
+          <t>준도시 — 그르노블 도심까지 트램 약 15분</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>파리 시내에서 지하철(Métro) 약 15분(도심에서 3km 이내) (도심 인접)</t>
+          <t>준도시 — 파리 도심까지 지하철 약 15분</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>보르도 시내 트램/버스 약 10-15분, 마르세유 시내 트램/버스 약 15-20분(추정) (도심 인접)</t>
+          <t>준도시 — 보르도 도심까지 트램 약 15분</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>파리 도심에서 RER/메트로 약 20-30분, 릴 도심에서 트램/버스 약 15분 (도심 인접)</t>
+          <t>준도시 — 파리 도심까지 지하철 약 15분</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>파리 시내에서 RER B/C 또는 버스 약 30분 (Cachan) | 몽펠리에 시내에서 트램/버스 약 15분 (Montpellier) (도심 인접|교외/소도시)</t>
+          <t>준도시 — 파리 도심까지 지하철 약 25분</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -6044,7 +6044,7 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>도심에 위치</t>
+          <t>도시 — 파리 도심에 위치</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>시내에서 트램/버스 약 10~15분(추정) (도심 인접)</t>
+          <t>준도시 — 릴 도심까지 지하철 약 15분</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>니스 캠퍼스는 시내에서 트램/버스 약 10분, 릴 캠퍼스는 도보 15분 이내(도심 인접)</t>
+          <t>준도시 — 니스 &amp; 릴 도심까지 트램 약 15분</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>시내에서 트램/버스 약 15~20분(추정) (도심 인접)</t>
+          <t>준도시 — 툴루즈 도심까지 지하철 약 15분</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6352,7 +6352,7 @@
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스/메트로 약 15분(추정) (도심 인접)</t>
+          <t>준도시 — 파리 도심까지 지하철 약 15분</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6425,7 +6425,7 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스/메트로 약 15분(도심 인접, 추정)</t>
+          <t>준도시 — 파리 도심까지 지하철 약 15분</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6502,7 +6502,7 @@
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>파리 캠퍼스는 도심 위치, 랑스 캠퍼스는 도심 인접, 루앙 캠퍼스는 외곽(버스/트램 약 15-20분 추정) (도심 인접|외곽|도심)</t>
+          <t>준도시 — 소도시 랭스 시내 (파리에서 기차 약 120분)</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>파리 도심에서 RER A 전철로 약 45분(추정) (교외/소도시)</t>
+          <t>준도시 — 파리 도심까지 지하철 약 20분</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6648,7 +6648,7 @@
       <c r="I83" s="2" t="inlineStr"/>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>뷔르펠탈 시내 중심부에서 버스/트램 약 10~15분(추정) (외곽)</t>
+          <t>준도시 — 부퍼탈 도심까지 기차 약 15분</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6721,7 +6721,7 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>도심에 위치</t>
+          <t>도시 — 만하임 도심에 위치</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스/트램 약 10분(도심 인접)</t>
+          <t>도시 — 보훔 도심에 위치</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6868,7 +6868,7 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>도심에서 대중교통으로 약 10~15분(추정) (도심 인접)</t>
+          <t>준도시 — 쾰른 도심까지 지하철 약 15분</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6945,7 +6945,7 @@
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>도심에서 버스/트램 약 10~15분(추정) (도심 인접)</t>
+          <t>도시 — 로스토크 도심에 위치</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>시내에서 도보 또는 트램 10분 이내(도심 인접)</t>
+          <t>준도시 — 소도시 켐니츠 시내 (라이프치히에서 기차 약 40분)</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>도심에서 도보 또는 자전거 10~15분(추정) (도심 인접)</t>
+          <t>준도시 — 소도시 뤼네부르크 시내 (함부르크에서 기차 약 50분)</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7164,7 +7164,7 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>시내에서 지하철(U-Bahn) 약 10분 (도심 인접)</t>
+          <t>준도시 — 프랑크푸르트암마인 도심까지 지하철 약 15분</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7237,7 +7237,7 @@
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>도심에서 트램/버스 약 10-15분 (도심 인접)</t>
+          <t>도시 — 쾰른 도심에 위치</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>도심에서 버스 약 10~15분(추정) (도심 인접)</t>
+          <t>준도시 — 킬 도심까지 버스 약 15분</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>도심에서 버스/트램 약 10-15분(추정) (도심 인접)</t>
+          <t>준도시 — 소도시 오스나브뤼크 시내 (하노버에서 기차 약 60분)</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스/트램 약 15~20분(추정) (도심 인접)</t>
+          <t>준도시 — 베를린 도심까지 지하철 약 15분</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7537,7 +7537,7 @@
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>도심에서 트램/지하철 약 10~15분 (도심 인접)</t>
+          <t>도시 — 뮌헨 도심에 위치</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7614,7 +7614,7 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>Furtwangen은 소도시로 도심 개념이 명확하지 않음. 가장 가까운 대도시 프라이부르크에서 버스/기차 약 1시간(추정) (교외/소도시)</t>
+          <t>준도시 — 소도시 푸르트방엔 시내 (프라이부르크에서 버스 및 기차 환승 약 45분)</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>시내에서 U-반/트램 약 10~15분 (도심 인접)</t>
+          <t>준도시 — 프랑크푸르트암마인 도심까지 지하철 약 15분</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>도심에 위치</t>
+          <t>도시 — 프랑크푸르트암마인 도심에 위치</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>도심에서 대중교통으로 약 10~20분(추정) (도심 인접)</t>
+          <t>도시 — 베를린 도심에 위치</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7918,7 +7918,7 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>도심에 위치</t>
+          <t>도시 — 본 도심에 위치</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>시내에서 도보 또는 버스 약 10~15분 (도심 인접)</t>
+          <t>도시 — 아헨 도심에 위치</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>도심에서 도보 또는 트램 약 10분 이내 (도심 인접)</t>
+          <t>준도시 — 소도시 에를랑겐 시내 (뉘른베르크에서 기차 약 50분)</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>시내에서 MTR(지하철) 약 30~40분 (외곽)</t>
+          <t>준도시 — 샤틴 도심까지 지하철 약 30분</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>도심에서 도보 또는 버스 약 10~15분 (도심 인접)</t>
+          <t>준도시 — 홍콩 도심까지 지하철 약 15분</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>도심에서 MTR(약 10~15분) 또는 버스(약 20분) (도심 인접)</t>
+          <t>준도시 — 홍콩 도심까지 지하철 약 15분</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스/지하철 약 10~15분 (도심 인접)</t>
+          <t>준도시 — 홍콩 도심까지 지하철 약 15분</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8437,7 +8437,7 @@
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스/트램 약 10-15분(추정) (도심 인접)</t>
+          <t>준도시 — 소도시 페치 시내 (부다페스트에서 기차 약 2시간)</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스/오토바이 택시 약 10~15분(추정) (도심 인접)</t>
+          <t>준도시 — 욕야카르타 도심까지 버스 약 15분</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>자카르타 시내에서 대중교통으로 대략 30~45분(추정) (도심 인접)</t>
+          <t>준도시 — 소도시 데폭 시내 (자카르타에서 버스 약 60분)</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>도심에서 버스/트램 약 10~20분 (추정) (도심 인접)</t>
+          <t>준도시 — 소도시 베로나 시내 (밀라노에서 기차 약 2시간)</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>밀라노 도심에서 지하철/트램으로 약 10~15분(추정) (도심 인접)</t>
+          <t>준도시 — 밀라노 도심까지 지하철 약 15분</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>도심에 위치</t>
+          <t>준도시 — 베네치아 도심까지 버스 약 20분</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>도심에 위치</t>
+          <t>도시 — 밀라노 도심에 위치</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -8972,7 +8972,7 @@
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스 약 30분(추정) (외곽)</t>
+          <t>준도시 — 소도시 쓰시마 시내 (오카야마에서 버스와 기차 환승 약 120분)</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -9049,7 +9049,7 @@
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>도쿄 도심(시부야 기준)에서 전철 약 1시간 10분~1시간 30분(추정) (교외/소도시)</t>
+          <t>도시 외곽 — 소도시 히가시마쓰야마 중심까지 기차 약 100분 (도쿄에서 기차 약 60분)</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -9126,7 +9126,7 @@
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>도심에서 지하철로 약 10~15분(추정) (도심 인접)</t>
+          <t>도시 — 도쿄 도심에 위치</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>도심에서 지하철로 약 10~15분(도쿄 메트로 긴자선·후쿠토신선 아오야마-잇초메 역 인접) (도심 인접)</t>
+          <t>도시 — 도쿄 도심에 위치</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스/지하철 약 30~40분(추정) (외곽)</t>
+          <t>준도시 — 후쿠오카 도심까지 지하철 약 30분</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>도쿄 도심(시부야)에서 전철(야마노테선+주오선) 약 1시간 10분(추정) (교외/소도시)</t>
+          <t>도시 외곽 — 소도시 코다이라 중심까지 기차 약 45분 (도쿄에서 기차 약 60분)</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -9426,7 +9426,7 @@
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>도심(신주쿠)에서 전철로 약 50~60분(추정) (교외/소도시)</t>
+          <t>준도시 — 소도시 히노 중심까지 기차 약 50분 (도쿄에서 기차 약 40분)</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -9503,7 +9503,7 @@
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>도심(키타야마 역)에서 버스 약 10분(KIC) / 오사카 도심에서 전철 약 30분(OIC) / 시가 교외(버스/JR 이용, 약 1시간 이상)(BKC) (도심 인접|외곽|교외/소도시)</t>
+          <t>준도시 — 교토 도심까지 버스 약 15분</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -9580,7 +9580,7 @@
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>도심(히치난시 중심)에서 버스 약 20-30분(추정) (교외/소도시)</t>
+          <t>준도시 — 소도시 소카 시내 (도쿄에서 기차 약 50분)</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>도심에서 전철로 약 20~30분(추정) (도심 인접)</t>
+          <t>준도시 — 도쿄 도심까지 지하철 약 15분</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -9730,7 +9730,7 @@
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>각 캠퍼스는 해당 도시 중심부에서 대중교통으로 대략 10~30분(추정) (교외/소도시)</t>
+          <t>준도시 — 소도시 마쓰모토 시내 (나가노에서 버스와 기차 환승 약 2시간)</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9807,7 +9807,7 @@
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>시내에서 지하철 약 10~15분 (도심 인접)</t>
+          <t>준도시 — 나고야 도심까지 지하철 약 20분</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스/지하철 약 15~25분 (도심 인접)</t>
+          <t>준도시 — 교토 도심까지 지하철 약 15분</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>도심(도쿄)에서 전철로 약 1시간 10분~1시간 30분(추정) (교외/소도시)</t>
+          <t>준도시 — 소도시 사와타 시내 (도쿄에서 기차 약 50분)</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
@@ -10038,7 +10038,7 @@
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>시내에서 지하철/버스 약 15~20분 (도심 인접)</t>
+          <t>도시 — 삿포로 도심에 위치</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -10115,7 +10115,7 @@
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>시내에서 지하철/버스 약 15~25분 (도심 인접)</t>
+          <t>준도시 — 센다이 도심까지 지하철 약 20분</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>시내에서 지하철/버스 약 15~25분 (대표 캠퍼스 Maidashi 기준) (도심 인접)</t>
+          <t>준도시 — 후쿠오카 도심까지 지하철 약 20분</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -10265,7 +10265,7 @@
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>시내에서 도보 또는 버스 약 10~15분(추정) (도심 인접)</t>
+          <t>준도시 — 알마티 도심까지 버스 약 15분</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
@@ -10342,7 +10342,7 @@
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스/트램 약 10~15분 (도심 인접)</t>
+          <t>준도시 — 카우나스 도심까지 버스 약 15분</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -10419,7 +10419,7 @@
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>도심에서 대중교통으로 대략 20~40분(추정)|도심 인접|도심에서 버스 약 30분(추정)|도심에서 버스 약 25분(추정) (외곽|도심 인접|교외/소도시|교외/소도시)</t>
+          <t>준도시 — 몬테레이 도심까지 버스 약 30분</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
@@ -10496,7 +10496,7 @@
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스 약 10-15분 (도심 인접)</t>
+          <t>준도시 — 소도시 흐로닝언 시내 (암스테르담에서 기차 약 2시간)</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
@@ -10569,7 +10569,7 @@
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스 약 10분(도심 인접)</t>
+          <t>준도시 — 소도시 니메헌 시내 (위트레흐트에서 기차 약 1시간)</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
@@ -10642,7 +10642,7 @@
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>도심에서 도보 또는 자전거 10~15분(추정) (도심 인접)</t>
+          <t>준도시 — 소도시 틸뷔르흐 시내 (로테르담에서 기차 약 80분)</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -10719,7 +10719,7 @@
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스 약 10-15분 (도심 인접)</t>
+          <t>준도시 — 소도시 르우아르던 시내 (암스테르담에서 기차 약 2시간 30분)</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
@@ -10796,7 +10796,7 @@
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스/트램 약 10~15분 (도심 인접)</t>
+          <t>도시 — 에인트호번 도심에 위치</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>도심에서 도보 또는 버스 약 10~15분 (도심 인접)</t>
+          <t>준도시 — 소도시 마스트리흐트 시내 (아헨에서 버스 및 기차 환승 약 60분)</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
@@ -10962,7 +10962,7 @@
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>암스테르담 캠퍼스: 도심에 위치 / 헤이그 캠퍼스: 도심 인접 / 알크마르·하를럼 캠퍼스: 교외/소도시 (대중교통 약 30-40분 추정) / 로테르담 캠퍼스: 도심 인접 (도심|도심 인접|외곽|교외/소도시 중 하나)</t>
+          <t>도시 — 암스테르담 도심에 위치</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -11035,7 +11035,7 @@
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>로테르담 중앙역에서 트램/버스 약 10-15분 (도심 인접)</t>
+          <t>도시 — 로테르담 도심에 위치</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
@@ -11108,7 +11108,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>시내에서 트램/버스 약 10~15분 (도심 인접)</t>
+          <t>도시 — 위트레흐트 도심에 위치</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -11181,7 +11181,7 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>시내에서 트램/버스 약 10~15분 (도심 인접)</t>
+          <t>준도시 — 암스테르담 도심까지 트램 약 15분</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -11258,7 +11258,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>레이던 도심에서 도보 또는 자전거 10~15분, 헤이그 캠퍼스는 헤이그 도심에서 도보 10분 이내 (도심 인접)</t>
+          <t>준도시 — 소도시 레이던 시내 (암스테르담에서 기차 약 45분)</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -11331,7 +11331,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>도심에서 트램/버스 약 10~15분 (도심 인접)</t>
+          <t>도시 — 오슬로 도심에 위치</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -11400,7 +11400,7 @@
       <c r="I146" s="2" t="inlineStr"/>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>도심에서 버스/트램 약 10~15분 (도심 인접)</t>
+          <t>준도시 — 소도시 베르겐 시내 (오슬로에서 기차 약 5시간 (300분))</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>리마 시내에서 버스/택시 약 15-20분(추정) (도심 인접)</t>
+          <t>준도시 — 리마 도심까지 버스 약 30분</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
@@ -11546,7 +11546,7 @@
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>도심에서 도보 또는 트램으로 약 10~15분 (도심 인접)</t>
+          <t>준도시 — 바르샤바 도심까지 지하철 약 15분</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -11623,7 +11623,7 @@
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스/지하철 약 15~20분 (도심 인접)</t>
+          <t>준도시 — 리스본 도심까지 버스 약 15분</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>도심에서 버스/MRT 약 15~20분(추정) (도심 인접)</t>
+          <t>준도시 — 싱가포르 도심까지 지하철 약 20분</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -11773,7 +11773,7 @@
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>시내에서 MRT 및 버스 환승 시 약 30~40분(추정) (외곽)</t>
+          <t>준도시 — 싱가포르 도심까지 버스 약 45분</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
@@ -11852,7 +11852,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>도심에 위치</t>
+          <t>도시 — 싱가포르 도심에 위치</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -11925,7 +11925,7 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>알리칸테 도심에서 버스 약 15-20분(추정) (외곽)</t>
+          <t>준도시 — 알리칸테 도심까지 버스 약 15분</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -11998,7 +11998,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스/지하철 약 15~20분 (도심 인접)</t>
+          <t>준도시 — 발렌시아 도심까지 지하철 약 20분</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -12075,7 +12075,7 @@
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>바르셀로나 도심에서 지하철+버스 약 40~50분(추정) (교외/소도시)</t>
+          <t>준도시 — 소도시 셀라트 시내 (바르셀로나에서 버스 및 기차 약 45분)</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -12152,7 +12152,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>바르셀로나 시내에서 기차(FGC) 또는 버스 약 30분 (도심 인접)</t>
+          <t>준도시 — 소도시 산트 쿠가트 델 발레스 중심까지 버스 약 40분 (바르셀로나에서 버스 약 35분)</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -12229,7 +12229,7 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>빌바오 캠퍼스는 도심에 위치, 산세바스티안 캠퍼스는 시내에서 버스/트램 약 10-15분 (도심 인접)</t>
+          <t>준도시 — 빌바오 도심까지 지하철 약 15분</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -12306,7 +12306,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>팜플로나 도심에 위치 (도심 인접)</t>
+          <t>준도시 — 소도시 팜플로나 시내 (빌바오에서 기차 약 120분)</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>마드리드 캠퍼스는 도심에 위치 / 세고비아 캠퍼스는 마드리드 시내에서 기차 약 30분(대략 25-35분 추정) (도심|외곽)</t>
+          <t>도시 외곽 — 소도시·마을(세고비아) 소재, 마드리드에서 버스 약 60분</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
@@ -12456,7 +12456,7 @@
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>시내에서 도보 또는 버스 약 10-15분 (도심 인접)</t>
+          <t>준도시 — 소도시 할름스타드 시내 (예테보리에서 기차 약 120분)</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -12533,7 +12533,7 @@
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
-          <t>Linköping 시내 중심부에서 버스 약 10분, Norrköping 시내 중심부에서 버스/트램 약 15분 (도심 인접)</t>
+          <t>준도시 — 소도시 링셰핑 시내 (스톡홀름에서 기차 약 120분)</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -12610,7 +12610,7 @@
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>도심에서 도보 또는 버스 약 10~15분 (도심 인접)</t>
+          <t>준도시 — 소도시 웁살라 시내 (스톡홀름에서 기차 약 45분)</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
@@ -12687,7 +12687,7 @@
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
-          <t>칼마르/벡셰 시내에서 대중교통으로 대략 10~15분(추정) (도심 인접)</t>
+          <t>준도시 — 소도시 칼마르 또는 벡셰 시내 (말뫼에서 기차 약 120분)</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
@@ -12764,7 +12764,7 @@
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>Olten은 소도시 중심, Brugg-Windisch는 바젤 도심에서 트램/기차 약 15분, Basel은 도심에 위치 (도심 인접|교외/소도시)</t>
+          <t>준도시 — 소도시 올텐 시내 (취리히에서 기차 약 20분)</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="J165" s="2" t="inlineStr">
         <is>
-          <t>취리히 도심에서 S-Bahn(기차) 약 20분 (도심 인접)</t>
+          <t>준도시 — 소도시 빈터투어 시내 (취리히에서 기차 약 20분)</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
@@ -12914,7 +12914,7 @@
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>도심에서 도보 또는 트램으로 약 10분 이내 (도심 인접)</t>
+          <t>준도시 — 소도시 베른 시내 (취리히에서 기차 약 1시간 20분)</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>타이중 시내에서 버스 약 15~20분(추정) (도심 인접)</t>
+          <t>준도시 — 타이중 도심까지 버스 약 20분</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스/MRT 약 30-40분(추정) (외곽)</t>
+          <t>준도시 — 가오슝 도심까지 버스 약 30분</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -13141,7 +13141,7 @@
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스 약 20~30분(추정) (외곽)</t>
+          <t>준도시 — 신주 도심까지 버스 약 15분</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -13218,7 +13218,7 @@
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>타이베이 도심에서 대중교통으로 대략 30~40분(추정) (외곽)</t>
+          <t>준도시 — 신베이시 도심까지 버스 약 30분</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
@@ -13291,7 +13291,7 @@
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>타이페이 시내에서 MRT(약 10-15분) 또는 버스 이용 (도심 인접)</t>
+          <t>준도시 — 타이베이 도심까지 버스 약 20분</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>타이페이 도심에서 MRT(타이페이 지하철) 약 10~15분 (도심 인접)</t>
+          <t>준도시 — 타이베이 도심까지 지하철 약 15분</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
@@ -13441,7 +13441,7 @@
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>시내에서 대중교통으로 대략 20~30분(추정) (외곽)</t>
+          <t>준도시 — 소도시 치앙라이 시내 (치앙마이에서 버스 약 12시간)</t>
         </is>
       </c>
       <c r="K173" s="2" t="inlineStr">
@@ -13514,7 +13514,7 @@
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스/택시 약 10~20분(추정) (도심 인접)</t>
+          <t>준도시 — 방콕 도심까지 버스 약 15분</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스 약 20-30분(추정) (도심 인접)</t>
+          <t>준도시 — 방콕 도심까지 버스 약 30분</t>
         </is>
       </c>
       <c r="K175" s="2" t="inlineStr">
@@ -13660,7 +13660,7 @@
       <c r="I176" s="2" t="inlineStr"/>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>도심에서 버스/메트로 약 10~20분(추정) (도심 인접)</t>
+          <t>준도시 — 앙카라 도심까지 버스 약 20분</t>
         </is>
       </c>
       <c r="K176" s="2" t="inlineStr">
@@ -13737,7 +13737,7 @@
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>도심에서 버스/메트로 약 10~20분(추정) (도심 인접)</t>
+          <t>준도시 — 앙카라 도심까지 버스 약 15분</t>
         </is>
       </c>
       <c r="K177" s="2" t="inlineStr">
@@ -13814,7 +13814,7 @@
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>도심(술탄아흐메트)에서 마슬락 캠퍼스까지 메트로 약 30분, 귀므쉬수유 캠퍼스는 트램/버스 15분 내외, 투즐라 캠퍼스는 교외로 버스/메트로버스 약 1시간 30분(추정) (도심 인접|외곽)</t>
+          <t>준도시 — 이스탄불 도심까지 지하철 약 30분</t>
         </is>
       </c>
       <c r="K178" s="2" t="inlineStr">
@@ -13889,7 +13889,7 @@
       <c r="I179" s="2" t="inlineStr"/>
       <c r="J179" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스/페리 약 20~30분(추정) (도심 인접)</t>
+          <t>준도시 — 이스탄불 도심까지 버스 약 30분</t>
         </is>
       </c>
       <c r="K179" s="2" t="inlineStr">
@@ -13962,7 +13962,7 @@
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>도심에 위치</t>
+          <t>도시 — 런던 도심에 위치</t>
         </is>
       </c>
       <c r="K180" s="2" t="inlineStr">
@@ -14035,7 +14035,7 @@
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스 약 10~15분 (도심 인접)</t>
+          <t>도시 — 레스터 도심에 위치</t>
         </is>
       </c>
       <c r="K181" s="2" t="inlineStr">
@@ -14108,7 +14108,7 @@
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>시내에서 트램/버스 약 10~15분 (도심 인접)</t>
+          <t>도시 — 셰필드 도심에 위치</t>
         </is>
       </c>
       <c r="K182" s="2" t="inlineStr">
@@ -14185,7 +14185,7 @@
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스 약 10~15분 (도심 인접)</t>
+          <t>준도시 — 소도시 레딩 시내 (런던에서 기차 약 25분)</t>
         </is>
       </c>
       <c r="K183" s="2" t="inlineStr">
@@ -14258,7 +14258,7 @@
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스 약 10~15분 (도심 인접)</t>
+          <t>준도시 — 소도시 엑서터 시내 (런던에서 기차 약 2시간 10분)</t>
         </is>
       </c>
       <c r="K184" s="2" t="inlineStr">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>콜체스터 시내에서 버스 약 15-20분(추정) (외곽)</t>
+          <t>준도시 — 소도시 콜체스터 시내 (런던에서 기차 약 50분)</t>
         </is>
       </c>
       <c r="K185" s="2" t="inlineStr">
@@ -14408,7 +14408,7 @@
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>시내에서 도보 또는 버스 약 10~15분 (도심 인접)</t>
+          <t>도시 — 브래드퍼드 도심에 위치</t>
         </is>
       </c>
       <c r="K186" s="2" t="inlineStr">
@@ -14485,7 +14485,7 @@
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스 약 15~20분(추정) (도심 인접)</t>
+          <t>준도시 — 브리스틀 도심까지 버스 약 15분</t>
         </is>
       </c>
       <c r="K187" s="2" t="inlineStr">
@@ -14562,7 +14562,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>시내에서 도보 또는 버스 약 10~15분 (도심 인접)</t>
+          <t>준도시 — 소도시 요크 시내 (리즈에서 기차 약 120분)</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr">
@@ -14635,7 +14635,7 @@
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>시내에서 도보 또는 버스 약 10~15분 (도심 인접)</t>
+          <t>도시 — 리즈 도심에 위치</t>
         </is>
       </c>
       <c r="K189" s="2" t="inlineStr">
@@ -14708,7 +14708,7 @@
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스 약 15~20분 (도심 인접)</t>
+          <t>준도시 — 브리스틀 도심까지 버스 약 20분</t>
         </is>
       </c>
       <c r="K190" s="2" t="inlineStr">
@@ -14781,7 +14781,7 @@
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>도심에서 도보 또는 버스 약 10~15분 (도심 인접)</t>
+          <t>준도시 — 소도시 더럼 시내 (뉴캐슬어폰타인 기차 약 30분)</t>
         </is>
       </c>
       <c r="K191" s="2" t="inlineStr">
@@ -14858,7 +14858,7 @@
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>도심에 위치</t>
+          <t>준도시 — 소도시 프레스턴 시내 (맨체스터에서 기차 약 45분)</t>
         </is>
       </c>
       <c r="K192" s="2" t="inlineStr">
@@ -14933,7 +14933,7 @@
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>도심에 위치</t>
+          <t>도시 — 버밍엄 도심에 위치</t>
         </is>
       </c>
       <c r="K193" s="2" t="inlineStr">
@@ -15010,7 +15010,7 @@
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>사우샘프턴 도심에 위치 (도심 인접)</t>
+          <t>도시 — 사우샘프턴 도심에 위치</t>
         </is>
       </c>
       <c r="K194" s="2" t="inlineStr">
@@ -15075,7 +15075,7 @@
       <c r="I195" s="2" t="inlineStr"/>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>도심에서 버스 약 10~15분(추정) (도심 인접)</t>
+          <t>도시 — 올버니 도심에 위치</t>
         </is>
       </c>
       <c r="K195" s="2" t="inlineStr">
@@ -15140,7 +15140,7 @@
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>도심에 위치</t>
+          <t>도시 — 호놀룰루 도심에 위치</t>
         </is>
       </c>
       <c r="K196" s="2" t="inlineStr">
@@ -15217,7 +15217,7 @@
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>포츠담은 소도시로 도심 개념이 명확하지 않음. 대중교통은 지역 버스만 운영되며, 인근 주요 도시(시러큐스 등)까지 차량 1시간 이상 소요 (교외/소도시)</t>
+          <t>도시 외곽 — 소도시·마을(포츠담) 소재, 시러큐스에서 버스 약 5시간</t>
         </is>
       </c>
       <c r="K197" s="2" t="inlineStr">
@@ -15294,7 +15294,7 @@
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>도심에서 대중교통으로 약 15-20분(추정) (도심 인접)</t>
+          <t>준도시 — 시카고 도심까지 지하철 약 15분</t>
         </is>
       </c>
       <c r="K198" s="2" t="inlineStr">
@@ -15371,7 +15371,7 @@
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>Pullman은 소도시로 도심 개념이 명확하지 않음. 대중교통은 제한적 (교외/소도시)</t>
+          <t>도시 외곽 — 소도시·마을(풀먼) 소재, 스포캔에서 버스 약 2시간</t>
         </is>
       </c>
       <c r="K199" s="2" t="inlineStr">
@@ -15444,7 +15444,7 @@
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>도심(댈러스 시내)에서 대중교통으로 대략 30~45분(추정) (교외/소도시)</t>
+          <t>준도시 — 소도시 리처드슨 시내 (댈러스에서 버스/기차 약 30분)</t>
         </is>
       </c>
       <c r="K200" s="2" t="inlineStr">
@@ -15521,7 +15521,7 @@
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>도심에서 대중교통으로 약 15-20분(추정) (도심 인접)</t>
+          <t>준도시 — 보스턴 도심까지 버스 약 15분</t>
         </is>
       </c>
       <c r="K201" s="2" t="inlineStr">
@@ -15598,7 +15598,7 @@
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>도심에 위치</t>
+          <t>준도시 — 소도시 스프링필드 시내 (시카고에서 버스+기차 약 2시간 30분)</t>
         </is>
       </c>
       <c r="K202" s="2" t="inlineStr">
@@ -15675,7 +15675,7 @@
       </c>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>도심에서 버스/메트로레일 약 10~15분 (도심 인접)</t>
+          <t>준도시 — 휴스턴 도심까지 버스 약 15분</t>
         </is>
       </c>
       <c r="K203" s="2" t="inlineStr">
@@ -15748,7 +15748,7 @@
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>보스턴 도심에서 대중교통으로 약 30-40분(추정) (교외/소도시)</t>
+          <t>준도시 — 소도시·마을(월섬) 소재, 보스턴에서 기차 약 20분</t>
         </is>
       </c>
       <c r="K204" s="2" t="inlineStr">
@@ -15821,7 +15821,7 @@
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>도심에서 도보 또는 버스 약 10-15분 (도심 인접)</t>
+          <t>도시 — 보이시 도심에 위치</t>
         </is>
       </c>
       <c r="K205" s="2" t="inlineStr">
@@ -15898,7 +15898,7 @@
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>도심(피닉스)에서 버스/경전철 약 15~20분(추정) (도심 인접)</t>
+          <t>준도시 — 소도시 템피 시내 (피닉스 도심에서 버스 약 45분)</t>
         </is>
       </c>
       <c r="K206" s="2" t="inlineStr">
@@ -15975,7 +15975,7 @@
       </c>
       <c r="J207" s="2" t="inlineStr">
         <is>
-          <t>Laramie는 소도시이며 캠퍼스는 도심에 위치 (교외/소도시)</t>
+          <t>준도시 — 소도시 라라미 시내 (덴버에서 버스/기차 약 2시간)</t>
         </is>
       </c>
       <c r="K207" s="2" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="J208" s="2" t="inlineStr">
         <is>
-          <t>도심에서 버스/트램 약 15-20분(추정) (도심 인접)</t>
+          <t>준도시 — 탬파 도심까지 버스 약 15분</t>
         </is>
       </c>
       <c r="K208" s="2" t="inlineStr">
@@ -16129,7 +16129,7 @@
       </c>
       <c r="J209" s="2" t="inlineStr">
         <is>
-          <t>도심(다운타운)에서 버스 약 10-15분(추정) (교외/소도시)</t>
+          <t>준도시 — 소도시 블루밍턴 시내 (인디애나폴리스에서 버스 약 2시간)</t>
         </is>
       </c>
       <c r="K209" s="2" t="inlineStr">
@@ -16202,7 +16202,7 @@
       </c>
       <c r="J210" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스 약 10-15분(추정) (도심 인접)</t>
+          <t>준도시 — 소도시 그린즈버러 시내 (샬럿에서 버스/기차 약 90분)</t>
         </is>
       </c>
       <c r="K210" s="2" t="inlineStr">
@@ -16279,7 +16279,7 @@
       </c>
       <c r="J211" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스/경전철 약 15~20분(추정) (외곽)</t>
+          <t>준도시 — 버펄로 도심까지 버스 약 15분</t>
         </is>
       </c>
       <c r="K211" s="2" t="inlineStr">
@@ -16356,7 +16356,7 @@
       </c>
       <c r="J212" s="2" t="inlineStr">
         <is>
-          <t>State College 자체가 소도시이며, University Park 캠퍼스는 도심에 위치 (교외/소도시)</t>
+          <t>준도시 — 소도시 스테이트 칼리지 시내 (필라델피아에서 버스+기차 약 2시간)</t>
         </is>
       </c>
       <c r="K212" s="2" t="inlineStr">
@@ -16433,7 +16433,7 @@
       </c>
       <c r="J213" s="2" t="inlineStr">
         <is>
-          <t>밀워키 도심에서 버스/트램 약 10~15분 (도심 인접)</t>
+          <t>도시 — 밀워키 도심에 위치</t>
         </is>
       </c>
       <c r="K213" s="2" t="inlineStr">
@@ -16506,7 +16506,7 @@
       </c>
       <c r="J214" s="2" t="inlineStr">
         <is>
-          <t>보스턴 도심에서 대중교통(지하철/버스)으로 약 30-40분 (도심 인접)</t>
+          <t>준도시 — 소도시·마을(월섬) 소재, 보스턴에서 버스 약 20분</t>
         </is>
       </c>
       <c r="K214" s="2" t="inlineStr">
@@ -16579,7 +16579,7 @@
       </c>
       <c r="J215" s="2" t="inlineStr">
         <is>
-          <t>도시 자체가 소도시이며 도심이 없음 (교외/소도시)</t>
+          <t>준도시 — 소도시 이스트랜싱 시내 (디트로이트에서 버스+기차 약 3시간)</t>
         </is>
       </c>
       <c r="K215" s="2" t="inlineStr">
@@ -16656,7 +16656,7 @@
       </c>
       <c r="J216" s="2" t="inlineStr">
         <is>
-          <t>산타크루즈 도심에서 버스 약 15~20분(추정) (외곽)</t>
+          <t>준도시 — 소도시 산타크루즈 시내 (샌프란시스코에서 버스/기차 약 45분)</t>
         </is>
       </c>
       <c r="K216" s="2" t="inlineStr">
@@ -16733,7 +16733,7 @@
       </c>
       <c r="J217" s="2" t="inlineStr">
         <is>
-          <t>도심에서 도보 또는 대중교통으로 약 10~15분(추정) (도심 인접)</t>
+          <t>준도시 — 오스틴 도심까지 버스 약 15분</t>
         </is>
       </c>
       <c r="K217" s="2" t="inlineStr">
@@ -16810,7 +16810,7 @@
       </c>
       <c r="J218" s="2" t="inlineStr">
         <is>
-          <t>도심에서 도보 또는 버스 약 10~15분 (도심 인접)</t>
+          <t>도시 — 새너제이 도심에 위치</t>
         </is>
       </c>
       <c r="K218" s="2" t="inlineStr">
@@ -16883,7 +16883,7 @@
       </c>
       <c r="J219" s="2" t="inlineStr">
         <is>
-          <t>도심에서 도보 또는 대중교통으로 약 10~15분(추정) (도심 인접)</t>
+          <t>준도시 — 소도시 찰스턴 시내 (샬럿에서 버스 및 기차 환승 약 2시간)</t>
         </is>
       </c>
       <c r="K219" s="2" t="inlineStr">
@@ -16960,7 +16960,7 @@
       </c>
       <c r="J220" s="2" t="inlineStr">
         <is>
-          <t>Chapel Hill은 소도시이며, 도심(다운타운)에서 캠퍼스까지 도보 10~15분 또는 버스 5분 이내 (교외/소도시)</t>
+          <t>준도시 — 소도시 채플힐 시내 (롤리에서 버스 약 20분)</t>
         </is>
       </c>
       <c r="K220" s="2" t="inlineStr">
@@ -17033,7 +17033,7 @@
       </c>
       <c r="J221" s="2" t="inlineStr">
         <is>
-          <t>도심 중심부에서 대중교통으로 약 10-15분(추정) (교외/소도시)</t>
+          <t>준도시 — 소도시 탤러해시 시내 (올랜도에서 버스+기차 약 4시간)</t>
         </is>
       </c>
       <c r="K221" s="2" t="inlineStr">
@@ -17110,7 +17110,7 @@
       </c>
       <c r="J222" s="2" t="inlineStr">
         <is>
-          <t>시내에서 버스/택시 약 20-30분(추정) (도심 인접)</t>
+          <t>준도시 — 하노이 도심까지 버스 약 45분</t>
         </is>
       </c>
       <c r="K222" s="2" t="inlineStr">

--- a/out/universities.xlsx
+++ b/out/universities.xlsx
@@ -4066,7 +4066,7 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>도시 외곽 — 소도시·마을(쿰바야) 소재, 키토에서 버스 약 1시간</t>
+          <t>준도시 — 소도시·마을(쿰바야) 소재, 키토에서 버스 약 1시간</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -9049,7 +9049,7 @@
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>도시 외곽 — 소도시 히가시마쓰야마 중심까지 기차 약 100분 (도쿄에서 기차 약 60분)</t>
+          <t>준도시 — 소도시 히가시마쓰야마 중심까지 기차 약 100분 (도쿄에서 기차 약 60분)</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>도시 외곽 — 소도시 코다이라 중심까지 기차 약 45분 (도쿄에서 기차 약 60분)</t>
+          <t>준도시 — 소도시 코다이라 중심까지 기차 약 45분 (도쿄에서 기차 약 60분)</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>도시 외곽 — 소도시·마을(세고비아) 소재, 마드리드에서 버스 약 60분</t>
+          <t>준도시 — 소도시·마을(세고비아) 소재, 마드리드에서 버스 약 60분</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
@@ -15217,7 +15217,7 @@
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>도시 외곽 — 소도시·마을(포츠담) 소재, 시러큐스에서 버스 약 5시간</t>
+          <t>준도시 — 소도시·마을(포츠담) 소재, 시러큐스에서 버스 약 5시간</t>
         </is>
       </c>
       <c r="K197" s="2" t="inlineStr">
@@ -15371,7 +15371,7 @@
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>도시 외곽 — 소도시·마을(풀먼) 소재, 스포캔에서 버스 약 2시간</t>
+          <t>준도시 — 소도시·마을(풀먼) 소재, 스포캔에서 버스 약 2시간</t>
         </is>
       </c>
       <c r="K199" s="2" t="inlineStr">

--- a/out/universities.xlsx
+++ b/out/universities.xlsx
@@ -1316,7 +1316,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>현지어</t>
+          <t>독일어, 영어</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>프랑스어, 영어</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>현지어</t>
+          <t>포르투갈어</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>GPA:시트 · 어학:시트 · 수업언어:확인필요 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>현지어</t>
+          <t>포르투갈어</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>GPA:시트 · 어학:이메일문의 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:시트 · 어학:이메일문의 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>현지어</t>
+          <t>포르투갈어</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>영어, 프랑스어</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>현지어</t>
+          <t>프랑스어</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>GPA:이메일문의 · 어학:이메일문의 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:이메일문의 · 어학:이메일문의 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>현지어</t>
+          <t>프랑스어</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>프랑스어, 영어</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>중국어, 영어</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>중국어, 영어</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>영어</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>GPA:시트 · 어학:이메일문의 · 수업언어:확인필요 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:시트 · 어학:이메일문의 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>중국어, 영어</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>현지어</t>
+          <t>중국어, 영어</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>GPA:시트 · 어학:시트 · 수업언어:확인필요 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr"/>
@@ -5137,7 +5137,7 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>현지어</t>
+          <t>프랑스어, 영어</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>프랑스어, 영어</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>프랑스어, 영어</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>프랑스어, 영어</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>프랑스어, 영어</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>프랑스어, 영어</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>프랑스어, 영어</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>프랑스어, 영어</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>현지어</t>
+          <t>프랑스어</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>프랑스어, 영어</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>프랑스어, 영어</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>독일어, 영어</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>독일어, 영어</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>독일어, 영어</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>독일어, 영어</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>독일어, 영어</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>독일어, 영어</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>GPA:이메일문의 · 어학:시트 · 수업언어:확인필요 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:이메일문의 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>독일어, 영어</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>독일어, 영어</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
@@ -7396,7 +7396,7 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>독일어, 영어</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>독일어, 영어</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>독일어, 영어</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
@@ -7619,7 +7619,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>독일어, 영어</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>독일어, 영어</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>독일어, 영어</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
@@ -7996,7 +7996,7 @@
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>독일어, 영어</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
@@ -8069,7 +8069,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>독일어, 영어</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
@@ -8442,7 +8442,7 @@
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>현지어</t>
+          <t>헝가리어, 영어</t>
         </is>
       </c>
       <c r="L107" s="2" t="inlineStr">
@@ -8452,7 +8452,7 @@
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -8519,7 +8519,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>인도네시아어, 영어</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
@@ -8529,7 +8529,7 @@
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>GPA:시트 · 어학:시트 · 수업언어:확인필요 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -8673,7 +8673,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>이탈리아어, 영어</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>이탈리아어, 영어</t>
         </is>
       </c>
       <c r="L111" s="2" t="inlineStr">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>GPA:시트 · 어학:시트 · 수업언어:확인필요 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
@@ -8900,7 +8900,7 @@
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>이탈리아어, 영어</t>
         </is>
       </c>
       <c r="L113" s="2" t="inlineStr">
@@ -8977,7 +8977,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>일본어, 영어</t>
         </is>
       </c>
       <c r="L114" s="2" t="inlineStr">
@@ -9054,7 +9054,7 @@
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>일본어</t>
         </is>
       </c>
       <c r="L115" s="2" t="inlineStr">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>GPA:시트 · 어학:시트 · 수업언어:확인필요 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
@@ -9131,7 +9131,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>현지어</t>
+          <t>일본어</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -9208,7 +9208,7 @@
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>일본어, 영어</t>
         </is>
       </c>
       <c r="L117" s="2" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>현지어</t>
+          <t>일본어</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
@@ -9358,7 +9358,7 @@
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>일본어, 영어</t>
         </is>
       </c>
       <c r="L119" s="2" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>일본어, 영어</t>
         </is>
       </c>
       <c r="L121" s="2" t="inlineStr">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>현지어</t>
+          <t>일본어</t>
         </is>
       </c>
       <c r="L122" s="2" t="inlineStr">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>현지어</t>
+          <t>일본어, 영어</t>
         </is>
       </c>
       <c r="L123" s="2" t="inlineStr">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
@@ -9735,7 +9735,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>일본어, 영어</t>
         </is>
       </c>
       <c r="L124" s="2" t="inlineStr">
@@ -9812,7 +9812,7 @@
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>일본어, 영어</t>
         </is>
       </c>
       <c r="L125" s="2" t="inlineStr">
@@ -9966,7 +9966,7 @@
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>일본어, 영어</t>
         </is>
       </c>
       <c r="L127" s="2" t="inlineStr">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>일본어, 영어</t>
         </is>
       </c>
       <c r="L128" s="2" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>일본어, 영어</t>
         </is>
       </c>
       <c r="L129" s="2" t="inlineStr">
@@ -10197,7 +10197,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>일본어, 영어</t>
         </is>
       </c>
       <c r="L130" s="2" t="inlineStr">
@@ -10270,7 +10270,7 @@
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>영어</t>
         </is>
       </c>
       <c r="L131" s="2" t="inlineStr">
@@ -10280,7 +10280,7 @@
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>GPA:시트 · 어학:시트 · 수업언어:확인필요 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N131" s="2" t="inlineStr">
@@ -10424,7 +10424,7 @@
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>스페인어, 영어</t>
         </is>
       </c>
       <c r="L133" s="2" t="inlineStr">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>네덜란드어, 영어</t>
         </is>
       </c>
       <c r="L135" s="2" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>현지어</t>
+          <t>스페인어</t>
         </is>
       </c>
       <c r="L147" s="2" t="inlineStr">
@@ -11488,7 +11488,7 @@
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>GPA:이메일문의 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:이메일문의 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N147" s="2" t="inlineStr">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>폴란드어, 영어</t>
         </is>
       </c>
       <c r="L148" s="2" t="inlineStr">
@@ -11628,7 +11628,7 @@
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>포르투갈어, 영어</t>
         </is>
       </c>
       <c r="L149" s="2" t="inlineStr">
@@ -11930,7 +11930,7 @@
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>스페인어, 영어</t>
         </is>
       </c>
       <c r="L153" s="2" t="inlineStr">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>현지어</t>
+          <t>스페인어</t>
         </is>
       </c>
       <c r="L154" s="2" t="inlineStr">
@@ -12311,7 +12311,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>스페인어, 영어</t>
         </is>
       </c>
       <c r="L158" s="2" t="inlineStr">
@@ -12769,7 +12769,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>독일어, 영어</t>
         </is>
       </c>
       <c r="L164" s="2" t="inlineStr">
@@ -12846,7 +12846,7 @@
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>독일어, 영어</t>
         </is>
       </c>
       <c r="L165" s="2" t="inlineStr">
@@ -12919,7 +12919,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>독일어, 영어</t>
         </is>
       </c>
       <c r="L166" s="2" t="inlineStr">
@@ -12996,7 +12996,7 @@
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>중국어, 영어</t>
         </is>
       </c>
       <c r="L167" s="2" t="inlineStr">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="K169" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>중국어, 영어</t>
         </is>
       </c>
       <c r="L169" s="2" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>중국어, 영어</t>
         </is>
       </c>
       <c r="L170" s="2" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
-          <t>현지어</t>
+          <t>중국어, 영어</t>
         </is>
       </c>
       <c r="L171" s="2" t="inlineStr">
@@ -13306,7 +13306,7 @@
       </c>
       <c r="M171" s="2" t="inlineStr">
         <is>
-          <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N171" s="2" t="inlineStr">
@@ -13373,7 +13373,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>중국어, 영어</t>
         </is>
       </c>
       <c r="L172" s="2" t="inlineStr">
@@ -13596,7 +13596,7 @@
       </c>
       <c r="K175" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>태국어, 영어</t>
         </is>
       </c>
       <c r="L175" s="2" t="inlineStr">
@@ -13665,7 +13665,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>현지어</t>
+          <t>터키어, 영어</t>
         </is>
       </c>
       <c r="L176" s="2" t="inlineStr">
@@ -13675,7 +13675,7 @@
       </c>
       <c r="M176" s="2" t="inlineStr">
         <is>
-          <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N176" s="2" t="inlineStr">
@@ -13742,7 +13742,7 @@
       </c>
       <c r="K177" s="2" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>터키어, 영어</t>
         </is>
       </c>
       <c r="L177" s="2" t="inlineStr">
@@ -13819,7 +13819,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>터키어, 영어</t>
         </is>
       </c>
       <c r="L178" s="2" t="inlineStr">
@@ -13829,7 +13829,7 @@
       </c>
       <c r="M178" s="2" t="inlineStr">
         <is>
-          <t>GPA:시트 · 어학:시트 · 수업언어:확인필요 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N178" s="2" t="inlineStr">

--- a/out/universities.xlsx
+++ b/out/universities.xlsx
@@ -853,7 +853,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3.0 / 4.0</t>
+          <t>3.0/4.0</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2.5 on 4-point scale</t>
+          <t>2.5/4.0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4 out of 7</t>
+          <t>4.0/7.0</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>according to home institution</t>
+          <t>제한 없음 (홈교 기준)</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2.0 out of 4.0</t>
+          <t>2.0/4.0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>60%/100</t>
+          <t>60/100</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2.5 out of 4.0 - or 70%</t>
+          <t>2.5/4.0</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Good academic standing as defined by Yonsei</t>
+          <t>Good standing (수치 기준 없음)</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2.7 / 4.3</t>
+          <t>2.7/4.3</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3.0 out of 4.0</t>
+          <t>3.0/4.0</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2.5 for Cumbaya and 3 for Galapagos</t>
+          <t>2.5/4.0 (갈라파고스 캠퍼스 3.0/4.0)</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>3 on a scale 1-5</t>
+          <t>3.0/5.0</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>0~20</t>
+          <t>명시 없음 (프랑스식 0~20 체계)</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>No minimum GPA required but required academic level : For Bachelor 2 level : Required academic level: minimum 1 year of completed studies / 60 ECTS credits. For Bachelor 3 level : Required academic level: minimum 2 years of completed studies / 120 ECTS credits. For Master 1 level (PGE2 &amp; MSc1) : Required academic level: minimum 3 years of completed studies / 180 ECTS credits. For Master 2 level (PGE3 &amp; MSc2) : Required academic level: minimum 4 years of studies / 240 ECTS credits.</t>
+          <t>제한 없음 (학년별 최소 이수학점/ECTS 요건만)</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>excellent academic standard</t>
+          <t>명시 없음 (우수한 성적 요구)</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>Good standing</t>
+          <t>Good standing (수치 기준 없음)</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -8198,7 +8198,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>3.33/4.3 (B+), 2:1 또는 3.0/4.0 (법·경영 제외)</t>
+          <t>3.3/4.3 (법·경영 제외 전공은 3.0/4.0)</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -8417,7 +8417,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>2.5/4.0 or 3.5/5.0</t>
+          <t>2.5/4.0 (또는 3.5/5.0)</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>3.0 out of 4.0</t>
+          <t>3.0/4.0</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -8875,7 +8875,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>Bocconi University does not foresee any specific GPA requirements as we fully trust our partner’s selection. The Grading scale used at Bocconi University ranges from 18 to 30. Being 30 the highest grade, and 18 the lowest pass grade.</t>
+          <t>제한 없음/명시 없음</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -8952,7 +8952,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>2.0 / 4.0</t>
+          <t>2.0/4.0</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>GPA 2.5/4.0</t>
+          <t>2.5/4.0</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -10322,7 +10322,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>70% of maximum grade</t>
+          <t>70/100</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -10399,7 +10399,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>2.5/4.0 (USA System), 80 (Mexican System)</t>
+          <t>2.5/4.0 (멕시코식 80/100)</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -10776,7 +10776,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>Differs per programme</t>
+          <t>프로그램별 상이</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>School of Business and Economics: null, Univeristy College Maastricht: 3.0/4.0, Maastricht Science Programme: 3.0/4.0</t>
+          <t>3.0/4.0 (경영경제대학 SBE는 제한 없음)</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -11015,7 +11015,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>sufficient courses in Microeconomics, Macroeconomics, Statistics and Mathematics</t>
+          <t>명시 없음 (미시·거시경제, 통계, 수학 선수과목 요구)</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -11311,7 +11311,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C 이상 (ECTS 등급)</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -11603,7 +11603,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>12.50 out of 20</t>
+          <t>12.5/20</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>3.0 on a 5.0 scale</t>
+          <t>3.0/5.0</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
@@ -11753,7 +11753,7 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>CGPA of at least 3.3/5 or equivalent</t>
+          <t>3.3/5.0</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
@@ -13198,7 +13198,7 @@
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>3.0/4.0 (ECE), 3.5/5.0 or 3.0/4.0 (CS), 2.75/4.0 (Bioscience)</t>
+          <t>2.75~3.0/4.0 (전공별 상이)</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
@@ -13648,7 +13648,7 @@
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>4.00 grading scale</t>
+          <t>명시 없음 (4.0 스케일만 기재)</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
@@ -13942,7 +13942,7 @@
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>3.3 on a 4.0 scale (3.0 with strong academic motivation)</t>
+          <t>3.3/4.0 (학업동기 우수 시 3.0/4.0)</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
@@ -14088,7 +14088,7 @@
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>UK 2.2 (50%)</t>
+          <t>50/100 (UK 2:2)</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
@@ -14165,7 +14165,7 @@
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>3.0 on a 4.0 scale</t>
+          <t>3.0/4.0</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
@@ -14465,7 +14465,7 @@
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t>3.5 GPA out of 5.0/B/80 out of 100 (or 3.0 out of 4.0 Grade Point Average system)</t>
+          <t>3.0/4.0 (또는 3.5/5.0, 80/100)</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>2.6 out of 4.0</t>
+          <t>2.6/4.0</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
@@ -14761,7 +14761,7 @@
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>3.0 on a 4.0 scale</t>
+          <t>3.0/4.0</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
@@ -15351,7 +15351,7 @@
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t>3.0 on a 4.0 scale</t>
+          <t>3.0/4.0</t>
         </is>
       </c>
       <c r="G199" s="2" t="inlineStr">
@@ -15424,7 +15424,7 @@
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3.0/4.0</t>
         </is>
       </c>
       <c r="G200" s="2" t="inlineStr">
@@ -15655,7 +15655,7 @@
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>2.5 on a 4.0 scale</t>
+          <t>2.5/4.0</t>
         </is>
       </c>
       <c r="G203" s="2" t="inlineStr">
@@ -15728,7 +15728,7 @@
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>3.0 out of 4.0</t>
+          <t>3.0/4.0</t>
         </is>
       </c>
       <c r="G204" s="2" t="inlineStr">
@@ -16032,7 +16032,7 @@
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t>2.5 on 4.0 scale (undergraduates)</t>
+          <t>2.5/4.0</t>
         </is>
       </c>
       <c r="G208" s="2" t="inlineStr">
@@ -16109,7 +16109,7 @@
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
-          <t>3.0 on 4.0 scale</t>
+          <t>3.0/4.0</t>
         </is>
       </c>
       <c r="G209" s="2" t="inlineStr">
@@ -16259,7 +16259,7 @@
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
-          <t>3.0 / 4.0</t>
+          <t>3.0/4.0</t>
         </is>
       </c>
       <c r="G211" s="2" t="inlineStr">
@@ -16336,7 +16336,7 @@
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
-          <t>3.00 out of 4.00 cumulative GPA</t>
+          <t>3.0/4.0</t>
         </is>
       </c>
       <c r="G212" s="2" t="inlineStr">
@@ -16413,7 +16413,7 @@
       </c>
       <c r="F213" s="2" t="inlineStr">
         <is>
-          <t>3.0 out of 4.0</t>
+          <t>3.0/4.0</t>
         </is>
       </c>
       <c r="G213" s="2" t="inlineStr">

--- a/out/universities.xlsx
+++ b/out/universities.xlsx
@@ -640,12 +640,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>30 - 40 units (3 -4 courses)</t>
+          <t>30~40 units (3~4과목)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>50 units (5 courses)</t>
+          <t>50 units (5과목)</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37.5 credit points per semester</t>
+          <t>37.5 credit points</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50 credit points per semester</t>
+          <t>50 credit points</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22.5 ECTS / 18 UWA cp</t>
+          <t>18 UWA credit points (22.5 ECTS)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30 ECTS / 24 UWA cp</t>
+          <t>24 UWA credit points (30 ECTS)</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -863,12 +863,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18 UoC per half year</t>
+          <t>18 UoC</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24 UoC per half year</t>
+          <t>24 UoC</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -940,12 +940,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36 QUT credits (22.5 ECTS) per semester</t>
+          <t>36 QUT credits (22.5 ECTS)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48 QUT credits (30 ECTS) per semester</t>
+          <t>48 QUT credits (30 ECTS)</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1017,12 +1017,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Credit Information can be found here https://www.uts.edu.au/for-students/international/study-abroad-exchange-uts/subjects-and-academic-information</t>
+          <t>18 credit points</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Credit Information can be found here https://www.uts.edu.au/for-students/international/study-abroad-exchange-uts/subjects-and-academic-information</t>
+          <t>24 credit points</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3 courses</t>
+          <t>3과목</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4 courses</t>
+          <t>4과목</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1161,8 +1161,16 @@
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
           <t>준도시 — 캔버라 도심까지 버스 약 15분</t>
@@ -1228,12 +1236,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21(if they want to do more or less we need a confirmation from their university)</t>
+          <t>21 ECTS (증감 시 홈교 확인)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30 ECTS</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1301,12 +1309,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16 ECTS (recommended)</t>
+          <t>16 ECTS</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>제한 없음</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1374,12 +1382,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18 ECTS</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30 ECTS</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1451,7 +1459,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1528,12 +1536,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20 ECTS</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30 ECTS</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1605,7 +1613,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1682,12 +1690,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1 course (5 ECTS)/semester</t>
+          <t>5 ECTS (1과목)</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30 ECTS/semester</t>
+          <t>30 ECTS</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1759,12 +1767,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10 ects + French evening course</t>
+          <t>10 ECTS (+프랑스어 야간강좌)</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30 ects</t>
+          <t>30 ECTS</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1836,12 +1844,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18 ECTS per semester</t>
+          <t>18 ECTS</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33 ECTS per semester</t>
+          <t>33 ECTS</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1913,12 +1921,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16 Unisinos Academic Credits</t>
+          <t>16 Unisinos credits</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>제한 없음</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1990,12 +1998,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>This is for the home university of the student to deliberate.</t>
+          <t>홈교 기준</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>This is for the home university of the student to deliberate.</t>
+          <t>홈교 기준</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2067,12 +2075,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>15 credits</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>32 credits</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2144,12 +2152,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9 Canadian credits (3 courses)</t>
+          <t>9 credits (3과목)</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15 Canadian credits (5 courses)</t>
+          <t>15 credits (5과목)</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2217,12 +2225,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25 credits</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30 credits</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -2371,12 +2379,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Undergraduate students are required to take a minimum of 9 credit units (or 3 courses)</t>
+          <t>9 credit units (3과목)</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Undergraduate students a maximum is 15 credit units (or 5 courses) per term</t>
+          <t>15 credit units (5과목)</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2442,8 +2450,16 @@
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
           <t>도시 — 몬트리올 도심에 위치</t>
@@ -2513,12 +2529,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12 credits</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>15 credits</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2590,12 +2606,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9 SFU units (3 courses)</t>
+          <t>9 SFU units (3과목)</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>18 SFU units (4~5 courses), NOT recommended.</t>
+          <t>18 SFU units (4~5과목, 비권장)</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2667,12 +2683,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6 credits</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>15 credits</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2739,8 +2755,16 @@
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
           <t>준도시 — 밴쿠버 도심까지 버스 약 25분</t>
@@ -2804,8 +2828,16 @@
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
           <t>도시 — 토론토 도심에 위치</t>
@@ -2871,12 +2903,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>https://international.umontreal.ca/english/international-students/student-exchange-program/#credits</t>
+          <t>12 credits (학부)</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>https://international.umontreal.ca/english/international-students/student-exchange-program/#credits</t>
+          <t>15 credits (학부)</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2948,12 +2980,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>12 credits (4 courses) per semester</t>
+          <t>12 credits (4과목)</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>15 credits (5 courses) per semester</t>
+          <t>15 credits (5과목)</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -3025,12 +3057,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>It depens on student's home instituation's credit transfer requirements,we will not set limit to students.</t>
+          <t>홈교 기준</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Maximum 12 Credits (1 Credit = 16 Study Hours)</t>
+          <t>12 credits</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -3098,12 +3130,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>depending on the major</t>
+          <t>전공별 상이</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>depending on the major</t>
+          <t>전공별 상이</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -3169,8 +3201,16 @@
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr"/>
-      <c r="I37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
           <t>준도시 — 지난 도심까지 버스 약 30분</t>
@@ -3240,12 +3280,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>We don't have any resitrictions.</t>
+          <t>제한 없음</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>We don't have any resitrictions.</t>
+          <t>제한 없음</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -3315,10 +3355,14 @@
           <t>2학기</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>26 credits (1-6 credits / course)</t>
+          <t>26 credits</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -3391,12 +3435,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>at least enroll in one course; credit requirements follow home school regulations</t>
+          <t>홈교 기준</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>no maximum, subject to availability</t>
+          <t>제한 없음</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -3464,12 +3508,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>We recommend not less than 20 ECTS</t>
+          <t>20 ECTS (권장)</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>We recommend no more that 30 ECTS</t>
+          <t>30 ECTS (권장)</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -3537,12 +3581,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>20 ECTS for MU students</t>
+          <t>20 ECTS</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>No limit, 35-40 is realistic maximum</t>
+          <t>제한 없음 (현실적 최대 35~40 ECTS)</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -3614,12 +3658,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>https://cuni.cz/UKEN-344.html</t>
+          <t>4과목 (학부; 대학원 3과목)</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Undergraduate exchange students are asked to apply to at least four courses, graduate students to at least three ones. Students are expected to check in advance whether the selected courses will be approved for equivalency by their home university.</t>
+          <t>홈교 기준</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -3768,12 +3812,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>20 ECTS per semester</t>
+          <t>20 ECTS</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>35 ECTS per semester</t>
+          <t>35 ECTS</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -3845,12 +3889,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>no requirement</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>no requirement</t>
+          <t>제한 없음</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -3912,8 +3956,16 @@
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr"/>
-      <c r="I47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
           <t>준도시 — 소도시 로스킬데 시내 (코펜하겐에서 기차 약 45분)</t>
@@ -3979,12 +4031,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30 ECTS</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>30 per semester</t>
+          <t>30 ECTS</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -4061,7 +4113,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>16 credits</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -4129,12 +4181,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>제한 없음</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -4206,12 +4258,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>20 ECTS credits</t>
+          <t>20 ECTS</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>No maximum has been set.</t>
+          <t>제한 없음</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -4283,12 +4335,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>No minimum credits required. The regular study pace is 20-30 ECTS credits per semester</t>
+          <t>명시 없음 (통상 20~30 ECTS)</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>No maximum. Students are recommended to take 20-30 ECTS credits per semester.</t>
+          <t>제한 없음 (권장 20~30 ECTS)</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -4360,12 +4412,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25 ECTS</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>35 ECTS</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -4437,12 +4489,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20 ECTS</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30 ECTS</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -4519,7 +4571,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>No limit</t>
+          <t>제한 없음</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -4587,12 +4639,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>30 ECTS/semester</t>
+          <t>30 ECTS</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>제한 없음</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -4664,12 +4716,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>24-30 ECTS (30 ECTS is normal workload) per semester</t>
+          <t>24~30 ECTS</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>30-36 ECTS per semester</t>
+          <t>30~36 ECTS</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -4741,12 +4793,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Up to SKKU, no min.</t>
+          <t>홈교 기준</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Up to SKKU, no max.</t>
+          <t>홈교 기준</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -4818,12 +4870,12 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Normal study load is 30 ECTS per semester, completing a little less (liek 20 ECTS) is ok.</t>
+          <t>명시 없음 (통상 30 ECTS)</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>no maximum, but as 30 ECTS is a full time study load per semester, we do not recommend going a lot over</t>
+          <t>제한 없음 (통상 30 ECTS)</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -4891,12 +4943,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>20 ECT/semester</t>
+          <t>20 ECTS</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>제한 없음</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -4968,7 +5020,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>SKKU decides</t>
+          <t>홈교 기준</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -5045,12 +5097,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>180 crdits ECTS or equivalents</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40 ECTS</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -5122,12 +5174,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20 ECTS</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>35 ECTS</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -5276,7 +5328,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>No minimum credits/ECTS required. Exchange students must comply with the regulations of their home university.</t>
+          <t>홈교 기준</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -5353,12 +5405,12 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>MINIMUM credits: 8 ECTS</t>
+          <t>8 ECTS</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>No MAXIMUM credits for DEUF program. 31MAXIMUM credits for SELF program</t>
+          <t>제한 없음 (SELF 프로그램은 31 ECTS)</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -5576,12 +5628,12 @@
       <c r="G69" s="2" t="inlineStr"/>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>15 ECTS credits</t>
+          <t>15 ECTS</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>30 ECTS credits or 21 ECTS credits (depending the program)</t>
+          <t>30 ECTS (프로그램에 따라 21 ECTS)</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -5653,12 +5705,12 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>The home university determines the minimum credits</t>
+          <t>홈교 기준</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>30 credits per semester.</t>
+          <t>30 credits</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -6034,12 +6086,12 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Depend of hosting department</t>
+          <t>학과별 상이</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>Depend of hosting department</t>
+          <t>학과별 상이</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -6111,12 +6163,12 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20 ECTS</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30 ECTS</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -6265,12 +6317,12 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>It depends on the exchange, please check how many ECTs are required in the link: https://www.tbs-education.com/about-tbs/international/incoming-exchange-students/</t>
+          <t>24 ECTS</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>It depends on the exchange, please check how many ECTs are required in the link: https://www.tbs-education.com/about-tbs/international/incoming-exchange-students/</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -6342,7 +6394,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
@@ -6415,12 +6467,12 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Depends on SKKU</t>
+          <t>홈교 기준</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30 ECTS</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -6569,12 +6621,12 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10 ECTS</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>no max</t>
+          <t>제한 없음</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -6644,8 +6696,16 @@
           <t>2학기</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr"/>
-      <c r="I83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
           <t>준도시 — 부퍼탈 도심까지 기차 약 15분</t>
@@ -6711,12 +6771,12 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>No requirement</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>No requirement</t>
+          <t>제한 없음</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -6781,12 +6841,12 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>제한 없음</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -6935,12 +6995,12 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>제한 없음</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -7008,12 +7068,12 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>15 ECTS</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30 ECTS</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -7081,12 +7141,12 @@
       <c r="G89" s="2" t="inlineStr"/>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>The standard semester workload comprises 30 ECTS credits.</t>
+          <t>명시 없음 (통상 30 ECTS)</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>A standard module at Leuphana University comprises 5 ECTS credits</t>
+          <t>명시 없음 (모듈당 5 ECTS)</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
@@ -7154,12 +7214,12 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>제한 없음</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -7227,12 +7287,12 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>N/A; regular workload would be 5 courses/30 ECTS</t>
+          <t>명시 없음 (통상 30 ECTS/5과목)</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -7304,12 +7364,12 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>no requirements</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>approx. 25 to 30 (depending on the courses offered in English and personal preferences etc.)</t>
+          <t>약 25~30 ECTS</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -7381,12 +7441,12 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>20 ECTS per semester (recommended)</t>
+          <t>20 ECTS</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>32.5 ECTS per semester (recommended)</t>
+          <t>32.5 ECTS</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -7454,12 +7514,12 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>No requirement</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>No requirement</t>
+          <t>제한 없음</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -7527,12 +7587,12 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>No limit</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>No limit</t>
+          <t>제한 없음</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -7604,7 +7664,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>not specified</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
@@ -7682,7 +7742,7 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>30-35 ECTS</t>
+          <t>30~35 ECTS</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -7754,12 +7814,12 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>The minimum workload is one module (6 ECTS)</t>
+          <t>6 ECTS (1모듈)</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>The maximum workload is five modules (30 ECTS)</t>
+          <t>30 ECTS (5모듈)</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -7908,12 +7968,12 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>It is recommended that students take between 12 and 18 contact hours per semester for a total of around 30 ECTS credits per semester.</t>
+          <t>명시 없음 (권장 약 30 ECTS)</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>It is recommended that students take between 12 and 18 contact hours per semester for a total of around 30 ECTS credits per semester.</t>
+          <t>명시 없음 (권장 약 30 ECTS)</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -7981,12 +8041,12 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>15 ECTS</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30 ECTS</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -8056,10 +8116,14 @@
           <t>2학기</t>
         </is>
       </c>
-      <c r="H102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>We recommend a maximum of 30 ECTS per semester.</t>
+          <t>30 ECTS (권장)</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -8208,12 +8272,12 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>24-30 ECTS credits</t>
+          <t>24~30 ECTS</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>36 ECTS credits</t>
+          <t>36 ECTS</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -8427,12 +8491,12 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10 ECTS</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30 ECTS</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
@@ -8581,12 +8645,12 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Maximum 15 credit units/semester</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>Maximum 15 credit units/semester</t>
+          <t>15 credits</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
@@ -8658,12 +8722,12 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>N.A.</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>N.A.</t>
+          <t>제한 없음</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
@@ -8735,12 +8799,12 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>https://www.polimi.it/en/exchange-students-incoming/after-acceptance/exchange-programmes/before-arrival</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>https://www.polimi.it/en/exchange-students-incoming/after-acceptance/exchange-programmes/before-arrival</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
@@ -8812,12 +8876,12 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>This is up to the Home University</t>
+          <t>홈교 기준</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>Up to 30 per semester</t>
+          <t>30 ECTS</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
@@ -8885,12 +8949,12 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>There is no minimum number of course credits required. However, incoming exchange students must select minimum 1 course.</t>
+          <t>명시 없음 (최소 1과목)</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>Please note that there is no limit to the number of course credits, as long as students stay within the limit of a maximum of 5 courses.</t>
+          <t>제한 없음 (최대 5과목)</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
@@ -8962,12 +9026,12 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>10-credits per semester</t>
+          <t>10 credits</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>No limit</t>
+          <t>제한 없음</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
@@ -9044,7 +9108,7 @@
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>제한 없음</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
@@ -9116,12 +9180,12 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>제한 없음</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
@@ -9198,7 +9262,7 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>(there is no particular limit)</t>
+          <t>제한 없음</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
@@ -9266,12 +9330,12 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>제한 없음</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
@@ -9343,12 +9407,12 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>There are no minimum credits but they have to take 6 slots per week to maitain their visa status.</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>14 credits per quarter, 28 credits per semester</t>
+          <t>14 credits/쿼터 (28 credits/학기)</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
@@ -9416,12 +9480,12 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10 credits</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>24 credits</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
@@ -9493,12 +9557,12 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>International students are required by Japanese law to attend a minimum of 10 hours of classes per week. Since one class session lasts for 95 minutes at Ritsumeikan University, students must take at least 7 class sessions of classes per week. Students can register up to a maximum of 20 credits per semester, including Japanese classes.</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>20 RU credits</t>
+          <t>20 credits</t>
         </is>
       </c>
       <c r="J121" s="2" t="inlineStr">
@@ -9570,12 +9634,12 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>제한 없음</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
@@ -9647,12 +9711,12 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>There is no minimum credits</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>There is no maximum credits</t>
+          <t>제한 없음</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
@@ -9720,12 +9784,12 @@
       <c r="G124" s="2" t="inlineStr"/>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>7credits or more per semester</t>
+          <t>7 credits</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>There is no upper limit.</t>
+          <t>제한 없음</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
@@ -9797,12 +9861,12 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>Minimum 15 credits per semester (or 30 credits per year)</t>
+          <t>15 credits (연간 30)</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>There is not maximum limitation.</t>
+          <t>제한 없음</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
@@ -9951,12 +10015,12 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>https://www.toyo.ac.jp/academics/international-exchange/prospective/exchange_program/</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>https://www.toyo.ac.jp/academics/international-exchange/prospective/exchange_program/</t>
+          <t>제한 없음</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
@@ -10028,12 +10092,12 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>HUSTEP: Spring Half year course students must register for 7 or more timeslots a week to complete visa requirement.</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>HUSTEP: N/A</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
@@ -10105,12 +10169,12 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>Minimum workload per term/semester (in units/credits): Please check each website: COLABS, JYPE, DEEP and IPLA.</t>
+          <t>프로그램별 상이 (COLABS/JYPE/DEEP/IPLA)</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>Maximum workload per term/semester (in units/credits): Up to 24 credits per semester. (Credit System: 1 Tohoku University credit is awarded for 45 hours of school work.) Average no. of units/credit per course: 2.0 TU credits (Two credits are given for most of the lecture courses that meet once a week for 90 minutes.) Regular term/semester workload for full-time undergraduate students (in units/credits): Each semester consists of 15 weeks of course work. Total workload for full-time undergraduate programme (no. of units/credits and no. of years): Up to 48 credits per year (up to 24 credits per semester)</t>
+          <t>24 credits</t>
         </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
@@ -10182,12 +10246,12 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>46005.0</t>
+          <t>6과목 (JTW, 과목당 보통 2 credits)</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20 credits</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
@@ -10255,12 +10319,12 @@
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>9US/15ECTS</t>
+          <t>9 US credits (15 ECTS)</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>18 US/30ECTS</t>
+          <t>18 US credits (30 ECTS)</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
@@ -10332,12 +10396,12 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>24 ECTS per semester</t>
+          <t>24 ECTS</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>Recommended - 36 ECTS per semester</t>
+          <t>36 ECTS (권장)</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
@@ -10409,12 +10473,12 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>3 TEC Credits - 1 Tec credit = 1.67 ECTS</t>
+          <t>3 TEC credits (약 5 ECTS)</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>18 TEC Credits - 1 Tec credit = 1.67 ECTS</t>
+          <t>18 TEC credits (약 30 ECTS)</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
@@ -10559,12 +10623,12 @@
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>For us: 0, but in order to get a visa you need 25 ECTS</t>
+          <t>제한 없음 (비자상 25 ECTS 필요)</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>Full time courseload is 30 ECTS/semester. We don't enforce a maximum but advice not to take more courses than that.</t>
+          <t>제한 없음 (통상 30 ECTS)</t>
         </is>
       </c>
       <c r="J135" s="2" t="inlineStr">
@@ -10632,7 +10696,7 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>Minimum 1 course (most courses are 6 ECTS but some are 3, 4 or 5)</t>
+          <t>1과목 (보통 6 ECTS)</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
@@ -10709,12 +10773,12 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30 ECTS</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36 ECTS</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
@@ -10786,12 +10850,12 @@
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>30ECTS</t>
+          <t>30 ECTS</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>30ECTS</t>
+          <t>30 ECTS</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
@@ -10866,17 +10930,12 @@
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>1. School of Business and Economics: As exchange student, you can only register for a maximum of two courses per period (max. 13 ECTS credits) with a minimum of one course per period (5 / 6.5 ECTS credits), and only one skills training per period (4 ECTS credits). Skills trainings are not compulsory for exchange students. At SBE, we consider a fulltime study load per semester to be four courses and one skills training. Period 1: maximum two courses (max. 13 ECTS credits), minimum one course (5/6.5 ECTS credits) Period 2: maximum two courses (max. 13 ECTS credits), minimum one course (5/6.5 ECTS credits) Period 3: maximum one skills training (max. 4 ECTS credits) Period 4: maximum two courses (max. 13 ECTS credits), minimum one course (5/6.5 ECTS credits) Period 5: maximum two courses (max. 13 ECTS credits), minimum one course (5/6.5 ECTS credits) Period 6: maximum one skills training (max. 4 ECTS credits)
- 2. Univeristy College Maastricht: 20 ECTS
- 3. Maastricht Science Programme: No minimum but preferably 30 per semester</t>
+          <t>학부별 상이 (UCM 20 ECTS 등)</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>1. School of Business and Economics: 
- As exchange student, you can only register for a maximum of two courses per period (max. 13 ECTS credits) with a minimum of one course per period (5 / 6.5 ECTS credits), and only one skills training per period (4 ECTS credits). Skills trainings are not compulsory for exchange students. At SBE, we consider a fulltime study load per semester to be four courses and one skills training. Period 1: maximum two courses (max. 13 ECTS credits), minimum one course (5/6.5 ECTS credits) Period 2: maximum two courses (max. 13 ECTS credits), minimum one course (5/6.5 ECTS credits) Period 3: maximum one skills training (max. 4 ECTS credits) Period 4: maximum two courses (max. 13 ECTS credits), minimum one course (5/6.5 ECTS credits) Period 5: maximum two courses (max. 13 ECTS credits), minimum one course (5/6.5 ECTS credits) Period 6: maximum one skills training (max. 4 ECTS credits)
- 2. Univeristy College Maastricht: 30 ECTS
- 3. Maastricht Science Programme: 30 ECTS</t>
+          <t>30 ECTS (학부별 상이)</t>
         </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
@@ -10952,12 +11011,12 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>fixed course packages of 30 ECTS</t>
+          <t>30 ECTS (고정 패키지)</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>fixed course packages of 30 ECTS</t>
+          <t>30 ECTS (고정 패키지)</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
@@ -11025,12 +11084,12 @@
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>24 ECTS recommended</t>
+          <t>24 ECTS (권장)</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30 ECTS</t>
         </is>
       </c>
       <c r="J141" s="2" t="inlineStr">
@@ -11098,12 +11157,12 @@
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30 ECTS</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>35 (minor including Dutch for beginners course)</t>
+          <t>35 ECTS</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
@@ -11171,12 +11230,12 @@
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>24 per semester</t>
+          <t>24 ECTS</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>36 per semester</t>
+          <t>36 ECTS</t>
         </is>
       </c>
       <c r="J143" s="2" t="inlineStr">
@@ -11248,12 +11307,12 @@
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>15 ECTS</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30 ECTS</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
@@ -11321,12 +11380,12 @@
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>Should adhere to visa requirements. No minimum, but we expect students to be full-time students</t>
+          <t>명시 없음 (풀타임 기대)</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>No maximum</t>
+          <t>제한 없음</t>
         </is>
       </c>
       <c r="J145" s="2" t="inlineStr">
@@ -11394,10 +11453,14 @@
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>30 credits/semester</t>
-        </is>
-      </c>
-      <c r="I146" s="2" t="inlineStr"/>
+          <t>30 credits</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
           <t>준도시 — 소도시 베르겐 시내 (오슬로에서 기차 약 5시간 (300분))</t>
@@ -11463,12 +11526,12 @@
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>At least one course.</t>
+          <t>1과목 이상</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>maximum 22 pucp credits. We recommend to take between 12 to 15,because of the academic workload.</t>
+          <t>22 PUCP credits (권장 12~15)</t>
         </is>
       </c>
       <c r="J147" s="2" t="inlineStr">
@@ -11536,12 +11599,12 @@
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>up to partner institution</t>
+          <t>홈교 기준</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>up to partner institution</t>
+          <t>홈교 기준</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
@@ -11613,12 +11676,12 @@
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>6 ECTS per period/semester</t>
+          <t>6 ECTS</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>36 ECTS per semester</t>
+          <t>36 ECTS</t>
         </is>
       </c>
       <c r="J149" s="2" t="inlineStr">
@@ -11763,12 +11826,12 @@
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>Refer to the link https://gem.ntu.edu.sg/index.cfm?FuseAction=Programs.ViewProgramAngular&amp;id=10006 (Coursework tab)</t>
+          <t>제한 없음</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>Refer to the link https://gem.ntu.edu.sg/index.cfm?FuseAction=Programs.ViewProgramAngular&amp;id=10006 (Coursework tab)</t>
+          <t>20 AU (6과목)</t>
         </is>
       </c>
       <c r="J151" s="2" t="inlineStr">
@@ -11988,12 +12051,12 @@
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20 ECTS</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30 ECTS</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
@@ -12065,12 +12128,12 @@
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>None (but visa may require it)</t>
+          <t>명시 없음 (비자 요건 유의)</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>제한 없음</t>
         </is>
       </c>
       <c r="J155" s="2" t="inlineStr">
@@ -12142,12 +12205,12 @@
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>20 ECTS/semester</t>
+          <t>20 ECTS</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>33 ECTS/semester</t>
+          <t>33 ECTS</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
@@ -12224,7 +12287,7 @@
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>제한 없음</t>
         </is>
       </c>
       <c r="J157" s="2" t="inlineStr">
@@ -12296,12 +12359,12 @@
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>24 ECTS</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30 ECTS</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
@@ -12373,12 +12436,12 @@
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>No minimum ECTS requirement set by IEU. Minimum reqs are set by the home institution.</t>
+          <t>홈교 기준</t>
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>30 ECTS plus optional free 3 ECTS Spanish course</t>
+          <t>30 ECTS (+선택 스페인어 3 ECTS)</t>
         </is>
       </c>
       <c r="J159" s="2" t="inlineStr">
@@ -12446,12 +12509,12 @@
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30 ECTS</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>45 ECTS</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
@@ -12523,12 +12586,12 @@
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30 ECTS</t>
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>45 ECTS</t>
         </is>
       </c>
       <c r="J161" s="2" t="inlineStr">
@@ -12600,12 +12663,12 @@
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>Minimum: 22.5 credits, However, the Swedish Migration Agency requires students to be accepted to full–time studies to issue residence permits for non-EU/EEA students. Full-time study means 30 credits (or higher education points) per term. A residence permit cannot be received for distance learning or online courses.</t>
+          <t>22.5 credits (비EU 비자는 30 필요)</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>37,5</t>
+          <t>37.5 credits</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
@@ -12677,12 +12740,12 @@
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>30 credits/semester</t>
+          <t>30 credits</t>
         </is>
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>45 credits/semester</t>
+          <t>45 credits</t>
         </is>
       </c>
       <c r="J163" s="2" t="inlineStr">
@@ -12754,12 +12817,12 @@
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>A study program of at least 15 ECTS per semester is required by our university.</t>
+          <t>15 ECTS</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>It is recommended not to take more than 30-33 ECTS.</t>
+          <t>30~33 ECTS (권장)</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr">
@@ -12904,12 +12967,12 @@
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>There is no minimum, we recommend between 20-25 ECTS.</t>
+          <t>명시 없음 (권장 20~25 ECTS)</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>Max. 30 ECTS per semester</t>
+          <t>30 ECTS</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr">
@@ -12981,12 +13044,12 @@
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>12 for Undergraduate/ 3 for Graduate</t>
+          <t>12 credits (학부) / 3 (대학원)</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>25 for Undergraduate/ 12 for Graduate</t>
+          <t>25 credits (학부) / 12 (대학원)</t>
         </is>
       </c>
       <c r="J167" s="2" t="inlineStr">
@@ -13054,12 +13117,12 @@
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3 credits</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25 credits</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr">
@@ -13131,12 +13194,12 @@
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>For undergraduates, at least 9 credits for each semester(including a course from host department), for graduates , at least 1 course</t>
+          <t>9 credits (학부; 대학원 1과목)</t>
         </is>
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>。For undergraduate : maximum 25 credits.</t>
+          <t>25 credits (학부)</t>
         </is>
       </c>
       <c r="J169" s="2" t="inlineStr">
@@ -13208,12 +13271,12 @@
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>Minimum 9 NYCU credits per semester = 18 ECTS</t>
+          <t>9 NYCU credits (18 ECTS)</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>제한 없음</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
@@ -13281,12 +13344,12 @@
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25 credits</t>
         </is>
       </c>
       <c r="J171" s="2" t="inlineStr">
@@ -13358,12 +13421,12 @@
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>Exchange students must take 4 NTU credits or 2 courses per semester.</t>
+          <t>4 credits (2과목)</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>Generally, undergraduate students can take a maximum of 25 credits per semester and graduate students can take up to 20 credits per semester, unless otherwise specified by the academic department.</t>
+          <t>25 credits (학부) / 20 (대학원)</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
@@ -13431,12 +13494,12 @@
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>Minimum 9 credits</t>
+          <t>9 credits</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>Maximum 21 credits</t>
+          <t>21 credits</t>
         </is>
       </c>
       <c r="J173" s="2" t="inlineStr">
@@ -13504,12 +13567,12 @@
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>Undergraduate student: 22 credits (approx. 7-8 courses) Graduate student: 6 credits (approx. 2 courses)</t>
+          <t>22 credits (학부) / 6 (대학원)</t>
         </is>
       </c>
       <c r="J174" s="2" t="inlineStr">
@@ -13581,12 +13644,12 @@
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>8 credits</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12 credits</t>
         </is>
       </c>
       <c r="J175" s="2" t="inlineStr">
@@ -13656,8 +13719,16 @@
           <t>2학기</t>
         </is>
       </c>
-      <c r="H176" s="2" t="inlineStr"/>
-      <c r="I176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
           <t>준도시 — 앙카라 도심까지 버스 약 20분</t>
@@ -13727,12 +13798,12 @@
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>No restriction</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>Depends on the choice of Faculty</t>
+          <t>단과대별 상이</t>
         </is>
       </c>
       <c r="J177" s="2" t="inlineStr">
@@ -13804,12 +13875,12 @@
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10 ECTS</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>제한 없음</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
@@ -13881,12 +13952,14 @@
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>Erasmus and Exchange students are expected to take
- 4 - 6 courses, equaling 17- 21 Bogazici credits
- (approximately 20-30 ECTS).</t>
-        </is>
-      </c>
-      <c r="I179" s="2" t="inlineStr"/>
+          <t>17~21 Bogazici credits (약 20~30 ECTS, 4~6과목)</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
           <t>준도시 — 이스탄불 도심까지 버스 약 30분</t>
@@ -13952,12 +14025,12 @@
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>45 credits per semester for semester-only student and 60 per semester for full year</t>
+          <t>45 UK credits</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>60 per semester</t>
+          <t>60 UK credits</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
@@ -14025,12 +14098,12 @@
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>45 UK credits</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>60 UK credits</t>
         </is>
       </c>
       <c r="J181" s="2" t="inlineStr">
@@ -14098,12 +14171,12 @@
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>Students are expected to select 120 Sheffield credits (60 ECTS) for a full academic year or 60 Sheffield credits (30 ECTS) for one semester. Students can take no more than 60 credits per semester or 120 credits for the full academic year. Students can take fewer than 60 credits or 120 credits but must take a minimum of 40 credits for one semester or 100 credits for the academic year. Please indicate via the nomination form whether or not your student has permission to study a reduced credit load.</t>
+          <t>40 UK credits</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>Students are expected to select 120 Sheffield credits (60 ECTS) for a full academic year or 60 Sheffield credits (30 ECTS) for one semester. Students can take no more than 60 credits per semester or 120 credits for the full academic year. Students can take fewer than 60 credits or 120 credits but must take a minimum of 40 credits for one semester or 100 credits for the academic year. Please indicate via the nomination form whether or not your student has permission to study a reduced credit load.</t>
+          <t>60 UK credits (30 ECTS)</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr">
@@ -14175,12 +14248,12 @@
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>20 ECTS for a single semester; 50 for a full academic year</t>
+          <t>20 ECTS</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>30 ECTS for a single semester; 60 for a full academic year</t>
+          <t>30 ECTS</t>
         </is>
       </c>
       <c r="J183" s="2" t="inlineStr">
@@ -14250,10 +14323,14 @@
           <t>4~2학기</t>
         </is>
       </c>
-      <c r="H184" s="2" t="inlineStr"/>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>45 Exeter credits = 22.5 ECTs per semester</t>
+          <t>45 Exeter credits (22.5 ECTS)</t>
         </is>
       </c>
       <c r="J184" s="2" t="inlineStr">
@@ -14325,12 +14402,12 @@
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>30 ECTS (60 Essex credits)</t>
+          <t>60 Essex credits (30 ECTS)</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>30 ECTS (60 Essex credits)</t>
+          <t>60 Essex credits (30 ECTS)</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr">
@@ -14475,12 +14552,12 @@
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>60 Bristol credits (30 ECTs) per semester, 120 Bristol credits (60 ECTs) for full year</t>
+          <t>60 Bristol credits (30 ECTS)</t>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>60 Bristol credits (30 ECTs) per semester (This is the min and max)</t>
+          <t>60 Bristol credits (30 ECTS)</t>
         </is>
       </c>
       <c r="J187" s="2" t="inlineStr">
@@ -14552,12 +14629,12 @@
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>30 ECTS per semester</t>
+          <t>30 ECTS</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>30 ECTS per semester</t>
+          <t>30 ECTS</t>
         </is>
       </c>
       <c r="J188" s="2" t="inlineStr">
@@ -14625,12 +14702,12 @@
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25 UK credits</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30 UK credits</t>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr">
@@ -14698,12 +14775,12 @@
       <c r="G190" s="2" t="inlineStr"/>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>This will be dependent on any Visa requirements. We recommend at least 15 ECTS per semester.</t>
+          <t>명시 없음 (권장 15 ECTS 이상)</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>30ECTS per semester</t>
+          <t>30 ECTS</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr">
@@ -14771,12 +14848,12 @@
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>120 Durham credits</t>
+          <t>120 Durham credits (연간)</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>120 Durham credits</t>
+          <t>120 Durham credits (연간)</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr">
@@ -14848,12 +14925,12 @@
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>60 per semester/120 for a full year</t>
+          <t>60 UK credits (연간 120)</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>60 per semester/120 for a full year</t>
+          <t>60 UK credits (연간 120)</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr">
@@ -14921,14 +14998,12 @@
       <c r="G193" s="2" t="inlineStr"/>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>One semester students must take 60 BCU credits (30 ECTS) = 3-4 modules per semester
- Two semester students (full year) must take 120 BCU credits (60 ECTS) = 6-8 modules</t>
+          <t>60 BCU credits (30 ECTS)</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>One semester students must take 60 BCU credits (30 ECTS) = 3-4 modules per semester
- Two semester students (full year) must take 120 BCU credits (60 ECTS) = 6-8 modules</t>
+          <t>60 BCU credits (30 ECTS)</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr">
@@ -15000,12 +15075,12 @@
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>30 ECTS per semester</t>
+          <t>30 ECTS</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>30 ECTS per semester</t>
+          <t>30 ECTS</t>
         </is>
       </c>
       <c r="J194" s="2" t="inlineStr">
@@ -15071,8 +15146,16 @@
         </is>
       </c>
       <c r="G195" s="2" t="inlineStr"/>
-      <c r="H195" s="2" t="inlineStr"/>
-      <c r="I195" s="2" t="inlineStr"/>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="I195" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
           <t>도시 — 올버니 도심에 위치</t>
@@ -15130,12 +15213,12 @@
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>minimum 12 credits</t>
+          <t>12 US credits</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>maximum 17 credits</t>
+          <t>17 US credits</t>
         </is>
       </c>
       <c r="J196" s="2" t="inlineStr">
@@ -15207,12 +15290,12 @@
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>12 US credits (about 4 classes)</t>
+          <t>12 US credits (약 4과목)</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>18 US credits (about 6 classes)</t>
+          <t>18 US credits (약 6과목)</t>
         </is>
       </c>
       <c r="J197" s="2" t="inlineStr">
@@ -15284,12 +15367,12 @@
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>12 credits</t>
+          <t>12 US credits</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>17 credits</t>
+          <t>17 US credits</t>
         </is>
       </c>
       <c r="J198" s="2" t="inlineStr">
@@ -15361,12 +15444,12 @@
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12 US credits</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18 US credits</t>
         </is>
       </c>
       <c r="J199" s="2" t="inlineStr">
@@ -15434,12 +15517,12 @@
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>12 U.S. credits per semester (undergraduate)</t>
+          <t>12 US credits</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>18 U.S. credits per semester (undegraduate)- not recommended. We recommend 15 max.</t>
+          <t>18 US credits (권장 15)</t>
         </is>
       </c>
       <c r="J200" s="2" t="inlineStr">
@@ -15511,12 +15594,12 @@
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>12 undergrad, 9 grad</t>
+          <t>12 US credits (학부) / 9 (대학원)</t>
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>17 undergrad, 12 grad</t>
+          <t>17 US credits (학부) / 12 (대학원)</t>
         </is>
       </c>
       <c r="J201" s="2" t="inlineStr">
@@ -15588,12 +15671,12 @@
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>12 credit hours - full time</t>
+          <t>12 US credits</t>
         </is>
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>18 credit hours</t>
+          <t>18 US credits</t>
         </is>
       </c>
       <c r="J202" s="2" t="inlineStr">
@@ -15665,12 +15748,12 @@
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t>12 US credits/24 ECTS credits</t>
+          <t>12 US credits (24 ECTS)</t>
         </is>
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>18 US credits/36 ECTS credits</t>
+          <t>18 US credits (36 ECTS)</t>
         </is>
       </c>
       <c r="J203" s="2" t="inlineStr">
@@ -15738,12 +15821,12 @@
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12 US credits</t>
         </is>
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>22 US credits</t>
         </is>
       </c>
       <c r="J204" s="2" t="inlineStr">
@@ -15888,12 +15971,12 @@
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
-          <t>Undergradaute - 12 credits / Graduate - 9 credits</t>
+          <t>12 US credits (학부) / 9 (대학원)</t>
         </is>
       </c>
       <c r="I206" s="2" t="inlineStr">
         <is>
-          <t>18 credits</t>
+          <t>18 US credits</t>
         </is>
       </c>
       <c r="J206" s="2" t="inlineStr">
@@ -15965,12 +16048,12 @@
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
-          <t>12 US Credits</t>
+          <t>12 US credits</t>
         </is>
       </c>
       <c r="I207" s="2" t="inlineStr">
         <is>
-          <t>18 US Credits</t>
+          <t>18 US credits</t>
         </is>
       </c>
       <c r="J207" s="2" t="inlineStr">
@@ -16042,12 +16125,12 @@
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t>Minimum 12 credits</t>
+          <t>12 US credits</t>
         </is>
       </c>
       <c r="I208" s="2" t="inlineStr">
         <is>
-          <t>Maximum 15 credits</t>
+          <t>15 US credits</t>
         </is>
       </c>
       <c r="J208" s="2" t="inlineStr">
@@ -16119,12 +16202,12 @@
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
-          <t>12 credits</t>
+          <t>12 US credits</t>
         </is>
       </c>
       <c r="I209" s="2" t="inlineStr">
         <is>
-          <t>18 credits</t>
+          <t>18 US credits</t>
         </is>
       </c>
       <c r="J209" s="2" t="inlineStr">
@@ -16192,12 +16275,12 @@
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t>12 credits</t>
+          <t>12 US credits</t>
         </is>
       </c>
       <c r="I210" s="2" t="inlineStr">
         <is>
-          <t>15 credits</t>
+          <t>15 US credits</t>
         </is>
       </c>
       <c r="J210" s="2" t="inlineStr">
@@ -16269,12 +16352,12 @@
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
-          <t>12 credits per semester</t>
+          <t>12 US credits</t>
         </is>
       </c>
       <c r="I211" s="2" t="inlineStr">
         <is>
-          <t>19 undergrad or 16 grad per semester</t>
+          <t>19 US credits (학부) / 16 (대학원)</t>
         </is>
       </c>
       <c r="J211" s="2" t="inlineStr">
@@ -16346,12 +16429,12 @@
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
-          <t>12 U.S. credits</t>
+          <t>12 US credits</t>
         </is>
       </c>
       <c r="I212" s="2" t="inlineStr">
         <is>
-          <t>19 credits for semester only, 30 credits for full year</t>
+          <t>19 US credits (연간 30)</t>
         </is>
       </c>
       <c r="J212" s="2" t="inlineStr">
@@ -16423,12 +16506,12 @@
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
-          <t>12 per semester</t>
+          <t>12 US credits</t>
         </is>
       </c>
       <c r="I213" s="2" t="inlineStr">
         <is>
-          <t>18 per semester</t>
+          <t>18 US credits</t>
         </is>
       </c>
       <c r="J213" s="2" t="inlineStr">
@@ -16569,12 +16652,12 @@
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>24 US credits</t>
         </is>
       </c>
       <c r="I215" s="2" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30 US credits</t>
         </is>
       </c>
       <c r="J215" s="2" t="inlineStr">
@@ -16646,12 +16729,12 @@
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
-          <t>12 per quarter</t>
+          <t>12 US credits/쿼터</t>
         </is>
       </c>
       <c r="I216" s="2" t="inlineStr">
         <is>
-          <t>19 per quarter (without special permission for more)</t>
+          <t>19 US credits/쿼터</t>
         </is>
       </c>
       <c r="J216" s="2" t="inlineStr">
@@ -16723,12 +16806,12 @@
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12 US credits</t>
         </is>
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>17 US credits</t>
         </is>
       </c>
       <c r="J217" s="2" t="inlineStr">
@@ -16800,12 +16883,12 @@
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12 US credits</t>
         </is>
       </c>
       <c r="I218" s="2" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>16 US credits</t>
         </is>
       </c>
       <c r="J218" s="2" t="inlineStr">
@@ -16873,12 +16956,12 @@
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
-          <t>12 US credits (equivalent of 24 ECTS)</t>
+          <t>12 US credits (24 ECTS)</t>
         </is>
       </c>
       <c r="I219" s="2" t="inlineStr">
         <is>
-          <t>15 US credits (equivalent of 30 ECTS)</t>
+          <t>15 US credits (30 ECTS)</t>
         </is>
       </c>
       <c r="J219" s="2" t="inlineStr">
@@ -16950,12 +17033,12 @@
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
-          <t>12 credits for undergraduates</t>
+          <t>12 US credits (학부)</t>
         </is>
       </c>
       <c r="I220" s="2" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18 US credits</t>
         </is>
       </c>
       <c r="J220" s="2" t="inlineStr">
@@ -17023,12 +17106,12 @@
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
-          <t>12 FSU credits (semester based US credit system with 15 week semseter)</t>
+          <t>12 US credits</t>
         </is>
       </c>
       <c r="I221" s="2" t="inlineStr">
         <is>
-          <t>15, must request permission to take higher than 12 credits and have it approved by SKKU advisor</t>
+          <t>15 US credits (12 초과 시 SKKU 승인 필요)</t>
         </is>
       </c>
       <c r="J221" s="2" t="inlineStr">
@@ -17100,12 +17183,12 @@
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
-          <t>at least 12 credits</t>
+          <t>12 credits</t>
         </is>
       </c>
       <c r="I222" s="2" t="inlineStr">
         <is>
-          <t>no more than 22 credits</t>
+          <t>22 credits</t>
         </is>
       </c>
       <c r="J222" s="2" t="inlineStr">

--- a/out/universities.xlsx
+++ b/out/universities.xlsx
@@ -558,7 +558,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1학기</t>
+          <t>1학기 이상</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026~2027학기</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1학기</t>
+          <t>1학기 이상</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1160,7 +1160,11 @@
           <t>4.0/7.0</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>제한 없음</t>
+        </is>
+      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
           <t>확인필요</t>
@@ -1231,7 +1235,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1304,7 +1308,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1377,7 +1381,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3학기</t>
+          <t>3학기 이상</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1454,7 +1458,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>4~2학기</t>
+          <t>4학기 이상 (학부) / 2학기 (대학원)</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1531,7 +1535,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1608,7 +1612,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4학기</t>
+          <t>4학기 이상</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1685,7 +1689,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5학기</t>
+          <t>5학기 이상</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1762,7 +1766,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>최소 4학기</t>
+          <t>4학기 이상</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1839,7 +1843,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3학기</t>
+          <t>3학기 이상</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1916,7 +1920,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1993,7 +1997,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>This is for the home university of the student to deliberate.</t>
+          <t>홈교 기준</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2070,7 +2074,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2147,7 +2151,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>최소 1~2학기</t>
+          <t>1~2학기 이상</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2220,7 +2224,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4학기</t>
+          <t>4학기 이상</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2297,7 +2301,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2374,7 +2378,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>4학기</t>
+          <t>4학기 이상</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2449,7 +2453,11 @@
           <t>담당자 이메일 문의</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>제한 없음</t>
+        </is>
+      </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
           <t>확인필요</t>
@@ -2524,7 +2532,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2601,7 +2609,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>SFU does not have this requirement.</t>
+          <t>제한 없음</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2678,7 +2686,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2754,7 +2762,11 @@
           <t>담당자 이메일 문의</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>제한 없음</t>
+        </is>
+      </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
           <t>확인필요</t>
@@ -2827,7 +2839,11 @@
           <t>담당자 이메일 문의</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>제한 없음</t>
+        </is>
+      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
           <t>확인필요</t>
@@ -2898,7 +2914,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2~1학기</t>
+          <t>2학기 이상 (학부) / 1학기 (대학원)</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2975,7 +2991,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3052,7 +3068,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3125,7 +3141,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>at least one semester to be completed</t>
+          <t>1학기 이상</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3200,7 +3216,11 @@
           <t>담당자 이메일 문의</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>제한 없음</t>
+        </is>
+      </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
           <t>확인필요</t>
@@ -3275,7 +3295,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>We don't have any requirements on this matter.</t>
+          <t>제한 없음</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3352,7 +3372,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3430,7 +3450,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>2~1학기</t>
+          <t>2학기 이상 (학부) / 1학기 (대학원)</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3503,7 +3523,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3576,7 +3596,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3653,7 +3673,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3730,7 +3750,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>30~35학기</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3807,7 +3827,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>4학기</t>
+          <t>4학기 이상</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3884,7 +3904,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3955,7 +3975,11 @@
           <t>담당자 이메일 문의</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>제한 없음</t>
+        </is>
+      </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
           <t>확인필요</t>
@@ -4026,7 +4050,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>4~6학기</t>
+          <t>4학기 이상 (학부) / 6학기 (대학원)</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4103,7 +4127,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4176,7 +4200,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4253,7 +4277,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>No limitation has been set. Preferably two semesters before the exchange.</t>
+          <t>제한 없음 (권장 2학기)</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4330,7 +4354,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>No requirements</t>
+          <t>제한 없음</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4407,7 +4431,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4484,7 +4508,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4561,7 +4585,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Two</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4634,7 +4658,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4711,7 +4735,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>2~1학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4788,7 +4812,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Two</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4865,7 +4889,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>최소 4학기</t>
+          <t>4학기 이상</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4938,7 +4962,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -5015,7 +5039,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -5092,7 +5116,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>3학기</t>
+          <t>3학기 이상</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5169,7 +5193,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>6학기</t>
+          <t>6학기 이상</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5246,7 +5270,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>1학기</t>
+          <t>1학기 이상</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5323,7 +5347,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>1학기</t>
+          <t>1학기 이상</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5400,7 +5424,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>3학기</t>
+          <t>3학기 이상</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5473,7 +5497,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5550,7 +5574,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>3학기</t>
+          <t>3학기 이상</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5625,7 +5649,11 @@
           <t>2.5/4</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>제한 없음</t>
+        </is>
+      </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
           <t>15 ECTS</t>
@@ -5700,7 +5728,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>The home university determines the number of semesters</t>
+          <t>홈교 기준</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5777,7 +5805,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>4학기</t>
+          <t>4학기 이상</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5854,7 +5882,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5931,7 +5959,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>4학기</t>
+          <t>4학기 이상</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -6008,7 +6036,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>4학기</t>
+          <t>4학기 이상</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -6081,7 +6109,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6158,7 +6186,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -6235,7 +6263,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>최소 1~2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6312,7 +6340,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>최소 1~3학기</t>
+          <t>2학기 이상 (학사과정; 석사는 6학기)</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6389,7 +6417,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6462,7 +6490,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>4~6학기</t>
+          <t>4~6학기 이상 (프로그램별)</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -6539,7 +6567,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>We trust our partners to select their students, no requirement</t>
+          <t>제한 없음</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6616,7 +6644,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Depends on which program they apply to - check factsheet)</t>
+          <t>프로그램별 상이</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6693,7 +6721,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6766,7 +6794,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -6836,7 +6864,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6913,7 +6941,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>To join our exchange program, students must have completed at least one academic year (two semesters) in a Business-, Management-, Information Systems-, or Engineering-related field.</t>
+          <t>2학기 이상 (경영·IT·공학 관련 전공)</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -6990,7 +7018,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>1학기</t>
+          <t>1학기 이상</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -7063,7 +7091,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -7138,7 +7166,11 @@
           <t>담당자 이메일 문의</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>제한 없음</t>
+        </is>
+      </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
           <t>명시 없음 (통상 30 ECTS)</t>
@@ -7209,7 +7241,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -7282,7 +7314,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>3학기</t>
+          <t>3학기 이상</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -7359,7 +7391,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>4~5학기</t>
+          <t>4학기 이상</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -7436,7 +7468,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>4~2학기</t>
+          <t>제한 없음 (학부; 대학원 4학기)</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -7509,7 +7541,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -7582,7 +7614,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>최소 3학기</t>
+          <t>3학기 이상</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7659,7 +7691,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>4학기</t>
+          <t>4학기 이상</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -7732,7 +7764,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>최소 2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7809,7 +7841,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Students should have studied for at least two years in a business or economics related programme to enrol in our bachelor programme. To enrol in our master programmes, students need to have finished their undergraduate studies and should have studied at least one semester at graduate level.</t>
+          <t>4학기 이상 (학부, 경영·경제 전공)</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -7886,7 +7918,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>제한 없음</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -7963,7 +7995,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>1학기</t>
+          <t>1학기 이상</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -8036,7 +8068,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>최소 5학기</t>
+          <t>5학기 이상</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -8113,7 +8145,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -8190,7 +8222,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -8267,7 +8299,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -8340,7 +8372,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -8413,7 +8445,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>At least one year of continuous study of the host university.</t>
+          <t>2학기 이상 (1년)</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -8486,7 +8518,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -8563,7 +8595,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -8640,7 +8672,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>최소 2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -8717,7 +8749,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -8794,7 +8826,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>최소 6학기</t>
+          <t>6학기 이상</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -8871,7 +8903,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>최소 1학기</t>
+          <t>1학기 이상</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -8944,7 +8976,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -9021,7 +9053,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -9098,7 +9130,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -9175,7 +9207,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -9252,7 +9284,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>1학기</t>
+          <t>1학기 이상</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -9325,7 +9357,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -9402,7 +9434,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>4학기</t>
+          <t>4학기 이상</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -9475,7 +9507,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -9552,7 +9584,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>at least one year of their degree program at their home institution</t>
+          <t>2학기 이상 (1년)</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -9629,7 +9661,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -9706,7 +9738,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -9781,7 +9813,11 @@
           <t>담당자 이메일 문의</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>제한 없음</t>
+        </is>
+      </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
           <t>7 credits</t>
@@ -9856,7 +9892,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>As long as their are able to provide an academic transcript from their home university, there is no minimum requirement with the semesters.</t>
+          <t>제한 없음 (성적표 제출만)</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -10010,7 +10046,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>https://www.toyo.ac.jp/academics/international-exchange/prospective/exchange_program/</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -10087,7 +10123,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>최소 2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -10164,7 +10200,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>It's depends on the exchange program, so please check our website. https://www.insc.tohoku.ac.jp/english/exchange/ &lt;Reference information&gt; JYPE: Starting from the third year students. IPLA: Starting from the second year students.</t>
+          <t>프로그램별 상이 (JYPE 4학기·IPLA 2학기 이상)</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -10241,7 +10277,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -10314,7 +10350,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -10391,7 +10427,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>2~1학기</t>
+          <t>2학기 이상 (학부) / 1학기 (대학원)</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -10468,7 +10504,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -10545,7 +10581,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -10618,7 +10654,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>60학기</t>
+          <t>명시 없음 (법·경영 과목은 60 ECTS 이수 필요)</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -10691,7 +10727,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>최소 3~4학기</t>
+          <t>3학기 이상 (권장 4학기)</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -10768,7 +10804,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>4학기</t>
+          <t>4학기 이상</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -10845,7 +10881,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>최소 2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -10925,7 +10961,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>최소 1~60학기</t>
+          <t>2학기 이상 (SBE 기준, 60 ECTS)</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -11006,7 +11042,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>4학기</t>
+          <t>4학기 이상</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -11079,7 +11115,7 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>at least one year of your Bachelor’s degree programme.</t>
+          <t>2학기 이상 (1년)</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -11152,7 +11188,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>4학기</t>
+          <t>4학기 이상</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -11225,7 +11261,7 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -11302,7 +11338,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>4학기</t>
+          <t>4학기 이상</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -11375,7 +11411,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>4학기</t>
+          <t>4학기 이상</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -11448,7 +11484,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>최소 60학기</t>
+          <t>2학기 이상 (60 ECTS)</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -11521,7 +11557,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -11594,7 +11630,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -11671,7 +11707,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>5학기</t>
+          <t>5학기 이상</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -11744,7 +11780,7 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -11821,7 +11857,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -11900,7 +11936,7 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -11973,7 +12009,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -12046,7 +12082,7 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -12123,7 +12159,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>4학기</t>
+          <t>4학기 이상</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -12200,7 +12236,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Students should have completed at least one year of studies at the undergraduate level.</t>
+          <t>2학기 이상 (1년)</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -12277,7 +12313,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -12354,7 +12390,7 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>3학기</t>
+          <t>3학기 이상</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -12431,7 +12467,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>1학기</t>
+          <t>1학기 이상</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -12504,7 +12540,7 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>60학기</t>
+          <t>2학기 이상 (1년)</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
@@ -12581,7 +12617,7 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>2~4학기</t>
+          <t>명시 없음 (권장 2~4학기)</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
@@ -12658,7 +12694,7 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
@@ -12735,7 +12771,7 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>There are different entry requirements for different courses, so that depends of what they will apply for.</t>
+          <t>과정별 상이</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
@@ -12812,7 +12848,7 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>최소 60학기</t>
+          <t>2학기 이상 (60 ECTS)</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -12889,7 +12925,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>A minimum of two completed semesters prior to the start of the exchange (at bachelor’s level)</t>
+          <t>2학기 이상 (학사과정)</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -12962,7 +12998,7 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>최소 2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -13039,7 +13075,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -13112,7 +13148,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -13189,7 +13225,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -13266,7 +13302,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>4학기</t>
+          <t>4학기 이상</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -13339,7 +13375,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -13416,7 +13452,7 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>at least one semester</t>
+          <t>1학기 이상</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -13489,7 +13525,7 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -13562,7 +13598,7 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
@@ -13639,7 +13675,7 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
@@ -13716,7 +13752,7 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
@@ -13793,7 +13829,7 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>1학기</t>
+          <t>1학기 이상</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
@@ -13870,7 +13906,7 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>최소 2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
@@ -13947,7 +13983,7 @@
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>4학기</t>
+          <t>4학기 이상</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
@@ -14020,7 +14056,7 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
@@ -14093,7 +14129,7 @@
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
@@ -14166,7 +14202,7 @@
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
@@ -14243,7 +14279,7 @@
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>최소 2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
@@ -14320,7 +14356,7 @@
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>4~2학기</t>
+          <t>4학기 이상 (2년)</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
@@ -14397,7 +14433,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -14470,7 +14506,7 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
@@ -14547,7 +14583,7 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>최소 4~2학기</t>
+          <t>2학기 이상 (1년)</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
@@ -14624,7 +14660,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>We recommend that students have completed at least one semester at their home university before coming to study at YSJ.</t>
+          <t>명시 없음 (권장 1학기)</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -14697,7 +14733,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -14772,7 +14808,11 @@
           <t>담당자 이메일 문의</t>
         </is>
       </c>
-      <c r="G190" s="2" t="inlineStr"/>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>제한 없음</t>
+        </is>
+      </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
           <t>명시 없음 (권장 15 ECTS 이상)</t>
@@ -14843,7 +14883,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -14920,7 +14960,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>최소 2~4학기</t>
+          <t>과목 수준별 상이</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -14995,7 +15035,11 @@
           <t>담당자 이메일 문의</t>
         </is>
       </c>
-      <c r="G193" s="2" t="inlineStr"/>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>제한 없음</t>
+        </is>
+      </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
           <t>60 BCU credits (30 ECTS)</t>
@@ -15070,7 +15114,7 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
@@ -15145,7 +15189,11 @@
           <t>확인필요</t>
         </is>
       </c>
-      <c r="G195" s="2" t="inlineStr"/>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>제한 없음</t>
+        </is>
+      </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
           <t>확인필요</t>
@@ -15208,7 +15256,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>최소 1학기</t>
+          <t>1학기 이상</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -15285,7 +15333,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>3~4학기</t>
+          <t>3~4학기 이상</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -15362,7 +15410,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -15439,7 +15487,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -15512,7 +15560,7 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
@@ -15589,7 +15637,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -15666,7 +15714,7 @@
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>1~2학기</t>
+          <t>1~2학기 이상</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
@@ -15743,7 +15791,7 @@
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
@@ -15816,7 +15864,7 @@
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
@@ -15966,7 +16014,7 @@
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>We do not have a minimum class standing, and defer to the home university for these requirements</t>
+          <t>홈교 기준</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
@@ -16043,7 +16091,7 @@
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
@@ -16120,7 +16168,7 @@
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>2~3학기</t>
+          <t>명시 없음 (권장 2~3학기)</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
@@ -16197,7 +16245,7 @@
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>4학기</t>
+          <t>4학기 이상</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr">
@@ -16270,7 +16318,7 @@
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
@@ -16347,7 +16395,7 @@
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr">
@@ -16424,7 +16472,7 @@
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>4학기</t>
+          <t>4학기 이상</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr">
@@ -16501,7 +16549,7 @@
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
@@ -16574,7 +16622,7 @@
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>최소 4학기</t>
+          <t>4학기 이상</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr">
@@ -16647,7 +16695,7 @@
       </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="H215" s="2" t="inlineStr">
@@ -16724,7 +16772,7 @@
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
@@ -16801,7 +16849,7 @@
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr">
@@ -16878,7 +16926,7 @@
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>1학기</t>
+          <t>1학기 이상</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
@@ -16951,7 +16999,7 @@
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr">
@@ -17028,7 +17076,7 @@
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>1학기</t>
+          <t>1학기 이상</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
@@ -17101,7 +17149,7 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>최소 1학기</t>
+          <t>1학기 이상</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
@@ -17178,7 +17226,7 @@
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>2학기</t>
+          <t>2학기 이상</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr">

--- a/out/universities.xlsx
+++ b/out/universities.xlsx
@@ -733,7 +733,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>IELTS 6.0+, TOEFL iBT 64+, PTE Academic 50+</t>
+          <t>IELTS 6.0점 이상 또는 TOEFL iBT 64점 이상 또는 PTE Academic 50점 이상</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>IELTS 6.5+, TOEFL iBT 79+</t>
+          <t>IELTS 6.5점 이상 또는 TOEFL iBT 79점 이상</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>TOEFL 90+, IELTS 6.5+</t>
+          <t>TOEFL 90점 이상 또는 IELTS 6.5점 이상</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>IELTS 6.5+, TOEFL iBT 79+, PTE 58+</t>
+          <t>IELTS 6.5점 이상 또는 TOEFL iBT 79점 이상 또는 PTE 58점 이상</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 79+, IELTS 6.0+, PTE Academic 54+</t>
+          <t>TOEFL iBT 79점 이상 또는 IELTS 6.0점 이상 또는 PTE Academic 54점 이상</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>IELTS 6.5+, TOEFL iBT 80+, PTE Academic 64+, Cambridge C1 Advanced</t>
+          <t>IELTS 6.5점 이상 또는 TOEFL iBT 80점 이상 또는 PTE Academic 64점 이상 또는 Cambridge C1 Advanced</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>CEFR B2 or equivalent in the language of instruction. For German Studies: German CEFR C1</t>
+          <t>수업언어 CEFR B2 이상 (독문학은 독일어 C1)</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>English B2 according to CEFR</t>
+          <t>영어 CEFR B2 이상</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>SKKU Letter of proficiency</t>
+          <t>SKKU 어학확인서 인정</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Letter of proficiency (min. B1)</t>
+          <t>SKKU 어학확인서 인정 (B1 이상)</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>IELTS 6.0+</t>
+          <t>IELTS 6.0점 이상</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>공식 영어 능력 증명 (B2 이상 학사, C1 이상 석사)</t>
+          <t>영어 CEFR B2 이상 (석사 C1)</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>There's no language certificate requirement.</t>
+          <t>공인성적 불요</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>Duolingo 105+, TOEFL iBT 79+, IELTS 6.0+</t>
+          <t>Duolingo 105점 이상 또는 TOEFL iBT 79점 이상 또는 IELTS 6.0점 이상</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>IELTS 6.5+, TOEFL iBT 80+, Duolingo 120+</t>
+          <t>IELTS 6.5점 이상 또는 TOEFL iBT 80점 이상 또는 Duolingo 120점 이상</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>IELTS 6.5+, TOEFL iBT 80+, CAEL 60+</t>
+          <t>IELTS 6.5점 이상 또는 TOEFL iBT 80점 이상 또는 CAEL 60점 이상</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 80+, IELTS 6.5+</t>
+          <t>TOEFL iBT 80점 이상 또는 IELTS 6.5점 이상</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>B2 French, B2 English (English Studies)</t>
+          <t>프랑스어 CEFR B2 이상 (영문학 전공은 영어 B2)</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>New HSK-5+ (Chinese), TOEFL iBT 80+, IELTS 6.0+</t>
+          <t>TOEFL iBT 80점 이상 또는 IELTS 6.0점 이상 또는 HSK 5급 이상</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT ≥80, IELTS ≥6.0, HSK 4 ≥180 (Science/Engineering/Medicine), HSK 5 ≥180 (Economics/Management/Literature/Education/Philosophy/Arts/Law)</t>
+          <t>TOEFL iBT 80점 이상 또는 IELTS 6.0점 이상 또는 HSK 4급 180점 이상 (이공·의학) / HSK 5급 180점 (인문·사회)</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>New HSK 180+, TOEFL iBT 80+, IELTS 6.0+</t>
+          <t>TOEFL iBT 80점 이상 또는 IELTS 6.0점 이상 또는 HSK 180점 이상</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>IELTS 6+</t>
+          <t>IELTS 6점 이상</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>TOEIC 700+, TOEFL iBT 79+, IELTS 6.0+</t>
+          <t>TOEIC 700점 이상 또는 TOEFL iBT 79점 이상 또는 IELTS 6.0점 이상</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>B2 level</t>
+          <t>영어 CEFR B2 이상</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>IELTS 5.5+, TOEFL IBT 72+, TOEFL ITP 543+</t>
+          <t>IELTS 5.5점 이상 또는 TOEFL IBT 72점 이상 또는 TOEFL ITP 543점 이상</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 88+, IELTS 6.5+</t>
+          <t>TOEFL iBT 88점 이상 또는 IELTS 6.5점 이상</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 100+, IELTS 6.5+, CEFR B2+</t>
+          <t>TOEFL iBT 100점 이상 또는 IELTS 6.5점 이상 또는 CEFR B2 이상</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Letter of proficiency issued by the Office of International Relations SKKU</t>
+          <t>SKKU 어학확인서 인정</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>CEFR B2+</t>
+          <t>영어 CEFR B2 이상</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Cambridge B2 First 180+, C1 Advanced/C2 Proficiency A/B/C, IELTS 6.5+, TOEFL iBT 90+, PTE Academic 62+</t>
+          <t>IELTS 6.5점 이상 또는 TOEFL iBT 90점 이상 또는 PTE Academic 62점 이상 또는 Cambridge B2 First 180점 이상</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -4379,7 +4379,7 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>We expect students to have a minimum of B2 English level. No official language test required.</t>
+          <t>공인성적 불요 (영어 B2 기대)</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>IELTS 6+, TOEFL iBT 87+</t>
+          <t>IELTS 6점 이상 또는 TOEFL iBT 87점 이상</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -4533,7 +4533,7 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>N/A: CEFR B2 level English recommended</t>
+          <t>명시 없음 (영어 B2 권장)</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 92+, IELTS 6.5+, Duolingo 115+</t>
+          <t>TOEFL iBT 92점 이상 또는 IELTS 6.5점 이상 또는 Duolingo 115점 이상</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 78+, IELTS 6.0+</t>
+          <t>TOEFL iBT 78점 이상 또는 IELTS 6.0점 이상</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>SKKU Letter of Proficiency</t>
+          <t>SKKU 어학확인서 인정</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>CEFR B2+</t>
+          <t>영어 CEFR B2 이상</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>N/A Home university is expected to check that the student meets the CEFR B2 level</t>
+          <t>공인성적 불요 (홈교가 B2 확인)</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>IELTS 6.0+</t>
+          <t>IELTS 6.0점 이상</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>B2 - Letter of proficiency issued by the Office of International Relations SKKU</t>
+          <t>SKKU 어학확인서 인정 (B2 이상)</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 79+, IELTS 6.5+, TOEIC 785+</t>
+          <t>TOEFL iBT 79점 이상 또는 IELTS 6.5점 이상 또는 TOEIC 785점 이상</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 80+, IELTS 6.5+, TOEIC 750+, Duolingo 110+</t>
+          <t>TOEFL iBT 80점 이상 또는 IELTS 6.5점 이상 또는 TOEIC 750점 이상 또는 Duolingo 110점 이상</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>B2 CEFR equivalent (Official test or home university certificate)</t>
+          <t>영어 CEFR B2 이상 (홈교 확인서 가능)</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>CEFR B2+</t>
+          <t>영어 CEFR B2 이상</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 80+, TOEIC 850, IELTS 6.5+, Duolingo 115</t>
+          <t>TOEFL iBT 80점 이상 또는 TOEIC 850점 이상 또는 IELTS 6.5점 이상 또는 Duolingo 115점 이상</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>French B1/B2 or English B1/B2</t>
+          <t>프랑스어 또는 영어 CEFR B1~B2</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 92+, IELTS 6.5+</t>
+          <t>TOEFL iBT 92점 이상 또는 IELTS 6.5점 이상</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 79+, IELTS 6.0+, TOEIC 785+</t>
+          <t>TOEFL iBT 79점 이상 또는 IELTS 6.0점 이상 또는 TOEIC 785점 이상</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 72+, TOEFL ITP 543+, TOEIC 785+, IELTS 5.5+</t>
+          <t>TOEFL iBT 72점 이상 또는 TOEFL ITP 543점 이상 또는 TOEIC 785점 이상 또는 IELTS 5.5점 이상</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
@@ -6288,7 +6288,7 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 79+, IELTS 6.0+, Duolingo 110+, PTE Academic 50+</t>
+          <t>TOEFL iBT 79점 이상 또는 IELTS 6.0점 이상 또는 Duolingo 110점 이상 또는 PTE Academic 50점 이상</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>DELF/DALF B1+ (Language and Civilisation), DELF/DALF C1+ (Professional Track), JLPT N3 (Japanese 2nd year), JLPT N2 (Japanese 3rd year)</t>
+          <t>DELF/DALF B1 이상 (언어·문명과정) / C1 (전문과정), JLPT N2~N3 (일본어 전공)</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -6515,7 +6515,7 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>B2 English, B1 French (if courses in French)</t>
+          <t>영어 CEFR B2 이상 (프랑스어 수업 수강 시 프랑스어 B1)</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -6592,7 +6592,7 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>IELTS 6.0+, French B2+</t>
+          <t>IELTS 6.0점 이상, 프랑스어 CEFR B2 이상</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
@@ -6819,8 +6819,7 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>English or German (level B2)- we will not ask 
- students to submit certificates.</t>
+          <t>영어 또는 독일어 CEFR B2 (증빙 불요)</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
@@ -6966,7 +6965,7 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 83+, IELTS 6.5+, B2 level</t>
+          <t>TOEFL iBT 83점 이상 또는 IELTS 6.5점 이상 (CEFR B2 상당)</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -7043,7 +7042,7 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>German B1/B2 (Human Medicine, Dentistry, Medical Biotechnology: B2), English B1 (CEFR)</t>
+          <t>독일어 CEFR B1 이상·영어 B1 이상 (의학계열은 독일어 B2)</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
@@ -7116,7 +7115,7 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>B2 level in English is strongly recommended but no language certificate needs to b provided</t>
+          <t>공인성적 불요 (영어 B2 강력 권장)</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
@@ -7266,7 +7265,7 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>B1 level German</t>
+          <t>독일어 CEFR B1 이상</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
@@ -7339,7 +7338,7 @@
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>English B2</t>
+          <t>영어 CEFR B2 이상</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
@@ -7416,7 +7415,7 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>German B1+, English B1+; Medicine/German Philology: German B2+; Biology: German C1+; Pharmacy: German B2+; Master Medical Life Sciences: English C1+</t>
+          <t>독일어·영어 CEFR B1 이상 (일부 학과 B2~C1)</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
@@ -7493,7 +7492,7 @@
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>Undergraduate: English B1 and/or German B2; Graduate: English B2 and/or German B2</t>
+          <t>학부: 영어 B1·독일어 B2 이상 / 대학원: 영어 B2·독일어 B2 이상</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
@@ -7716,7 +7715,7 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>B1 English or German</t>
+          <t>영어 또는 독일어 CEFR B1 이상</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
@@ -7789,7 +7788,7 @@
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>B2 level (certificate or university letter)</t>
+          <t>영어 CEFR B2 이상 (홈교 확인서 가능)</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
@@ -7866,7 +7865,7 @@
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>TOEFL IBT 90+, IELTS 7.0+, PTE Academic</t>
+          <t>TOEFL iBT 90점 이상 또는 IELTS 7.0점 이상 또는 PTE Academic</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
@@ -7943,7 +7942,7 @@
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>English Level B2 according to CEFR</t>
+          <t>영어 CEFR B2 이상</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
@@ -8020,7 +8019,7 @@
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>English B2/C1, German B2</t>
+          <t>영어 CEFR B2~C1·독일어 B2 이상</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
@@ -8093,7 +8092,7 @@
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>CEFR B1.1 in English or German</t>
+          <t>영어 또는 독일어 CEFR B1 이상</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
@@ -8170,7 +8169,7 @@
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>CEFR B1 or B2 in English or CEFR B1 in German</t>
+          <t>영어 CEFR B1~B2 또는 독일어 B1</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
@@ -8247,7 +8246,7 @@
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 80+, TOEFL PBT 550+, IELTS 6.0+</t>
+          <t>TOEFL iBT 80점 이상 또는 TOEFL PBT 550점 이상 또는 IELTS 6.0점 이상</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
@@ -8324,7 +8323,7 @@
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 97+, IELTS 7.0+ (법대), TOEFL iBT 80+, IELTS 6.5+ (기타)</t>
+          <t>TOEFL iBT 97점 이상 또는 IELTS 7.0점 이상 (법대) 또는 TOEFL iBT 80점 이상 또는 IELTS 6.5점 이상 (기타)</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
@@ -8397,7 +8396,7 @@
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 79+, IELTS 6.5+</t>
+          <t>TOEFL iBT 79점 이상 또는 IELTS 6.5점 이상</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
@@ -8470,7 +8469,7 @@
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>IELTS 6.0+, TOEFL iBT 80+</t>
+          <t>IELTS 6.0점 이상 또는 TOEFL iBT 80점 이상</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
@@ -8543,7 +8542,7 @@
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>B2 level</t>
+          <t>영어 CEFR B2 이상</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
@@ -8620,7 +8619,7 @@
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>TOEFL 500+, IELTS 5.0+, TOEFL iBT 70+, TOEIC 500+</t>
+          <t>TOEFL 500점 이상 또는 IELTS 5.0점 이상 또는 TOEFL iBT 70점 이상 또는 TOEIC 500점 이상</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
@@ -8697,7 +8696,7 @@
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 80+, TOEFL ITP/PBT 550+, IELTS 6.0+</t>
+          <t>TOEFL iBT 80점 이상 또는 TOEFL ITP/PBT 550점 이상 또는 IELTS 6.0점 이상</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
@@ -8774,7 +8773,7 @@
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>B1 level in Italian Language+, B1 level in English Language+</t>
+          <t>이탈리아어 또는 영어 CEFR B1 이상</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
@@ -8851,7 +8850,7 @@
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
@@ -8928,7 +8927,7 @@
       </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 72+, IELTS 5.5+, PTE Academic 59+</t>
+          <t>TOEFL iBT 72점 이상 또는 IELTS 5.5점 이상 또는 PTE Academic 59점 이상</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
@@ -9001,7 +9000,7 @@
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
@@ -9078,7 +9077,7 @@
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>TOEFL 500PBT+, TOEFL 61iBT+, IELTS 5.5+</t>
+          <t>TOEFL PBT 500점 이상 또는 TOEFL iBT 61점 이상 또는 IELTS 5.5점 이상</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
@@ -9155,7 +9154,7 @@
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
@@ -9232,7 +9231,7 @@
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>JLPT N2+</t>
+          <t>JLPT N2 이상</t>
         </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
@@ -9309,7 +9308,7 @@
       </c>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 68+, IELTS 5.5+, JLPT N5+</t>
+          <t>TOEFL iBT 68점 이상 또는 IELTS 5.5점 이상 또는 JLPT N5 이상</t>
         </is>
       </c>
       <c r="M117" s="2" t="inlineStr">
@@ -9382,7 +9381,7 @@
       </c>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>JLPT N2+ (Undergraduate Course), JLPT N4/N3 (Japanese Language and Culture Course)</t>
+          <t>JLPT N2 이상 (학부 과정) / N4~N3 (일본어·문화 과정)</t>
         </is>
       </c>
       <c r="M118" s="2" t="inlineStr">
@@ -9459,7 +9458,7 @@
       </c>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 79+, IELTS 6.0+, CEFR B2+, JLPT N2+</t>
+          <t>TOEFL iBT 79점 이상 또는 IELTS 6.0점 이상 또는 CEFR B2 이상 또는 JLPT N2 이상</t>
         </is>
       </c>
       <c r="M119" s="2" t="inlineStr">
@@ -9532,7 +9531,7 @@
       </c>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>TOEFL-iBT 71+, IELTS 5.5+, CEFR B2+</t>
+          <t>TOEFL-iBT 71점 이상 또는 IELTS 5.5점 이상 또는 CEFR B2 이상</t>
         </is>
       </c>
       <c r="M120" s="2" t="inlineStr">
@@ -9609,7 +9608,7 @@
       </c>
       <c r="L121" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 68+, TOEFL PBT 520+, IELTS 6.0+, CEFR B2</t>
+          <t>TOEFL iBT 68점 이상 또는 TOEFL PBT 520점 이상 또는 IELTS 6.0점 이상 또는 CEFR B2 이상</t>
         </is>
       </c>
       <c r="M121" s="2" t="inlineStr">
@@ -9686,7 +9685,7 @@
       </c>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>JLPT N5+, CEFR A1+</t>
+          <t>JLPT N5 이상 또는 CEFR A1 이상</t>
         </is>
       </c>
       <c r="M122" s="2" t="inlineStr">
@@ -9763,7 +9762,7 @@
       </c>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>JLPT N2+ (학과별 상이)</t>
+          <t>JLPT N2 이상 (학과별 상이)</t>
         </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
@@ -9917,7 +9916,7 @@
       </c>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 79+, IELTS 6.0+, TOEIC 780+, JLPT N1</t>
+          <t>TOEFL iBT 79점 이상 또는 IELTS 6.0점 이상 또는 TOEIC 780점 이상 또는 JLPT N1 이상</t>
         </is>
       </c>
       <c r="M125" s="2" t="inlineStr">
@@ -10148,7 +10147,7 @@
       </c>
       <c r="L128" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 79+, IELTS 6.5+</t>
+          <t>TOEFL iBT 79점 이상 또는 IELTS 6.5점 이상</t>
         </is>
       </c>
       <c r="M128" s="2" t="inlineStr">
@@ -10225,7 +10224,7 @@
       </c>
       <c r="L129" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 79+, IELTS 6.0+ (DEEP: JLPT N1)</t>
+          <t>TOEFL iBT 79점 이상 또는 IELTS 6.0점 이상 (DEEP: JLPT N1)</t>
         </is>
       </c>
       <c r="M129" s="2" t="inlineStr">
@@ -10302,7 +10301,7 @@
       </c>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>TOEFL-iBT 79+, IELTS 6.0+</t>
+          <t>TOEFL-iBT 79점 이상 또는 IELTS 6.0점 이상</t>
         </is>
       </c>
       <c r="M130" s="2" t="inlineStr">
@@ -10375,7 +10374,7 @@
       </c>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>We accept Letter of proficiency issued by the Office of International Relations SKKU</t>
+          <t>SKKU 어학확인서 인정</t>
         </is>
       </c>
       <c r="M131" s="2" t="inlineStr">
@@ -10452,7 +10451,7 @@
       </c>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 72+, IELTS 5.5+, TOEIC 785+, Duolingo 100+</t>
+          <t>TOEFL iBT 72점 이상 또는 IELTS 5.5점 이상 또는 TOEIC 785점 이상 또는 Duolingo 100점 이상</t>
         </is>
       </c>
       <c r="M132" s="2" t="inlineStr">
@@ -10529,7 +10528,7 @@
       </c>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>English B1+</t>
+          <t>영어 CEFR B1 이상</t>
         </is>
       </c>
       <c r="M133" s="2" t="inlineStr">
@@ -10606,7 +10605,7 @@
       </c>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="M134" s="2" t="inlineStr">
@@ -10679,7 +10678,7 @@
       </c>
       <c r="L135" s="2" t="inlineStr">
         <is>
-          <t>IELTS Academic 6.0+, TOEFL iBT 80+, PTE Academic 61+, Cambridge B2 First 173+</t>
+          <t>IELTS Academic 6.0점 이상 또는 TOEFL iBT 80점 이상 또는 PTE Academic 61점 이상 또는 Cambridge B2 First 173점 이상</t>
         </is>
       </c>
       <c r="M135" s="2" t="inlineStr">
@@ -10752,7 +10751,7 @@
       </c>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>Bachelor: IELTS 6.0+, TOEFL iBT 80+; Master: IELTS 6.5+, TOEFL iBT 95+</t>
+          <t>학부: IELTS 6.0점 또는 TOEFL iBT 80점 이상 / 석사: IELTS 6.5점 또는 TOEFL iBT 95점 이상</t>
         </is>
       </c>
       <c r="M136" s="2" t="inlineStr">
@@ -10829,7 +10828,7 @@
       </c>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>English B2</t>
+          <t>영어 CEFR B2 이상</t>
         </is>
       </c>
       <c r="M137" s="2" t="inlineStr">
@@ -10906,7 +10905,7 @@
       </c>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>Differs per programme</t>
+          <t>프로그램별 상이</t>
         </is>
       </c>
       <c r="M138" s="2" t="inlineStr">
@@ -11067,7 +11066,7 @@
       </c>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>B2 level</t>
+          <t>영어 CEFR B2 이상</t>
         </is>
       </c>
       <c r="M140" s="2" t="inlineStr">
@@ -11140,7 +11139,7 @@
       </c>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 90+, IELTS 6.5+</t>
+          <t>TOEFL iBT 90점 이상 또는 IELTS 6.5점 이상</t>
         </is>
       </c>
       <c r="M141" s="2" t="inlineStr">
@@ -11213,7 +11212,7 @@
       </c>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>CEFR B2</t>
+          <t>영어 CEFR B2 이상</t>
         </is>
       </c>
       <c r="M142" s="2" t="inlineStr">
@@ -11286,7 +11285,7 @@
       </c>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="M143" s="2" t="inlineStr">
@@ -11363,7 +11362,7 @@
       </c>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 90+, IELTS 6.5+, Cambridge English C1 Advanced 180+ or C2 Proficiency</t>
+          <t>TOEFL iBT 90점 이상 또는 IELTS 6.5점 이상 또는 Cambridge C1 Advanced 180점 이상</t>
         </is>
       </c>
       <c r="M144" s="2" t="inlineStr">
@@ -11436,7 +11435,7 @@
       </c>
       <c r="L145" s="2" t="inlineStr">
         <is>
-          <t>IELTS 5.0+, TOEFL iBT 60+ (Bachelor), IELTS 6.5+, TOEFL iBT 90+ (Master)</t>
+          <t>학부: IELTS 5.0점 또는 TOEFL iBT 60점 이상 / 석사: IELTS 6.5점 또는 TOEFL iBT 90점 이상</t>
         </is>
       </c>
       <c r="M145" s="2" t="inlineStr">
@@ -11509,7 +11508,7 @@
       </c>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>B2 (General courses), C1 (English language and literature)</t>
+          <t>영어 CEFR B2 이상 (영문학 전공 C1)</t>
         </is>
       </c>
       <c r="M146" s="2" t="inlineStr">
@@ -11582,7 +11581,7 @@
       </c>
       <c r="L147" s="2" t="inlineStr">
         <is>
-          <t>Spanish B2</t>
+          <t>스페인어 CEFR B2 이상</t>
         </is>
       </c>
       <c r="M147" s="2" t="inlineStr">
@@ -11655,7 +11654,7 @@
       </c>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 79+, IELTS 6.0+, TOEIC 750+</t>
+          <t>TOEFL iBT 79점 이상 또는 IELTS 6.0점 이상 또는 TOEIC 750점 이상</t>
         </is>
       </c>
       <c r="M148" s="2" t="inlineStr">
@@ -11732,7 +11731,7 @@
       </c>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>IELTS 5.5+, TOEFL iBT 55+, Duolingo 95+, EFSET 55+</t>
+          <t>IELTS 5.5점 이상 또는 TOEFL iBT 55점 이상 또는 Duolingo 95점 이상 또는 EFSET 55점 이상</t>
         </is>
       </c>
       <c r="M149" s="2" t="inlineStr">
@@ -11805,7 +11804,7 @@
       </c>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>N/A (As long as student is capable of taking courses/research fully delivered in English)</t>
+          <t>공인성적 불요 (영어 수강 가능 수준)</t>
         </is>
       </c>
       <c r="M150" s="2" t="inlineStr">
@@ -11961,7 +11960,7 @@
       </c>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>TOEFL PBT 583+, TOEFL iBT 93+, IELTS 7.0+, C1 Advanced 185+</t>
+          <t>TOEFL PBT 583점 이상 또는 TOEFL iBT 93점 이상 또는 IELTS 7.0점 이상 또는 C1 Advanced 185점 이상</t>
         </is>
       </c>
       <c r="M152" s="2" t="inlineStr">
@@ -12034,7 +12033,7 @@
       </c>
       <c r="L153" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="M153" s="2" t="inlineStr">
@@ -12107,7 +12106,7 @@
       </c>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 80+</t>
+          <t>TOEFL iBT 80점 이상</t>
         </is>
       </c>
       <c r="M154" s="2" t="inlineStr">
@@ -12184,7 +12183,7 @@
       </c>
       <c r="L155" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="M155" s="2" t="inlineStr">
@@ -12261,7 +12260,7 @@
       </c>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>N/A. We trust our partners to nominate students with sufficient English level to follow the classes.</t>
+          <t>공인성적 불요</t>
         </is>
       </c>
       <c r="M156" s="2" t="inlineStr">
@@ -12338,7 +12337,7 @@
       </c>
       <c r="L157" s="2" t="inlineStr">
         <is>
-          <t>No requirements but we recommend having a B2 in english</t>
+          <t>공인성적 불요 (영어 B2 권장)</t>
         </is>
       </c>
       <c r="M157" s="2" t="inlineStr">
@@ -12415,7 +12414,7 @@
       </c>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>Spanish or English B2 level</t>
+          <t>스페인어 또는 영어 CEFR B2 이상</t>
         </is>
       </c>
       <c r="M158" s="2" t="inlineStr">
@@ -12492,7 +12491,7 @@
       </c>
       <c r="L159" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 100+, IELTS 7.0+, Duolingo 130+</t>
+          <t>TOEFL iBT 100점 이상 또는 IELTS 7.0점 이상 또는 Duolingo 130점 이상</t>
         </is>
       </c>
       <c r="M159" s="2" t="inlineStr">
@@ -12565,7 +12564,7 @@
       </c>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>Min B2</t>
+          <t>영어 CEFR B2 이상</t>
         </is>
       </c>
       <c r="M160" s="2" t="inlineStr">
@@ -12642,7 +12641,7 @@
       </c>
       <c r="L161" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 60+, IELTS 6.0+</t>
+          <t>TOEFL iBT 60점 이상 또는 IELTS 6.0점 이상</t>
         </is>
       </c>
       <c r="M161" s="2" t="inlineStr">
@@ -12719,7 +12718,7 @@
       </c>
       <c r="L162" s="2" t="inlineStr">
         <is>
-          <t>Students are expected to manage at least a B2 level on the Common European Framework of Reference for Languages. A langu</t>
+          <t>영어 CEFR B2 이상</t>
         </is>
       </c>
       <c r="M162" s="2" t="inlineStr">
@@ -12796,7 +12795,7 @@
       </c>
       <c r="L163" s="2" t="inlineStr">
         <is>
-          <t>B2 (CEFR) in English.</t>
+          <t>영어 CEFR B2 이상</t>
         </is>
       </c>
       <c r="M163" s="2" t="inlineStr">
@@ -12873,7 +12872,7 @@
       </c>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 72+, IELTS 6.0+, TOEIC 785+</t>
+          <t>TOEFL iBT 72점 이상 또는 IELTS 6.0점 이상 또는 TOEIC 785점 이상</t>
         </is>
       </c>
       <c r="M164" s="2" t="inlineStr">
@@ -12950,7 +12949,7 @@
       </c>
       <c r="L165" s="2" t="inlineStr">
         <is>
-          <t>The expected language proficiency level is B2+ (Common European Framework of Reference for Languages). Official confirma</t>
+          <t>영어 CEFR B2 이상</t>
         </is>
       </c>
       <c r="M165" s="2" t="inlineStr">
@@ -13023,7 +13022,7 @@
       </c>
       <c r="L166" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 80+, IELTS 6.0+</t>
+          <t>TOEFL iBT 80점 이상 또는 IELTS 6.0점 이상</t>
         </is>
       </c>
       <c r="M166" s="2" t="inlineStr">
@@ -13100,7 +13099,7 @@
       </c>
       <c r="L167" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 61+, TOEFL ITP 500+, TOEFL CBT 173+, TOEIC 550+, IELTS 4.0+, HSK Level 5+, TOCFL Level 3+</t>
+          <t>TOEFL iBT 61점 이상 또는 TOEFL ITP 500점 이상 또는 TOEFL CBT 173점 이상 또는 TOEIC 550점 이상 또는 IELTS 4.0점 이상 또는 HSK Level 5점 이상 또는 TOCFL Level 3점 이상</t>
         </is>
       </c>
       <c r="M167" s="2" t="inlineStr">
@@ -13173,7 +13172,7 @@
       </c>
       <c r="L168" s="2" t="inlineStr">
         <is>
-          <t>N/A, but at least a B2 English level is strongly recommended</t>
+          <t>명시 없음 (영어 B2 강력 권장)</t>
         </is>
       </c>
       <c r="M168" s="2" t="inlineStr">
@@ -13250,7 +13249,7 @@
       </c>
       <c r="L169" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 79+, IELTS 6.0+</t>
+          <t>TOEFL iBT 79점 이상 또는 IELTS 6.0점 이상</t>
         </is>
       </c>
       <c r="M169" s="2" t="inlineStr">
@@ -13327,7 +13326,7 @@
       </c>
       <c r="L170" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 79+, IELTS 6+, TOEIC 750+, CEFR B1</t>
+          <t>TOEFL iBT 79점 이상 또는 IELTS 6점 이상 또는 TOEIC 750점 이상 또는 CEFR B1 이상</t>
         </is>
       </c>
       <c r="M170" s="2" t="inlineStr">
@@ -13400,7 +13399,7 @@
       </c>
       <c r="L171" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="M171" s="2" t="inlineStr">
@@ -13477,7 +13476,7 @@
       </c>
       <c r="L172" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 72+, IELTS 5.5+, TOCFL Band B Level 3+, HSK Level 5+</t>
+          <t>TOEFL iBT 72점 이상 또는 IELTS 5.5점 이상 또는 TOCFL Band B Level 3점 이상 또는 HSK Level 5점 이상</t>
         </is>
       </c>
       <c r="M172" s="2" t="inlineStr">
@@ -13550,7 +13549,7 @@
       </c>
       <c r="L173" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="M173" s="2" t="inlineStr">
@@ -13623,7 +13622,7 @@
       </c>
       <c r="L174" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 79+, IELTS 6.0+</t>
+          <t>TOEFL iBT 79점 이상 또는 IELTS 6.0점 이상</t>
         </is>
       </c>
       <c r="M174" s="2" t="inlineStr">
@@ -13700,7 +13699,7 @@
       </c>
       <c r="L175" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="M175" s="2" t="inlineStr">
@@ -13777,7 +13776,7 @@
       </c>
       <c r="L176" s="2" t="inlineStr">
         <is>
-          <t>B1 level in the language of instruction</t>
+          <t>수업언어 CEFR B1 이상</t>
         </is>
       </c>
       <c r="M176" s="2" t="inlineStr">
@@ -13854,7 +13853,7 @@
       </c>
       <c r="L177" s="2" t="inlineStr">
         <is>
-          <t>Turkish or English (Minimum B2)</t>
+          <t>터키어 또는 영어 CEFR B2 이상</t>
         </is>
       </c>
       <c r="M177" s="2" t="inlineStr">
@@ -14081,7 +14080,7 @@
       </c>
       <c r="L180" s="2" t="inlineStr">
         <is>
-          <t>IELTS Academic/for UKVI/Online 6.0+, TOEFL iBT 95+</t>
+          <t>IELTS 6.0점 이상 (Academic/UKVI/Online) 또는 TOEFL iBT 95점 이상</t>
         </is>
       </c>
       <c r="M180" s="2" t="inlineStr">
@@ -14227,7 +14226,7 @@
       </c>
       <c r="L182" s="2" t="inlineStr">
         <is>
-          <t>IELTS 6.5+, TOEFL iBT 88+</t>
+          <t>IELTS 6.5점 이상 또는 TOEFL iBT 88점 이상</t>
         </is>
       </c>
       <c r="M182" s="2" t="inlineStr">
@@ -14304,7 +14303,7 @@
       </c>
       <c r="L183" s="2" t="inlineStr">
         <is>
-          <t>IELTS 6.5+, TOEFL iBT 88+, CPE C+, TEEP 6.5+</t>
+          <t>IELTS 6.5점 이상 또는 TOEFL iBT 88점 이상 또는 CPE C 이상 또는 TEEP 6.5점 이상</t>
         </is>
       </c>
       <c r="M183" s="2" t="inlineStr">
@@ -14381,7 +14380,7 @@
       </c>
       <c r="L184" s="2" t="inlineStr">
         <is>
-          <t>IELTS 6.5+, TOEFL iBT 90+</t>
+          <t>IELTS 6.5점 이상 또는 TOEFL iBT 90점 이상</t>
         </is>
       </c>
       <c r="M184" s="2" t="inlineStr">
@@ -14531,7 +14530,7 @@
       </c>
       <c r="L186" s="2" t="inlineStr">
         <is>
-          <t>IELTS 6.0+, TOEFL iBT 80+, Duolingo 110+, PTE Academic 62+</t>
+          <t>IELTS 6.0점 이상 또는 TOEFL iBT 80점 이상 또는 Duolingo 110점 이상 또는 PTE Academic 62점 이상</t>
         </is>
       </c>
       <c r="M186" s="2" t="inlineStr">
@@ -14608,7 +14607,7 @@
       </c>
       <c r="L187" s="2" t="inlineStr">
         <is>
-          <t>IELTS Academic 6.5+, TOEFL iBT 88+</t>
+          <t>IELTS Academic 6.5점 이상 또는 TOEFL iBT 88점 이상</t>
         </is>
       </c>
       <c r="M187" s="2" t="inlineStr">
@@ -14685,7 +14684,7 @@
       </c>
       <c r="L188" s="2" t="inlineStr">
         <is>
-          <t>IELTS 6.0+, Duolingo 105+, PTE 59+, TOEFL iBT 75+</t>
+          <t>IELTS 6.0점 이상 또는 Duolingo 105점 이상 또는 PTE 59점 이상 또는 TOEFL iBT 75점 이상</t>
         </is>
       </c>
       <c r="M188" s="2" t="inlineStr">
@@ -14758,7 +14757,7 @@
       </c>
       <c r="L189" s="2" t="inlineStr">
         <is>
-          <t>IELTS 6.0+, TOEFL iBT 80+ (0-120), TOEFL iBT 4+ (1-6)</t>
+          <t>IELTS 6.0점 이상 또는 TOEFL iBT 80점 이상 (0-120) 또는 TOEFL iBT 4점 이상 (1-6)</t>
         </is>
       </c>
       <c r="M189" s="2" t="inlineStr">
@@ -14835,7 +14834,7 @@
       </c>
       <c r="L190" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Students are expected to arrive with a sufficient level of English in order to be able to follow classes and submit all </t>
+          <t>공인성적 불요 (수강 가능 수준)</t>
         </is>
       </c>
       <c r="M190" s="2" t="inlineStr">
@@ -14908,7 +14907,7 @@
       </c>
       <c r="L191" s="2" t="inlineStr">
         <is>
-          <t>IELTS 6.5+, TOEFL iBT 92+</t>
+          <t>IELTS 6.5점 이상 또는 TOEFL iBT 92점 이상</t>
         </is>
       </c>
       <c r="M191" s="2" t="inlineStr">
@@ -14985,7 +14984,7 @@
       </c>
       <c r="L192" s="2" t="inlineStr">
         <is>
-          <t>IELTS 6.0+, TOEFL iBT 80+</t>
+          <t>IELTS 6.0점 이상 또는 TOEFL iBT 80점 이상</t>
         </is>
       </c>
       <c r="M192" s="2" t="inlineStr">
@@ -15062,7 +15061,7 @@
       </c>
       <c r="L193" s="2" t="inlineStr">
         <is>
-          <t>IELTS 6.0+ (no band below 5.5)</t>
+          <t>IELTS 6.0점 이상 (전 밴드 5.5 이상)</t>
         </is>
       </c>
       <c r="M193" s="2" t="inlineStr">
@@ -15139,7 +15138,7 @@
       </c>
       <c r="L194" s="2" t="inlineStr">
         <is>
-          <t>IELTS 6.5+</t>
+          <t>IELTS 6.5점 이상</t>
         </is>
       </c>
       <c r="M194" s="2" t="inlineStr">
@@ -15281,7 +15280,7 @@
       </c>
       <c r="L196" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 70+, IELTS 6.0+, Duolingo 105+, PTE 48+</t>
+          <t>TOEFL iBT 70점 이상 또는 IELTS 6.0점 이상 또는 Duolingo 105점 이상 또는 PTE 48점 이상</t>
         </is>
       </c>
       <c r="M196" s="2" t="inlineStr">
@@ -15435,7 +15434,7 @@
       </c>
       <c r="L198" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 71+, IELTS 6.0+, Duolingo 105+</t>
+          <t>TOEFL iBT 71점 이상 또는 IELTS 6.0점 이상 또는 Duolingo 105점 이상</t>
         </is>
       </c>
       <c r="M198" s="2" t="inlineStr">
@@ -15585,7 +15584,7 @@
       </c>
       <c r="L200" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 80+, IELTS 6.5+, Duolingo English Test 105+, PTE Academic 67+</t>
+          <t>TOEFL iBT 80점 이상 또는 IELTS 6.5점 이상 또는 Duolingo English Test 105점 이상 또는 PTE Academic 67점 이상</t>
         </is>
       </c>
       <c r="M200" s="2" t="inlineStr">
@@ -15662,7 +15661,7 @@
       </c>
       <c r="L201" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 4+ (2026-01-21 이후), TOEFL iBT 79+ (2026-01-21 이전), IELTS 6.0+, Duolingo 105+</t>
+          <t>TOEFL iBT 4점 이상 (2026-01-21 이후) 또는 TOEFL iBT 79점 이상 (2026-01-21 이전) 또는 IELTS 6.0점 이상 또는 Duolingo 105점 이상</t>
         </is>
       </c>
       <c r="M201" s="2" t="inlineStr">
@@ -15739,7 +15738,7 @@
       </c>
       <c r="L202" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 80+</t>
+          <t>TOEFL iBT 80점 이상</t>
         </is>
       </c>
       <c r="M202" s="2" t="inlineStr">
@@ -15816,7 +15815,7 @@
       </c>
       <c r="L203" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 79+, IELTS 6.5+, Duolingo 105+</t>
+          <t>TOEFL iBT 79점 이상 또는 IELTS 6.5점 이상 또는 Duolingo 105점 이상</t>
         </is>
       </c>
       <c r="M203" s="2" t="inlineStr">
@@ -15889,7 +15888,7 @@
       </c>
       <c r="L204" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 90+, IELTS 6.5+</t>
+          <t>TOEFL iBT 90점 이상 또는 IELTS 6.5점 이상</t>
         </is>
       </c>
       <c r="M204" s="2" t="inlineStr">
@@ -15962,7 +15961,7 @@
       </c>
       <c r="L205" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 68+, IELTS 6.0+, Duolingo 100+, PTE Academic 50+</t>
+          <t>TOEFL iBT 68점 이상 또는 IELTS 6.0점 이상 또는 Duolingo 100점 이상 또는 PTE Academic 50점 이상</t>
         </is>
       </c>
       <c r="M205" s="2" t="inlineStr">
@@ -16039,7 +16038,7 @@
       </c>
       <c r="L206" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 79+, IELTS 6.5+, PTE 58+, Duolingo 105+</t>
+          <t>TOEFL iBT 79점 이상 또는 IELTS 6.5점 이상 또는 PTE 58점 이상 또는 Duolingo 105점 이상</t>
         </is>
       </c>
       <c r="M206" s="2" t="inlineStr">
@@ -16116,7 +16115,7 @@
       </c>
       <c r="L207" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 71+, IELTS 6.0+, CET 4.0+ (학부), CET 6.0+ (대학원)</t>
+          <t>TOEFL iBT 71점 이상 또는 IELTS 6.0점 이상 또는 CET-4 (학부)/CET-6 (대학원)</t>
         </is>
       </c>
       <c r="M207" s="2" t="inlineStr">
@@ -16193,7 +16192,7 @@
       </c>
       <c r="L208" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 79+, IELTS 6.5+, Duolingo 110+</t>
+          <t>TOEFL iBT 79점 이상 또는 IELTS 6.5점 이상 또는 Duolingo 110점 이상</t>
         </is>
       </c>
       <c r="M208" s="2" t="inlineStr">
@@ -16270,7 +16269,7 @@
       </c>
       <c r="L209" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 79+, IELTS 6.5+, Duolingo 115+</t>
+          <t>TOEFL iBT 79점 이상 또는 IELTS 6.5점 이상 또는 Duolingo 115점 이상</t>
         </is>
       </c>
       <c r="M209" s="2" t="inlineStr">
@@ -16343,7 +16342,7 @@
       </c>
       <c r="L210" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 79+, IELTS 6.0+ (undergraduate), IELTS 6.5+ (graduate), Duolingo 110+</t>
+          <t>TOEFL iBT 79점 이상 또는 IELTS 6.0점 이상 (undergraduate) 또는 IELTS 6.5점 이상 (graduate) 또는 Duolingo 110점 이상</t>
         </is>
       </c>
       <c r="M210" s="2" t="inlineStr">
@@ -16420,7 +16419,7 @@
       </c>
       <c r="L211" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 70+, IELTS 6.0+</t>
+          <t>TOEFL iBT 70점 이상 또는 IELTS 6.0점 이상</t>
         </is>
       </c>
       <c r="M211" s="2" t="inlineStr">
@@ -16574,7 +16573,7 @@
       </c>
       <c r="L213" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 79+, IELTS 6.5+, Duolingo 105+, PTEA 56+</t>
+          <t>TOEFL iBT 79점 이상 또는 IELTS 6.5점 이상 또는 Duolingo 105점 이상 또는 PTEA 56점 이상</t>
         </is>
       </c>
       <c r="M213" s="2" t="inlineStr">
@@ -16647,7 +16646,7 @@
       </c>
       <c r="L214" s="2" t="inlineStr">
         <is>
-          <t>Attestation of English Proficiency</t>
+          <t>영어능력 증명 제출 (형식 자유)</t>
         </is>
       </c>
       <c r="M214" s="2" t="inlineStr">
@@ -16720,7 +16719,7 @@
       </c>
       <c r="L215" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 79+ (2026년 1월 21일 이전), TOEFL iBT 4+ (2026년 1월 21일 이후), IELTS 6.5+, Duolingo 110+</t>
+          <t>TOEFL iBT 79점 이상 (2026년 1월 21일 이전) 또는 TOEFL iBT 4점 이상 (2026년 1월 21일 이후) 또는 IELTS 6.5점 이상 또는 Duolingo 110점 이상</t>
         </is>
       </c>
       <c r="M215" s="2" t="inlineStr">
@@ -16797,7 +16796,7 @@
       </c>
       <c r="L216" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 80+, IELTS 6.5+, Duolingo 115+</t>
+          <t>TOEFL iBT 80점 이상 또는 IELTS 6.5점 이상 또는 Duolingo 115점 이상</t>
         </is>
       </c>
       <c r="M216" s="2" t="inlineStr">
@@ -16874,7 +16873,7 @@
       </c>
       <c r="L217" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 79+, IELTS 6.5+</t>
+          <t>TOEFL iBT 79점 이상 또는 IELTS 6.5점 이상</t>
         </is>
       </c>
       <c r="M217" s="2" t="inlineStr">
@@ -16951,7 +16950,7 @@
       </c>
       <c r="L218" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 61+, IELTS 6.0+, PTE 44+, Duolingo 95+ (Engineering: TOEFL iBT 80+, IELTS 6.5+, PTE 53+)</t>
+          <t>TOEFL iBT 61점 이상 또는 IELTS 6.0점 이상 또는 PTE 44점 이상 또는 Duolingo 95점 이상 (Engineering: TOEFL iBT 80+, IELTS 6.5+, PTE 53+)</t>
         </is>
       </c>
       <c r="M218" s="2" t="inlineStr">
@@ -17024,7 +17023,7 @@
       </c>
       <c r="L219" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 80+, iTEP 3.8+, IELTS 6.5+, Duolingo 105+</t>
+          <t>TOEFL iBT 80점 이상 또는 iTEP 3.8점 이상 또는 IELTS 6.5점 이상 또는 Duolingo 105점 이상</t>
         </is>
       </c>
       <c r="M219" s="2" t="inlineStr">
@@ -17101,7 +17100,7 @@
       </c>
       <c r="L220" s="2" t="inlineStr">
         <is>
-          <t>TOEFL 85+, IELTS 6+, Duolingo 130+</t>
+          <t>TOEFL 85점 이상 또는 IELTS 6점 이상 또는 Duolingo 130점 이상</t>
         </is>
       </c>
       <c r="M220" s="2" t="inlineStr">
@@ -17174,7 +17173,7 @@
       </c>
       <c r="L221" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 80+, IELTS 6.5+, Duolingo 120+</t>
+          <t>TOEFL iBT 80점 이상 또는 IELTS 6.5점 이상 또는 Duolingo 120점 이상</t>
         </is>
       </c>
       <c r="M221" s="2" t="inlineStr">
@@ -17251,7 +17250,7 @@
       </c>
       <c r="L222" s="2" t="inlineStr">
         <is>
-          <t>IELTS 6.5+, TOEFL iBT 79+, PTE Academic 58+, Cambridge English CAE 176+</t>
+          <t>IELTS 6.5점 이상 또는 TOEFL iBT 79점 이상 또는 PTE Academic 58점 이상 또는 Cambridge English CAE 176점 이상</t>
         </is>
       </c>
       <c r="M222" s="2" t="inlineStr">

--- a/out/universities.xlsx
+++ b/out/universities.xlsx
@@ -583,12 +583,12 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Students must meet our English requirements via https://study.unimelb.edu.au/how-to-apply/english-language-requirements/</t>
+          <t>IELTS 6.5점 이상 (전 밴드 6.0) 또는 TOEFL iBT 79점 이상</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:시트 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -660,12 +660,12 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>All English language requirements found on this website. We do not accept a letter from Home University - https://www.ne</t>
+          <t>IELTS 6.0점 이상 (전 밴드 6.0) 또는 TOEFL iBT 64점 이상 또는 Duolingo 110점 이상 또는 PTE 50점 이상 (학부 기준)</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>GPA:이메일문의 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:이메일문의 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Pleasse refer to entry requirements: https://www.qut.edu.au/study/international/apply-for-study-abroad#Ready_to_apply</t>
+          <t>IELTS 6.5점 이상 (전 밴드 6.0) 또는 TOEFL iBT 79점 이상</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:시트 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>IELTS 6.5+, TOEFL iBT 92-93+, MELAB 90+, PTE 60+</t>
+          <t>IELTS 6.5점 이상 또는 TOEFL iBT 92점 이상 또는 MELAB 90점 이상 또는 PTE 60점 이상</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -2711,13 +2711,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>We do not accept letter of proficiency.
- https://www.mun.ca/undergrad/admissions/i-want-to-apply/english-proficiency-tes</t>
+          <t>IELTS 6.5점 이상 (R·W 6.0) 또는 TOEFL iBT 4.5점 이상 (신척도) 또는 Duolingo 115점 이상 또는 PTE 60점 이상</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:시트 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3929,12 +3928,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>No language requirements for admission, but there are language requirments for some programmes: https://studies.ku.dk/st</t>
+          <t>일부 학과만 요구 (TOEFL iBT 83점 또는 신척도 4.5 또는 B2 확인; 그 외 불요)</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>GPA:이메일문의 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:이메일문의 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -4075,12 +4074,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>Please read language requirements in the link https://www.en.aau.dk/education/apply/exchange#language-requirements</t>
+          <t>영어 CEFR B2 이상</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>GPA:이메일문의 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:이메일문의 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5449,7 +5448,7 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 80+, IELTS 6.5+, TOEIC 1020+, Duolingo 125+</t>
+          <t>TOEFL iBT 80점 이상 또는 IELTS 6.5점 이상 또는 TOEIC 1020점 이상 (4기능 합산) 또는 Duolingo 125점 이상</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
@@ -6134,7 +6133,7 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>DELF/DALF/TCF B2+, IELTS/TOEFL+</t>
+          <t>프랑스어 CEFR B2 이상 (DELF/DALF/TCF 또는 홈교 교원 확인서)</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
@@ -6669,12 +6668,12 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>We accept Letter of proficiency from home universities (please check our factsheet for details https://www.ece.fr/en/int</t>
+          <t>IELTS 6.0점 이상 또는 TOEFL iBT 83점 이상 또는 TOEIC 780점 이상 (영어과정); 프랑스어과정은 CEFR B2</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>GPA:이메일문의 · 어학:시트 · 수업언어:웹 · 전공:웹 · 위치:AI추정</t>
+          <t>GPA:이메일문의 · 어학:웹 · 수업언어:웹 · 전공:웹 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6888,12 +6887,12 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>TOEFL, IELTS</t>
+          <t>학과별 상이 (통상 영어 CEFR B2 — TOEFL iBT 72점·IELTS 5.5점 상당)</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:시트 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -7192,12 +7191,12 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>Please check our fact sheet</t>
+          <t>영어 CEFR B2 이상 (TOEFL iBT 72점·IELTS 5.0점·TOEIC L&amp;R 785점 상당)</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>GPA:이메일문의 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:이메일문의 · 어학:웹 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -7638,12 +7637,12 @@
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>Website: www.lmu.de/en/international/incoming</t>
+          <t>독일어 CEFR B2 이상 (지원 시 B1); 영어강의만 수강 시 독일어 증명 불요</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>GPA:이메일문의 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:이메일문의 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -10070,7 +10069,7 @@
       </c>
       <c r="L127" s="2" t="inlineStr">
         <is>
-          <t>JLPT N3+, IELTS 5.5+, TOEFL iBT 72+, TOEIC 1530+</t>
+          <t>TOEFL iBT 72점 이상 또는 IELTS 5.5점 이상 또는 TOEIC 1530점 이상 (L&amp;R+S&amp;W×2.5 환산) 또는 JLPT N3 이상</t>
         </is>
       </c>
       <c r="M127" s="2" t="inlineStr">
@@ -10985,7 +10984,7 @@
       </c>
       <c r="L139" s="2" t="inlineStr">
         <is>
-          <t>School of Business and Economics: null, Univeristy College Maastricht: see website, Maastricht Science Programme: TOEFL iBT 90+, TOEFL PBT 575+, TOEFL CBT 232+, IELTS 6.5+</t>
+          <t>학부별 상이 (MSP는 TOEFL iBT 90점 이상 등, UCM은 웹사이트 참조)</t>
         </is>
       </c>
       <c r="M139" s="2" t="inlineStr">
@@ -11881,13 +11880,12 @@
       </c>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t>Last page in the link: https://gem.ntu.edu.sg/_customtags/ct_FileRetrieve.cfm?File_ID=21429 
- The proof of English Langu</t>
+          <t>IELTS 6.0점 이상 (Writing 6.0) 또는 TOEFL iBT 90점 이상 (홈교 확인서 대체 가능)</t>
         </is>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>GPA:웹 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:웹 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
@@ -13930,7 +13928,7 @@
       </c>
       <c r="L178" s="2" t="inlineStr">
         <is>
-          <t>yes we accept your proficiency letter,</t>
+          <t>SKKU 어학확인서 인정</t>
         </is>
       </c>
       <c r="M178" s="2" t="inlineStr">
@@ -14153,7 +14151,7 @@
       </c>
       <c r="L181" s="2" t="inlineStr">
         <is>
-          <t>IELTS 6.0+ (Science), IELTS 6.0+ (ELCC), IELTS 6.5+ (All other modules), IELTS 6.0+ (Law writing), IELTS 5.5+ (Law subscore)</t>
+          <t>IELTS 6.5점 이상 (일부 과목 6.0)</t>
         </is>
       </c>
       <c r="M181" s="2" t="inlineStr">
@@ -14457,12 +14455,12 @@
       </c>
       <c r="L185" s="2" t="inlineStr">
         <is>
-          <t>We have different English requirments depding on student's level of study and duration of stay, Please check 'entry requ</t>
+          <t>IELTS 6.0점 이상 (전 밴드 5.5, 학부) 또는 TOEFL iBT 88점 이상</t>
         </is>
       </c>
       <c r="M185" s="2" t="inlineStr">
         <is>
-          <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:시트 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N185" s="2" t="inlineStr">
@@ -15215,12 +15213,12 @@
       </c>
       <c r="L195" s="2" t="inlineStr">
         <is>
-          <t>확인필요(링크 참조)</t>
+          <t>TOEFL iBT 79점 이상 또는 IELTS 6.5점 이상 또는 PTE 53점 이상</t>
         </is>
       </c>
       <c r="M195" s="2" t="inlineStr">
         <is>
-          <t>GPA:확인필요 · 어학:확인필요 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:확인필요 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N195" s="2" t="inlineStr"/>
@@ -15357,12 +15355,12 @@
       </c>
       <c r="L197" s="2" t="inlineStr">
         <is>
-          <t>The Exchange Student English Proficiency form - https://drive.google.com/file/d/1oJsB3ksKZcm0AX3GsxXM3yOM1sNqgxVH/view?u</t>
+          <t>TOEFL iBT 80점 이상 또는 IELTS 6.5점 이상 (English Ability Form 대체 가능)</t>
         </is>
       </c>
       <c r="M197" s="2" t="inlineStr">
         <is>
-          <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:시트 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N197" s="2" t="inlineStr">
@@ -15511,7 +15509,7 @@
       </c>
       <c r="L199" s="2" t="inlineStr">
         <is>
-          <t>IELTS 6.5+, TOEFL iBT 4+, Duolingo 105+</t>
+          <t>IELTS 6.5점 이상 또는 TOEFL iBT 4점 이상 (2026년 신척도 1~6) 또는 Duolingo 105점 이상</t>
         </is>
       </c>
       <c r="M199" s="2" t="inlineStr">
@@ -16496,12 +16494,12 @@
       </c>
       <c r="L212" s="2" t="inlineStr">
         <is>
-          <t>See "English Language Proficiency for First-Year and Transfer Students" on https://www.psu.edu/resources/international-s</t>
+          <t>TOEFL iBT 80점 이상 (신척도 4.5) 또는 IELTS 6.5점 이상 또는 Duolingo 120점 이상</t>
         </is>
       </c>
       <c r="M212" s="2" t="inlineStr">
         <is>
-          <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:시트 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N212" s="2" t="inlineStr">

--- a/out/universities.xlsx
+++ b/out/universities.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N222"/>
+  <dimension ref="A1:O222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -442,9 +442,10 @@
     <col width="26" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="32" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -505,15 +506,20 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>특징</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>출처 요약</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>참고 링크</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>문의 이메일</t>
         </is>
@@ -577,15 +583,20 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · GPA 요건 없음 · QS 최상위권 종합대</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>https://study.unimelb.edu.au/how-to-apply/international-exchange-and-study-abroad-applications</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>belinda.price@unimelb.edu.au</t>
         </is>
@@ -647,17 +658,18 @@
           <t>IELTS 6.0점 이상 (전 밴드 6.0) 또는 TOEFL iBT 64점 이상 또는 Duolingo 110점 이상 또는 PTE 50점 이상 (학부 기준)</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>GPA:이메일문의 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>https://www.newcastle.edu.au/study/international/study-with-us/study-abroad-and-exchange</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>study-abroad@newcastle.edu.au</t>
         </is>
@@ -721,15 +733,20 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>GPA 요건 없음 · ELICOS 및 준비 과정 제공 · 공학 및 기술 특성화</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>https://www.swinburne.edu.au/courses/planning-your-future/study-abroad-in-melbourne/student-exchange-program/</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>exchange@swin.edu.au</t>
         </is>
@@ -793,15 +810,20 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
+          <t>160+ 학생 클럽 보유 · QS 세계 77위 종합대</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:웹 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>https://www.uwa.edu.au/study/discover-uwa/student-exchange/inbound</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -861,15 +883,20 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
+          <t>트라이메스터제 학사일정 · QS 세계대학랭킹 19위 종합대</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>https://www.unsw.edu.au/study/international-students/study-abroad#studentexchange</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>exchange@unsw.edu.au</t>
         </is>
@@ -933,15 +960,20 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · 호주 내 실용적 교육 강점</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>https://www.qut.edu.au/study/international/apply-for-study-abroad</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>stae@qut.edu.au</t>
         </is>
@@ -1005,15 +1037,20 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · 150+ 학생 동아리 및 과외 프로그램 · 호주 1위 젊은 대학(2024 THE)</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
           <t>GPA:웹 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>https://www.uts.edu.au/for-students/international/study-abroad-exchange-uts</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>studyabroad.exchange@uts.edu.au</t>
         </is>
@@ -1077,15 +1114,20 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
+          <t>트라이메스터제 운영(2월-6월, 7월-11월)</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>https://edit.usc.edu.au/international/global-learning</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>global@usc.edu.au</t>
         </is>
@@ -1149,15 +1191,20 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>OSHC(해외학생 건강보험) 필수 가입</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>https://study.anu.edu.au/apply/applying-exchange-anu</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>global.programs@anu.edu.au</t>
         </is>
@@ -1221,15 +1268,20 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · GPA 요건 없음 · 버디 프로그램 운영 · 교환학생 필수 오리엔테이션 및 교환페어 참석</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>https://www.fh-kufstein.ac.at/en/international/exchange-students</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>iro@fh-kufstein.ac.at</t>
         </is>
@@ -1293,15 +1345,20 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · GPA 요건 없음 · 기숙사 미보장·조기신청 필요 · 전담 오리엔테이션·멘토링</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>international.univie.ac.at/non-eu-in</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>non-eu-exchange@univie.ac.at</t>
         </is>
@@ -1365,15 +1422,20 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · GPA 요건 없음 · Welcome Week 제공 · 18~30 ECTS 학점 선택 가능</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>https://www.fhv.at/incomings/english-courses</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>exchange@fhv.at</t>
         </is>
@@ -1437,15 +1499,20 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · 공인 어학성적 없이 지원 가능 · 오리엔테이션 프로그램 제공 · 연 400명+ 교환학생 수용</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>https://www.mci4me.at/en/international/exchange-incoming</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>incoming@mci.edu</t>
         </is>
@@ -1509,15 +1576,20 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · 공인 어학성적 없이 지원 가능 · 공학·경영 특성화</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/open?id=1BJALvqm3SMEu9pqwMalzXcjExdjd1Vjv</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>international@fh-steyr.at</t>
         </is>
@@ -1581,15 +1653,20 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
+          <t>GPA 요건 없음 · 연 200명+ 교환학생 수용 · 유럽연합 학생 무료 건강보험 적용 · 경영·경영관리 특성화</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>https://www.ichec.be/en/incoming-students</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>kristien.minet@ichec.be</t>
         </is>
@@ -1653,15 +1730,20 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · GPA 요건 없음 · 학생 클럽 Cercle Solvay가 교환학생 대상 사회·커리어 이벤트 주최 · 경영 트리플크라운 인증(AACSB·AMBA·EQUIS) 보유</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>https://sbsem.ulb.be/international/incoming-students</t>
         </is>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>anne.georges@ulb.be</t>
         </is>
@@ -1725,15 +1807,20 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · 비영어권이지만 전 과정 영어 수업 · HEC 캠퍼스 근처 사설 기숙사 · 버디 프로그램 및 국제학생 전용 클럽 운영</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>https://www.programmes.uliege.be/cocoon/20252026/programmes/GZERAS01_B.html</t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>mbequet@uliege.be</t>
         </is>
@@ -1797,15 +1884,20 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · 오리엔테이션 &amp; 버디 프로그램 · 캠퍼스별 전공 특성 차이 (안트베르펜·브뤼셀-경영 실무, 루벤-경제·금융 분석) · 벨기에 최대 종합대</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>https://feb.kuleuven.be/eng/international/coming-to-feb-ku-leuven/informationforincomingstudents</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>internationaloffice.feb@kuleuven.be</t>
         </is>
@@ -1869,15 +1961,20 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
+          <t>공인 어학성적 없이 지원 가능 · 100% 온라인 수업 옵션 제공 · 50년 전통 종합대학</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>Our new website is in development. Students can verify academic offer by the UNISINOS main website.</t>
         </is>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>internacional@unisinos.br</t>
         </is>
@@ -1941,15 +2038,20 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
+          <t>학점 인정 가이드라인 및 성적 환산 기준 제공 · 브라질 최대 국립 종합대학</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:이메일문의 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>https://internationaloffice.usp.br/en/index.php/institutional/usp-units-offices/</t>
         </is>
       </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>mobility.area3@usp.br</t>
         </is>
@@ -2013,15 +2115,20 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>학부 과정 무료(등록금·월비 없음) · 공학·의학·자연과학 강점</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>https://internationaloffice.unicamp.br/en/estrangeiros/estudantes-estrangeiros/formas-de-ingresso/</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>derime@unicamp.br</t>
         </is>
@@ -2085,15 +2192,20 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · 교내 기숙사·홈스테이·개인 숙소 선택 가능 · 국제교육팀 지원 및 오리엔테이션 제공 · 의료보험 필수·교통비 월 $65~$208</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>https://www.okanagan.bc.ca/international/mobility/inbound-mobility</t>
         </is>
       </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>mobility@okanagan.bc.ca</t>
         </is>
@@ -2157,15 +2269,20 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · 비영어권이지만 전 과정 영어 수업 · 기숙사 미보장·조기신청 필요 · 전담 Academic Coordinator 지원</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>https://www.torontomu.ca/the-creative-school/international/exchanges/inbound/</t>
         </is>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>exchange@torontomu.ca</t>
         </is>
@@ -2229,15 +2346,20 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
+          <t>65세 이상 수강생 $100 행정 수수료 · 영어·프랑스어 이중 언어 교육</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:이메일문의 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>https://yorkinternational.yorku.ca/global-learning/incoming-global-learning/explore-academic-exchange/</t>
         </is>
       </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>exchange@yorku.ca</t>
         </is>
@@ -2301,15 +2423,20 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · 비영어권이지만 전 과정 영어 수업 · 교내 기숙사 미보장 · 국제학생지원센터(ISSAC) 운영</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:웹 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>https://students.usask.ca/international/exchange-students.php</t>
         </is>
       </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>issac@usask.ca</t>
         </is>
@@ -2373,15 +2500,20 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · 트라이메스터제 운영(겨울 2027 지원 접수) · 경영 트리플크라운 인증(AACSB, EQUIS, AMBA 보유)</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:이메일문의 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr">
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>https://esg.uqam.ca/international/</t>
         </is>
       </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>esg.international@uqam.ca</t>
         </is>
@@ -2445,15 +2577,20 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · 일부 파트너국 저비용 숙소 · 전체 과정 지원 · 65+ 영어 사용 파트너교</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>https://umanitoba.ca/asper/student-experience/asper-exchange-program#inbound-students-coming-to-asper</t>
         </is>
       </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>amber.pohl@umanitoba.ca</t>
         </is>
@@ -2517,15 +2654,20 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · 필수 보험(Guard.Me) 및 교통비(U-Pass) 납부 · 캐나다 밴쿠버 소재 종합대</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:이메일문의 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>https://www.sfu.ca/students/exchange.html</t>
         </is>
       </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>exchange@sfu.ca</t>
         </is>
@@ -2589,15 +2731,20 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · 캐나다 북대서양 연안에 위치한 종합대학</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>https://mun.ca/goabroad/</t>
         </is>
       </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>goabroad@mun.ca</t>
         </is>
@@ -2661,15 +2808,20 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · 교내 기숙사 신청 가능·수요 높음·조기신청 필요 · 도착 체크리스트·학생 서비스 제공 · QS 세계 40위권 종합대</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:이메일문의 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>https://global.ubc.ca/go-global/coming-ubc/coming-ubc-exchange</t>
         </is>
       </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>(UBC Vancouver) go.global@ubc.ca (UBC Okanagan) goglobal.okanagan@ubc.ca</t>
         </is>
@@ -2733,15 +2885,20 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · 비영어권이지만 전 과정 영어 수업 · 기숙사 미보장·경쟁적 신청 필요 · 여름 학기 기숙사 보장</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:웹 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>https://learningabroad.utoronto.ca/inbound-visiting/student-exchange-fact-sheet/</t>
         </is>
       </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>inbound.exchange@utoronto.ca</t>
         </is>
@@ -2805,15 +2962,20 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
+          <t>연 1000명+ 교환학생 수용 · 프랑스어 B2 이상 필수 · 캐나다 프랑스어권 종합대</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:웹 · 수업언어:웹 · 전공:웹 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr">
+      <c r="N33" s="2" t="inlineStr">
         <is>
           <t>https://international.umontreal.ca/english/international-students/student-exchange-program/</t>
         </is>
       </c>
-      <c r="N33" s="2" t="inlineStr">
+      <c r="O33" s="2" t="inlineStr">
         <is>
           <t>echange@umontreal.ca</t>
         </is>
@@ -2877,15 +3039,20 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
+          <t>연 4,000명+ 국제학생 수용 · 최소 12학점(4과목) 필수 등록, 최대 15학점(5과목)+언어 3학점 · 경영 트리플크라운 인증</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>https://www.hec.ca/en/students/international-exchanges/index.html</t>
         </is>
       </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>elodie.giannecchini@hec.ca</t>
         </is>
@@ -2949,11 +3116,16 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
+          <t>미디어·커뮤니케이션 분야 특성화 국립대</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr"/>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
         <is>
           <t>yjunli@cuc.edu.cn</t>
         </is>
@@ -3017,15 +3189,20 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
+          <t>교내 기숙사 700-1400 CNY/월 · 보험 800 CNY/년 필수 · 공학·의학 특성화 국립대</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr">
+      <c r="N36" s="2" t="inlineStr">
         <is>
           <t>https://iso.hust.edu.cn/info/1194/4633.htm</t>
         </is>
       </c>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>vivianyan@hust.edu.cn</t>
         </is>
@@ -3089,15 +3266,20 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · 글로벌 파트너 200개교 이상</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:이메일문의 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr">
+      <c r="N37" s="2" t="inlineStr">
         <is>
           <t>http://www.en.sdu.edu.cn/</t>
         </is>
       </c>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t>incoming@sdu.edu.cn</t>
         </is>
@@ -3161,15 +3343,20 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · 경영 트리플크라운 인증</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:이메일문의 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M38" s="2" t="inlineStr">
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t>https://international.rmbs.ruc.edu.cn/incoming/</t>
         </is>
       </c>
-      <c r="N38" s="2" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>rmbsexchangeincoming@rmbs.ruc.edu.cn</t>
         </is>
@@ -3233,16 +3420,21 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
+          <t>기숙사 제공 및 공항 픽업 서비스 · 오리엔테이션 및 심리 상담 서비스</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M39" s="2" t="inlineStr">
+      <c r="N39" s="2" t="inlineStr">
         <is>
           <t>Admission Office: https://admission-is.bnu.edu.cn/english/index.html
  International Students Office Website: http://iso.bnu.edu.cn/en/index</t>
         </is>
       </c>
-      <c r="N39" s="2" t="inlineStr">
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>nondegree@bnu.edu.cn</t>
         </is>
@@ -3306,11 +3498,16 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
+          <t>일부 과목 수강 경쟁률 높음 · 공학·경영 특성화</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M40" s="2" t="inlineStr"/>
-      <c r="N40" s="2" t="inlineStr">
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
         <is>
           <t>yayatao@sjtu.edu.cn</t>
         </is>
@@ -3374,15 +3571,20 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · 비영어권이지만 전 과정 영어 수업 · 석사 과정 수강 시 180 ECTS 이상 필요 · 크로아티아 최대 경제·경영 단과대학</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M41" s="2" t="inlineStr">
+      <c r="N41" s="2" t="inlineStr">
         <is>
           <t>https://studentexchange.net.efzg.hr/home</t>
         </is>
       </c>
-      <c r="N41" s="2" t="inlineStr">
+      <c r="O41" s="2" t="inlineStr">
         <is>
           <t>incoming-mobility@net.efzg.hr</t>
         </is>
@@ -3446,15 +3648,20 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · 비영어권이지만 전 과정 영어 수업 · 기숙사 신청 가능 · 버디 시스템·오리엔테이션 주 운영</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M42" s="2" t="inlineStr">
+      <c r="N42" s="2" t="inlineStr">
         <is>
           <t>https://czs.muni.cz/en/student-from-abroad/exchange-non-degree-studies/partner-universities</t>
         </is>
       </c>
-      <c r="N42" s="2" t="inlineStr">
+      <c r="O42" s="2" t="inlineStr">
         <is>
           <t>hrebeska@czs.muni.cz</t>
         </is>
@@ -3518,15 +3725,20 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · 비영어권이지만 전 과정 영어 수업 · 교환학생 기숙사 보장 (Větrník, Hvězda, Kajetánka) · 버디 프로그램 운영</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M43" s="2" t="inlineStr">
+      <c r="N43" s="2" t="inlineStr">
         <is>
           <t>https://cuni.cz/UKEN-344.html</t>
         </is>
       </c>
-      <c r="N43" s="2" t="inlineStr">
+      <c r="O43" s="2" t="inlineStr">
         <is>
           <t>adriana.cernohorska@ruk.cuni.cz</t>
         </is>
@@ -3590,15 +3802,20 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · 학생 기숙사 제공 (에스비에르, 콜딩, 오덴세, 쇠네르보르, 베일레) · 게스트 학생 학비 부과 · 영어 강의 제공 국제 대학</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M44" s="2" t="inlineStr">
+      <c r="N44" s="2" t="inlineStr">
         <is>
           <t>https://www.sdu.dk/en/uddannelse/exchange</t>
         </is>
       </c>
-      <c r="N44" s="2" t="inlineStr">
+      <c r="O44" s="2" t="inlineStr">
         <is>
           <t>incoming@sdu.dk</t>
         </is>
@@ -3662,15 +3879,20 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · 국제학생서비스 지원 · 연 900명+ 교환학생 수용 · 영어 B2 이상 요구</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M45" s="2" t="inlineStr">
+      <c r="N45" s="2" t="inlineStr">
         <is>
           <t>https://www.dtu.dk/english/education/incoming-students/exchange</t>
         </is>
       </c>
-      <c r="N45" s="2" t="inlineStr">
+      <c r="O45" s="2" t="inlineStr">
         <is>
           <t>international@adm.dtu.dk</t>
         </is>
@@ -3734,15 +3956,20 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · 비영어권이지만 전 과정 영어 수업 · 교환학생 기숙사 신청 보장 · 연 2000+ 과목 제공</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M46" s="2" t="inlineStr">
+      <c r="N46" s="2" t="inlineStr">
         <is>
           <t>https://studies.ku.dk/study-abroad/</t>
         </is>
       </c>
-      <c r="N46" s="2" t="inlineStr">
+      <c r="O46" s="2" t="inlineStr">
         <is>
           <t>incomingmobility@adm.ku.dk</t>
         </is>
@@ -3806,11 +4033,16 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · 덴마크 유일의 학제간 프로젝트 기반 교육</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:이메일문의 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M47" s="2" t="inlineStr"/>
-      <c r="N47" s="2" t="inlineStr">
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
         <is>
           <t>incoming-exchange@ruc.dk</t>
         </is>
@@ -3874,15 +4106,20 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · 코펜하겐 캠퍼스 기숙사 구하기 어려움 · 버디 프로그램 및 국제 사무실 지원 · 덴마크어 A레벨 요구(북유럽 교환생)</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M48" s="2" t="inlineStr">
+      <c r="N48" s="2" t="inlineStr">
         <is>
           <t>https://www.en.aau.dk/education/guest-exchange</t>
         </is>
       </c>
-      <c r="N48" s="2" t="inlineStr">
+      <c r="O48" s="2" t="inlineStr">
         <is>
           <t>internationaloffice@aau.dk</t>
         </is>
@@ -3946,15 +4183,20 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · 공인 어학성적 없이 지원 가능 · 갈라파고스 학기제 운영</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M49" s="2" t="inlineStr">
+      <c r="N49" s="2" t="inlineStr">
         <is>
           <t>https://www.usfq.edu.ec/en/opi/international/international-students/academic-programs/semester</t>
         </is>
       </c>
-      <c r="N49" s="2" t="inlineStr">
+      <c r="O49" s="2" t="inlineStr">
         <is>
           <t>vcastelo@usfq.edu.ec</t>
         </is>
@@ -4018,15 +4260,20 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · GPA 요건 없음 · 기숙사 미보장·조기신청 필요 · 학생 버디 프로그램·국제학생 오리엔테이션</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M50" s="2" t="inlineStr">
+      <c r="N50" s="2" t="inlineStr">
         <is>
           <t>www.tlu.ee/exchange</t>
         </is>
       </c>
-      <c r="N50" s="2" t="inlineStr">
+      <c r="O50" s="2" t="inlineStr">
         <is>
           <t>exchange@tlu.ee</t>
         </is>
@@ -4090,15 +4337,20 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · GPA 요건 없음 · ESN(Erasmus Student Network) 활동 · 연 200명+ 교환학생 수용</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M51" s="2" t="inlineStr">
+      <c r="N51" s="2" t="inlineStr">
         <is>
           <t>https://www.lut.fi/en/studies/exchange-studies</t>
         </is>
       </c>
-      <c r="N51" s="2" t="inlineStr">
+      <c r="O51" s="2" t="inlineStr">
         <is>
           <t>incoming@lut.fi</t>
         </is>
@@ -4162,15 +4414,20 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · 공인 어학성적 없이 지원 가능 · 기숙사 사실 미제공 · 교환학생 전용 튜터 배정</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M52" s="2" t="inlineStr">
+      <c r="N52" s="2" t="inlineStr">
         <is>
           <t>https://www.uwasa.fi/en/education/exchange</t>
         </is>
       </c>
-      <c r="N52" s="2" t="inlineStr">
+      <c r="O52" s="2" t="inlineStr">
         <is>
           <t>incoming.international@uwasa.fi</t>
         </is>
@@ -4234,15 +4491,20 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · 교환학생 오리엔테이션(8월 18-21일) 및 전담 인바운드 팀 지원 · 캠퍼스 내 5명 중 1명 국제학생 비율 · 유럽연합 최북단 종합대학(과학·예술 분야)</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M53" s="2" t="inlineStr">
+      <c r="N53" s="2" t="inlineStr">
         <is>
           <t>Exchange studies - University of Lapland</t>
         </is>
       </c>
-      <c r="N53" s="2" t="inlineStr">
+      <c r="O53" s="2" t="inlineStr">
         <is>
           <t>incoming@ulapland.fi</t>
         </is>
@@ -4306,15 +4568,20 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · GPA 요건 없음 · Clinical Medicine 지원자는 3-4월 신청 시 우선권 부여</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M54" s="2" t="inlineStr">
+      <c r="N54" s="2" t="inlineStr">
         <is>
           <t>https://www.uef.fi/en/exchange-studies</t>
         </is>
       </c>
-      <c r="N54" s="2" t="inlineStr">
+      <c r="O54" s="2" t="inlineStr">
         <is>
           <t>international@uef.fi</t>
         </is>
@@ -4378,15 +4645,20 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · 비영어권이지만 전 과정 영어 수업 · 다학제 연구 중심 국립대</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M55" s="2" t="inlineStr">
+      <c r="N55" s="2" t="inlineStr">
         <is>
           <t>https://www.tuni.fi/en/study-with-us/exchange-studies</t>
         </is>
       </c>
-      <c r="N55" s="2" t="inlineStr">
+      <c r="O55" s="2" t="inlineStr">
         <is>
           <t>mobility.tau@tuni.fi</t>
         </is>
@@ -4450,15 +4722,20 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · GPA 요건 없음 · 오리엔테이션 3일 제공 · EU 외 학생 필수 건강보험 가입</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:웹 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M56" s="2" t="inlineStr">
+      <c r="N56" s="2" t="inlineStr">
         <is>
           <t>https://kamk.fi/en/study-at-kamk/apply-to-kamk/exchange-students/</t>
         </is>
       </c>
-      <c r="N56" s="2" t="inlineStr">
+      <c r="O56" s="2" t="inlineStr">
         <is>
           <t>international.office@kamk.fi</t>
         </is>
@@ -4522,15 +4799,20 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · 비영어권이지만 전 과정 영어 수업 · 기숙사 정보 링크 제공 · 튜터 픽업 서비스 및 필수 오리엔테이션 제공</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M57" s="2" t="inlineStr">
+      <c r="N57" s="2" t="inlineStr">
         <is>
           <t>https://www.hanken.fi/en/students/international-opportunities/incoming-exchange-students</t>
         </is>
       </c>
-      <c r="N57" s="2" t="inlineStr">
+      <c r="O57" s="2" t="inlineStr">
         <is>
           <t>incoming.mobility@hanken.fi</t>
         </is>
@@ -4594,15 +4876,20 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · 비영어권이지만 전 과정 영어 수업 · 교환학생 기숙사 보장 · 학생 튜터·오리엔테이션·개인 학습 상담 지원</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M58" s="2" t="inlineStr">
+      <c r="N58" s="2" t="inlineStr">
         <is>
           <t>https://www.haaga-helia.fi/en/exchange-studies-haaga-helia</t>
         </is>
       </c>
-      <c r="N58" s="2" t="inlineStr">
+      <c r="O58" s="2" t="inlineStr">
         <is>
           <t>sami.krogerus@haaga-helia.fi</t>
         </is>
@@ -4666,15 +4953,20 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · GPA 요건 없음 · Housing for exchange students · Mandatory orientation</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M59" s="2" t="inlineStr">
+      <c r="N59" s="2" t="inlineStr">
         <is>
           <t>https://www.aalto.fi/en/international-students/incoming-exchange-students</t>
         </is>
       </c>
-      <c r="N59" s="2" t="inlineStr">
+      <c r="O59" s="2" t="inlineStr">
         <is>
           <t>international-chem@aalto.fi</t>
         </is>
@@ -4738,15 +5030,20 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · 비영어권이지만 전 과정 영어 수업 · 의학·심리학 수강 시 2년 이상 학업 요건, 생명과학은 2년 전공 이수 필요</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:웹 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M60" s="2" t="inlineStr">
+      <c r="N60" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/open?id=1kvv1THoj9gSKqqlS6A-acglLTdlP6gXo</t>
         </is>
       </c>
-      <c r="N60" s="2" t="inlineStr">
+      <c r="O60" s="2" t="inlineStr">
         <is>
           <t>studentexchange@helsinki.fi</t>
         </is>
@@ -4810,15 +5107,20 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · 교내 기숙사 미보장·조기신청 필요 · 학생 튜터 배정(오리엔테이션·실용 문제 지원) · 연 300명+ 교환학생 수용</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:이메일문의 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M61" s="2" t="inlineStr">
+      <c r="N61" s="2" t="inlineStr">
         <is>
           <t>https://www.turkuamk.fi/en/education/exchange-studies/practicalities-for-exchange-students/</t>
         </is>
       </c>
-      <c r="N61" s="2" t="inlineStr">
+      <c r="O61" s="2" t="inlineStr">
         <is>
           <t>incoming.exchange@turkuamk.fi</t>
         </is>
@@ -4882,15 +5184,20 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · GPA 요건 없음 · 필수 예방접종 증명(파상풍·B형 간염) 필요 · 생명공학 특성화 사립대</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:웹 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M62" s="2" t="inlineStr">
+      <c r="N62" s="2" t="inlineStr">
         <is>
           <t>https://www.supbiotech.fr/en/programs/exchange-programs/</t>
         </is>
       </c>
-      <c r="N62" s="2" t="inlineStr">
+      <c r="O62" s="2" t="inlineStr">
         <is>
           <t>incoming@supbiotech.fr</t>
         </is>
@@ -4954,15 +5261,20 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
+          <t>공인 어학성적 없이 지원 가능 · GPA 요건 없음 · 교환학생 브로슈어 제공 · 경영 트리플크라운 인증</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M63" s="2" t="inlineStr">
+      <c r="N63" s="2" t="inlineStr">
         <is>
           <t>https://www.inseec.com/incoming-students-inseec-grande-ecole/</t>
         </is>
       </c>
-      <c r="N63" s="2" t="inlineStr">
+      <c r="O63" s="2" t="inlineStr">
         <is>
           <t>incoming@inseec.com</t>
         </is>
@@ -5026,15 +5338,20 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · 비영어권이지만 전 과정 영어 수업 · 기숙사 미보장·조기신청 필요 · 버디 프로그램·학생협회 지원</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M64" s="2" t="inlineStr">
+      <c r="N64" s="2" t="inlineStr">
         <is>
           <t>https://www.iscparis.com/en/incoming-students/</t>
         </is>
       </c>
-      <c r="N64" s="2" t="inlineStr">
+      <c r="O64" s="2" t="inlineStr">
         <is>
           <t>exchange@iscparis.com</t>
         </is>
@@ -5098,15 +5415,20 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · GPA 요건 없음 · 경영 트리플크라운 인증</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M65" s="2" t="inlineStr">
+      <c r="N65" s="2" t="inlineStr">
         <is>
           <t>https://drive.google.com/drive/u/1/folders/16CUWxk2R1NtRBJqsZ6iO3zqDlAABqKwE</t>
         </is>
       </c>
-      <c r="N65" s="2" t="inlineStr">
+      <c r="O65" s="2" t="inlineStr">
         <is>
           <t>severine.myly@icn-artem.com</t>
         </is>
@@ -5170,15 +5492,20 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · 정보 세션 및 튜터 지원 · 비자 신청용 입학허가서 발급</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:웹 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M66" s="2" t="inlineStr">
+      <c r="N66" s="2" t="inlineStr">
         <is>
           <t>https://www.univ-lyon3.fr/exchange-students-1</t>
         </is>
       </c>
-      <c r="N66" s="2" t="inlineStr">
+      <c r="O66" s="2" t="inlineStr">
         <is>
           <t>lucien.yang@univ-lyon3.fr</t>
         </is>
@@ -5242,15 +5569,20 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · 프랑스어 레벨 테스트 필수 · 경영 트리플크라운 인증</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M67" s="2" t="inlineStr">
+      <c r="N67" s="2" t="inlineStr">
         <is>
           <t>https://aloha.rennes-sb.com/hc/en-us/categories/360002608799--Incoming-Exchange-Students</t>
         </is>
       </c>
-      <c r="N67" s="2" t="inlineStr">
+      <c r="O67" s="2" t="inlineStr">
         <is>
           <t>exchange@rennes-sb.com</t>
         </is>
@@ -5314,15 +5646,20 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · 파트너 230개교 · 학기당 25~35 ECTS 수강 · 경영 트리플크라운 인증</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M68" s="2" t="inlineStr">
+      <c r="N68" s="2" t="inlineStr">
         <is>
           <t>https://em-lyon.com/en/student/bachelor/global-bba/exchange-students</t>
         </is>
       </c>
-      <c r="N68" s="2" t="inlineStr">
+      <c r="O68" s="2" t="inlineStr">
         <is>
           <t>Incoming.globalbba@em-lyon.com</t>
         </is>
@@ -5386,15 +5723,20 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · Grande Ecole 21ECTS/학기, BBA 30ECTS/학기 · 경영 트리플크라운 인증</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M69" s="2" t="inlineStr">
+      <c r="N69" s="2" t="inlineStr">
         <is>
           <t>https://www.skema.edu/en/exchange-students</t>
         </is>
       </c>
-      <c r="N69" s="2" t="inlineStr">
+      <c r="O69" s="2" t="inlineStr">
         <is>
           <t>studentexchange.incoming@skema.edu</t>
         </is>
@@ -5458,15 +5800,20 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
+          <t>GPA 요건 없음 · 교내 기숙사 미보장·조기신청 필요 · 프랑스어 B1-B2 또는 영어 B2 권장 · 공학·자연과학·인문학 강점 종합대</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:웹 · 수업언어:웹 · 전공:웹 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M70" s="2" t="inlineStr">
+      <c r="N70" s="2" t="inlineStr">
         <is>
           <t>https://international.univ-grenoble-alpes.fr/come-to-uga/exchange-programs/come-on-exchange/come-on-exchange-784754.kjsp?RH=1610017301259</t>
         </is>
       </c>
-      <c r="N70" s="2" t="inlineStr">
+      <c r="O70" s="2" t="inlineStr">
         <is>
           <t>incoming@univ-grenoble-alpes.fr</t>
         </is>
@@ -5530,15 +5877,20 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
+          <t>프랑스어/영어 집중 세미나 및 언어 강좌 제공 · 전 세계 수백 개 대학과 교환 협약 체결 · 최대 30 ECTS(프랑스어 세미나 수강 시 33 ECTS) 수강 가능 · 경영·경제·수학·컴퓨터과학 분야 특성화 대학</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:웹 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M71" s="2" t="inlineStr">
+      <c r="N71" s="2" t="inlineStr">
         <is>
           <t>https://dauphine.psl.eu/international/venir-etudier-a-luniversite-paris-dauphine-psl/etudiants-en-echange</t>
         </is>
       </c>
-      <c r="N71" s="2" t="inlineStr">
+      <c r="O71" s="2" t="inlineStr">
         <is>
           <t>contact.echanges@dauphine.fr</t>
         </is>
@@ -5602,15 +5954,20 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
+          <t>연 1000명+ 교환학생 수용 · 프랑스어·영어 병행 수업 선택 가능 · 경영 트리플크라운 인증</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M72" s="2" t="inlineStr">
+      <c r="N72" s="2" t="inlineStr">
         <is>
           <t>https://student.kedge.edu/exchange-students</t>
         </is>
       </c>
-      <c r="N72" s="2" t="inlineStr">
+      <c r="O72" s="2" t="inlineStr">
         <is>
           <t>incoming@kedgebs.com</t>
         </is>
@@ -5674,15 +6031,20 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · GPA 요건 없음 · 교내·외 기숙사 지원 · 버디 시스템·국제 클럽·프랑스어 수업</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M73" s="2" t="inlineStr">
+      <c r="N73" s="2" t="inlineStr">
         <is>
           <t>https://www.ieseg.fr/en/international/study-at-ieseg-in-exchange/</t>
         </is>
       </c>
-      <c r="N73" s="2" t="inlineStr">
+      <c r="O73" s="2" t="inlineStr">
         <is>
           <t>incomingparis@ieseg.fr</t>
         </is>
@@ -5746,15 +6108,20 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · 프랑스어 불필요(교환 지원 시) · 공학 특성화</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M74" s="2" t="inlineStr">
+      <c r="N74" s="2" t="inlineStr">
         <is>
           <t>www.epf.fr/en</t>
         </is>
       </c>
-      <c r="N74" s="2" t="inlineStr">
+      <c r="O74" s="2" t="inlineStr">
         <is>
           <t>cecile.carnoy@epf.fr</t>
         </is>
@@ -5818,15 +6185,20 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · GPA 요건 없음 · 파트너 300개교+ · 인문학·사회과학 특성화</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:웹 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M75" s="2" t="inlineStr">
+      <c r="N75" s="2" t="inlineStr">
         <is>
           <t>https://international.pantheonsorbonne.fr/en/join-paris-1-pantheon-sorbonne/exchange-student</t>
         </is>
       </c>
-      <c r="N75" s="2" t="inlineStr">
+      <c r="O75" s="2" t="inlineStr">
         <is>
           <t>incoming-exchange@univ-paris1.fr</t>
         </is>
@@ -5890,15 +6262,20 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
+          <t>가톨릭 계열 종합대</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M76" s="2" t="inlineStr">
+      <c r="N76" s="2" t="inlineStr">
         <is>
           <t>https://www.univ-catholille.fr/en/exchange-programs-academic-calendars/</t>
         </is>
       </c>
-      <c r="N76" s="2" t="inlineStr">
+      <c r="O76" s="2" t="inlineStr">
         <is>
           <t>alizee.leducq@univ-catholille.fr</t>
         </is>
@@ -5962,15 +6339,20 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
+          <t>GPA 요건 없음 · 국제학생 오리엔테이션 필수 참석 · 160개 파트너 대학, 100+ 국적 학생 · 무료 프랑스어 수업(5 ECTS), 필수 출석</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:factsheet · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M77" s="2" t="inlineStr">
+      <c r="N77" s="2" t="inlineStr">
         <is>
           <t>chrome-extension://efaidnbmnnnibpcajpcglclefindmkaj/https://my.edhec.edu/sites/default/files/myedhec/Factsheet_EDHEC_BBA_25-26_2.pdf</t>
         </is>
       </c>
-      <c r="N77" s="2" t="inlineStr">
+      <c r="O77" s="2" t="inlineStr">
         <is>
           <t>hannah.sztumpf@edhec.edu</t>
         </is>
@@ -6034,15 +6416,20 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · 국제학생 대상 연중 행사 운영 · 모든 캠퍼스 교환 프로그램 가능 · 스페인어 집중 코스(8월 말 시작)</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M78" s="2" t="inlineStr">
+      <c r="N78" s="2" t="inlineStr">
         <is>
           <t>https://www.tbs-education.com/about-tbs/international/incoming-exchange-students/</t>
         </is>
       </c>
-      <c r="N78" s="2" t="inlineStr">
+      <c r="O78" s="2" t="inlineStr">
         <is>
           <t>tbs.incoming@tbs-education.fr</t>
         </is>
@@ -6106,15 +6493,20 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
+          <t>GPA 요건 없음 · 외부 기숙사 협력 (월 €450-700), 보장 불가 · 프랑스어 시험 필수 (도착 전), 학기별 시험 기간 2주 · 아시아·아프리카·중동 언어·문명 연구 특화 국립대</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:웹 · 수업언어:웹 · 전공:웹 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M79" s="2" t="inlineStr">
+      <c r="N79" s="2" t="inlineStr">
         <is>
           <t>https://www.inalco.fr/en/exchange-students-inalco</t>
         </is>
       </c>
-      <c r="N79" s="2" t="inlineStr">
+      <c r="O79" s="2" t="inlineStr">
         <is>
           <t>mob-in@inalco.fr</t>
         </is>
@@ -6178,15 +6570,20 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
+          <t>GPA 요건 없음 · 공학 특성화</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M80" s="2" t="inlineStr">
+      <c r="N80" s="2" t="inlineStr">
         <is>
           <t>https://www.eivp-paris.fr/international/study-at-eivp</t>
         </is>
       </c>
-      <c r="N80" s="2" t="inlineStr">
+      <c r="O80" s="2" t="inlineStr">
         <is>
           <t>julien.leroy@eivp-paris.fr</t>
         </is>
@@ -6250,15 +6647,20 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
+          <t>GPA 요건 없음 · HUB를 통한 전 과정 지원 · 연 2100명+ 교환학생 수용 · 프랑스어 B2 이상 필수</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:웹 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M81" s="2" t="inlineStr">
+      <c r="N81" s="2" t="inlineStr">
         <is>
           <t>https://neoma-bs.com/welcome-to-neoma</t>
         </is>
       </c>
-      <c r="N81" s="2" t="inlineStr">
+      <c r="O81" s="2" t="inlineStr">
         <is>
           <t>hub.rouen@neoma-bs.fr</t>
         </is>
@@ -6322,15 +6724,20 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · 교내 기숙사 미보장·조기신청 필요 · 버디 프로그램·학생협회 지원 · 월 평균 1200~1900유로 생활비</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:웹 · 수업언어:웹 · 전공:웹 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M82" s="2" t="inlineStr">
+      <c r="N82" s="2" t="inlineStr">
         <is>
           <t>https://www.ece.fr/en/international-en/</t>
         </is>
       </c>
-      <c r="N82" s="2" t="inlineStr">
+      <c r="O82" s="2" t="inlineStr">
         <is>
           <t>international@ece.fr</t>
         </is>
@@ -6394,15 +6801,20 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
+          <t>교환학생 기숙사 일부 보장·조기신청 필요 · 버디 프로그램·국제학생팀 지원 · 연 23,000명+ 학생·100개국 이상 국제학생 · 학기별 360유로 기여금(교통권 포함)</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:이메일문의 · 수업언어:factsheet · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M83" s="2" t="inlineStr">
+      <c r="N83" s="2" t="inlineStr">
         <is>
           <t>https://www.uni-wuppertal.de/fileadmin/data/bu/Internationales/IntSek/Gast-_und_Austauschstudium/Erasmus__/Fact_Sheet_for_Exchange_Students.pdf</t>
         </is>
       </c>
-      <c r="N83" s="2" t="inlineStr">
+      <c r="O83" s="2" t="inlineStr">
         <is>
           <t>myfey@uni-wuppertal.de</t>
         </is>
@@ -6466,11 +6878,16 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · 경영·경제 분야 강세</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M84" s="2" t="inlineStr"/>
-      <c r="N84" s="2" t="inlineStr">
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr">
         <is>
           <t>incomings@uni-mannheim.de</t>
         </is>
@@ -6534,15 +6951,20 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · GPA 요건 없음 · 교환학생 상담 서비스 제공 · 영어 강의 수강 가능</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M85" s="2" t="inlineStr">
+      <c r="N85" s="2" t="inlineStr">
         <is>
           <t>https://international.ruhr-uni-bochum.de/en/international-exchange-students</t>
         </is>
       </c>
-      <c r="N85" s="2" t="inlineStr">
+      <c r="O85" s="2" t="inlineStr">
         <is>
           <t>rubiss@ruhr-uni-bochum.de</t>
         </is>
@@ -6606,15 +7028,20 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · GPA 요건 없음 · 독일어 과정·기업 방문·소셜 활동 제공 · 경영·디지털 기술·AI 분야 특화</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M86" s="2" t="inlineStr">
+      <c r="N86" s="2" t="inlineStr">
         <is>
           <t>https://www.cbs.de/en/international/certificate-programmes</t>
         </is>
       </c>
-      <c r="N86" s="2" t="inlineStr">
+      <c r="O86" s="2" t="inlineStr">
         <is>
           <t>international.office@cbs.de</t>
         </is>
@@ -6678,15 +7105,20 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · 기숙사 신청 필수·조기신청 필요 · 오리엔테이션 주·버디 프로그램 · 영어 강의·과정 제공</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M87" s="2" t="inlineStr">
+      <c r="N87" s="2" t="inlineStr">
         <is>
           <t>https://www.uni-rostock.de/en/international-affairs/incoming/gueststudies-erasmus/</t>
         </is>
       </c>
-      <c r="N87" s="2" t="inlineStr">
+      <c r="O87" s="2" t="inlineStr">
         <is>
           <t>incoming.io@uni-rostock.de</t>
         </is>
@@ -6750,15 +7182,20 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
+          <t>공인 어학성적 없이 지원 가능 · GPA 요건 없음 · 보험 미제공, B2 어학 권장 · 공학·IT 특성화</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M88" s="2" t="inlineStr">
+      <c r="N88" s="2" t="inlineStr">
         <is>
           <t>https://www.tu-chemnitz.de/international/incoming/erasmus/index.php.en</t>
         </is>
       </c>
-      <c r="N88" s="2" t="inlineStr">
+      <c r="O88" s="2" t="inlineStr">
         <is>
           <t>nadja.hueller@iuz.tu-chemnitz.de</t>
         </is>
@@ -6822,15 +7259,20 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
+          <t>버디 프로그램 운영 · 모듈 핸드북 온라인 제공</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:웹 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M89" s="2" t="inlineStr">
+      <c r="N89" s="2" t="inlineStr">
         <is>
           <t>Studying at Leuphana | Leuphana</t>
         </is>
       </c>
-      <c r="N89" s="2" t="inlineStr">
+      <c r="O89" s="2" t="inlineStr">
         <is>
           <t>kirja.frommeyer@leuphana.de</t>
         </is>
@@ -6894,15 +7336,20 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
+          <t>교환학생 전용 오리엔테이션 및 온라인 상담 제공 · 파트너 대학 대상 GStEP 프로그램 운영 · 학기 시작 전 3개 트랙의 예비 수업 제공 · 프랑크푸르트 학파 이론 연구 중심 대학</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M90" s="2" t="inlineStr">
+      <c r="N90" s="2" t="inlineStr">
         <is>
           <t>https://www.uni-frankfurt.de/122909823/Incoming_Guest_students_and_Internships_at_Goethe_University?locale=en</t>
         </is>
       </c>
-      <c r="N90" s="2" t="inlineStr">
+      <c r="O90" s="2" t="inlineStr">
         <is>
           <t>incoming@uni-frankfurt.de</t>
         </is>
@@ -6966,15 +7413,20 @@
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · 비영어권이지만 전 과정 영어 수업</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M91" s="2" t="inlineStr">
+      <c r="N91" s="2" t="inlineStr">
         <is>
           <t>https://wiso.uni-koeln.de/de/studium/international/incoming-exchange-at-wiso/semester-exchange</t>
         </is>
       </c>
-      <c r="N91" s="2" t="inlineStr">
+      <c r="O91" s="2" t="inlineStr">
         <is>
           <t>incomings@wiso.uni-koeln.de</t>
         </is>
@@ -7038,15 +7490,20 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
+          <t>GPA 요건 없음</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M92" s="2" t="inlineStr">
+      <c r="N92" s="2" t="inlineStr">
         <is>
           <t>https://www.studium.uni-kiel.de/en/examinations/examination-procedure/general-information/the-grading-system</t>
         </is>
       </c>
-      <c r="N92" s="2" t="inlineStr">
+      <c r="O92" s="2" t="inlineStr">
         <is>
           <t>cau-exchange@uv.uni-kiel.de</t>
         </is>
@@ -7110,15 +7567,20 @@
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
+          <t>기숙사 엘리베이터 미설치·버디 지원 · 버디 프로그램 운영 · 다국적 학생 교류 활발 · 저렴한 생활비·짧은 통학 거리</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M93" s="2" t="inlineStr">
+      <c r="N93" s="2" t="inlineStr">
         <is>
           <t>https://www.hs-osnabrueck.de/en/university/faculties/wiso/international/incoming/</t>
         </is>
       </c>
-      <c r="N93" s="2" t="inlineStr">
+      <c r="O93" s="2" t="inlineStr">
         <is>
           <t>incoming-overseas-wiso@hs-osnabrueck.de</t>
         </is>
@@ -7182,15 +7644,20 @@
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
+          <t>GPA 요건 없음 · 120개 이상 대학 파트너십 · 비EU 국적자 거주허가 필요 · 독일 명문 종합대</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:이메일문의 · 수업언어:웹 · 전공:웹 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M94" s="2" t="inlineStr">
+      <c r="N94" s="2" t="inlineStr">
         <is>
           <t>Direct Exchange • Education • Freie Universität Berlin</t>
         </is>
       </c>
-      <c r="N94" s="2" t="inlineStr">
+      <c r="O94" s="2" t="inlineStr">
         <is>
           <t>incoming@fu-berlin.de</t>
         </is>
@@ -7254,15 +7721,20 @@
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · 기숙사 및 민간 숙소 지원 · 버디 프로그램 운영 · 비자·보험·등록 지원</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M95" s="2" t="inlineStr">
+      <c r="N95" s="2" t="inlineStr">
         <is>
           <t>www.lmu.de/en/international/incoming</t>
         </is>
       </c>
-      <c r="N95" s="2" t="inlineStr">
+      <c r="O95" s="2" t="inlineStr">
         <is>
           <t>lmuexchange-incoming@lmu.de</t>
         </is>
@@ -7326,15 +7798,20 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
+          <t>기숙사 비용 월 280~470유로, 1인 아파트 350유로 · 버디 프로그램 운영</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:웹 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M96" s="2" t="inlineStr">
+      <c r="N96" s="2" t="inlineStr">
         <is>
           <t>Exchange students | International | Furtwangen University</t>
         </is>
       </c>
-      <c r="N96" s="2" t="inlineStr">
+      <c r="O96" s="2" t="inlineStr">
         <is>
           <t>incoming@hs-furtwangen.de</t>
         </is>
@@ -7398,15 +7875,20 @@
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
+          <t>버디 프로그램 운영</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M97" s="2" t="inlineStr">
+      <c r="N97" s="2" t="inlineStr">
         <is>
           <t>https://www.frankfurt-university.de/en/studies/international-office/incomings/exchange/</t>
         </is>
       </c>
-      <c r="N97" s="2" t="inlineStr">
+      <c r="O97" s="2" t="inlineStr">
         <is>
           <t>incoming.exchange@io.fra-uas.de</t>
         </is>
@@ -7470,15 +7952,20 @@
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · 비영어권이지만 전 과정 영어 수업 · 교환학생 전담 지원 서비스 · 여름/겨울 학교 프로그램 운영</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M98" s="2" t="inlineStr">
+      <c r="N98" s="2" t="inlineStr">
         <is>
           <t>https://www.frankfurt-school.de/de/students-alumni/international-office</t>
         </is>
       </c>
-      <c r="N98" s="2" t="inlineStr">
+      <c r="O98" s="2" t="inlineStr">
         <is>
           <t>InternationalOffice@fs.de</t>
         </is>
@@ -7542,15 +8029,20 @@
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · 비영어권이지만 전 과정 영어 수업 · 기숙사 미보장·조기신청 필요 · 버디 프로그램·독일어 집중 코스</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M99" s="2" t="inlineStr">
+      <c r="N99" s="2" t="inlineStr">
         <is>
           <t>https://www.hwr-berlin.de/en/study/international-study/exchange-students-at-the-hwr-berlin/organizing-your-studies-at-department-1</t>
         </is>
       </c>
-      <c r="N99" s="2" t="inlineStr">
+      <c r="O99" s="2" t="inlineStr">
         <is>
           <t>incoming@hwr-berlin.de</t>
         </is>
@@ -7614,15 +8106,20 @@
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · 선택적 기숙사 제공 · 국제 사무실 지원 · 전 세계 40개 파트너 대학</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M100" s="2" t="inlineStr">
+      <c r="N100" s="2" t="inlineStr">
         <is>
           <t>https://www.uni-bonn.de/en/studying/international-students/exchange-students/global-exchange-program/global-exchange-program?set_language=en</t>
         </is>
       </c>
-      <c r="N100" s="2" t="inlineStr">
+      <c r="O100" s="2" t="inlineStr">
         <is>
           <t>globalexchange-incoming@uni-bonn.de</t>
         </is>
@@ -7686,15 +8183,20 @@
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · GPA 요건 없음 · 교내 기숙사 미보장·조기신청 필요 · 버디 프로그램(BeBuddy), 웰컴 위크, 전담 교환학생 서비스</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:factsheet · 수업언어:factsheet · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M101" s="2" t="inlineStr">
+      <c r="N101" s="2" t="inlineStr">
         <is>
           <t>https://www.wiwi.rwth-aachen.de/cms/wirtschaftswissenschaften/studium/Internationales/Exchange-Office/~icy/Incomings/</t>
         </is>
       </c>
-      <c r="N101" s="2" t="inlineStr">
+      <c r="O101" s="2" t="inlineStr">
         <is>
           <t>stefanie.spatafora@wiwi.rwth-aachen.de</t>
         </is>
@@ -7758,15 +8260,20 @@
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
+          <t>기숙사 사실 미보장·개별 신청 필요 · 월 생활비 992-1250유로·학기당 72유로 필수 납부 · 공학·의학·자연과학 강점 국립대</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M102" s="2" t="inlineStr">
+      <c r="N102" s="2" t="inlineStr">
         <is>
           <t>https://www.fau.eu/studying/international-students/students-on-exchange-programs/</t>
         </is>
       </c>
-      <c r="N102" s="2" t="inlineStr">
+      <c r="O102" s="2" t="inlineStr">
         <is>
           <t>mobility@fau.de</t>
         </is>
@@ -7830,15 +8337,20 @@
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
+          <t>홍콩 최상위권 종합대</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M103" s="2" t="inlineStr">
+      <c r="N103" s="2" t="inlineStr">
         <is>
           <t>https://www.oal.cuhk.edu.hk/campuslife/</t>
         </is>
       </c>
-      <c r="N103" s="2" t="inlineStr">
+      <c r="O103" s="2" t="inlineStr">
         <is>
           <t>claireli@cuhk.edu.hk</t>
         </is>
@@ -7902,15 +8414,20 @@
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
+          <t>봄학기 기숙사 가용성 높음 · 오리엔테이션 및 활동 제공 · 학점 24-30학점 권장, 법학 전공자 비법학 과목 제한 · 아시아 최상위권 종합대</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
           <t>GPA:웹 · 어학:웹 · 수업언어:웹 · 전공:웹 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M104" s="2" t="inlineStr">
+      <c r="N104" s="2" t="inlineStr">
         <is>
           <t>https://intlaffairs.hku.hk/exchange</t>
         </is>
       </c>
-      <c r="N104" s="2" t="inlineStr">
+      <c r="O104" s="2" t="inlineStr">
         <is>
           <t>exchange@hku.hk</t>
         </is>
@@ -7974,15 +8491,20 @@
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
+          <t>QS 세계대학랭킹 100위권 종합대</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M105" s="2" t="inlineStr">
+      <c r="N105" s="2" t="inlineStr">
         <is>
           <t>https://www.cityu.edu.hk/geo/global-opportunities/student-exchange/inbound-student-exchange</t>
         </is>
       </c>
-      <c r="N105" s="2" t="inlineStr">
+      <c r="O105" s="2" t="inlineStr">
         <is>
           <t>phoebe.sung@cityu.edu.hk</t>
         </is>
@@ -8046,15 +8568,20 @@
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
+          <t>공학·비즈니스·건설환경 분야 강세</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:웹 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M106" s="2" t="inlineStr">
+      <c r="N106" s="2" t="inlineStr">
         <is>
           <t>https://www.polyu.edu.hk/geo/exchange-and-study-abroad/incoming-students/incoming-exchange/</t>
         </is>
       </c>
-      <c r="N106" s="2" t="inlineStr">
+      <c r="O106" s="2" t="inlineStr">
         <is>
           <t>inbound.exchange@polyu.edu.hk</t>
         </is>
@@ -8118,15 +8645,20 @@
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
+          <t>ESN Pécs 지원 · 유럽 300만 명 이상 교환학생 참여 · 헝가리 최대 규모 종합대학</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M107" s="2" t="inlineStr">
+      <c r="N107" s="2" t="inlineStr">
         <is>
           <t>https://international.pte.hu/mobility-programs/erasmus</t>
         </is>
       </c>
-      <c r="N107" s="2" t="inlineStr">
+      <c r="O107" s="2" t="inlineStr">
         <is>
           <t>czeh.gabor@pte.hu</t>
         </is>
@@ -8190,15 +8722,20 @@
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
+          <t>저렴한 생활비, 친절한 지역사회, 활발한 학술분위기 · 인도네시아 최상위권 종합대</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M108" s="2" t="inlineStr">
+      <c r="N108" s="2" t="inlineStr">
         <is>
           <t>https://admission.ugm.ac.id/non-degree/student-exchange/</t>
         </is>
       </c>
-      <c r="N108" s="2" t="inlineStr">
+      <c r="O108" s="2" t="inlineStr">
         <is>
           <t>admission@ugm.ac.id</t>
         </is>
@@ -8262,15 +8799,20 @@
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · 오리엔테이션 프로그램·사전 출발 세션 제공 · 인도네시아 국립 종합대</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M109" s="2" t="inlineStr">
+      <c r="N109" s="2" t="inlineStr">
         <is>
           <t>https://international.ui.ac.id/exchange-program/</t>
         </is>
       </c>
-      <c r="N109" s="2" t="inlineStr">
+      <c r="O109" s="2" t="inlineStr">
         <is>
           <t>inbound@ui.ac.id</t>
         </is>
@@ -8334,15 +8876,20 @@
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
+          <t>월 €450 공유 학생 아파트 · 학기 초 오리엔테이션 데이 · 연간 500명+ 교환학생 수용 · 월 생활비 €1,000 (식비 €450 포함)</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M110" s="2" t="inlineStr">
+      <c r="N110" s="2" t="inlineStr">
         <is>
           <t>https://www.univr.it/en/our-services/incoming-students-and-staff/exchange-students#doc_715</t>
         </is>
       </c>
-      <c r="N110" s="2" t="inlineStr">
+      <c r="O110" s="2" t="inlineStr">
         <is>
           <t>relazioni.internazionali@ateneo.univr.it</t>
         </is>
@@ -8406,15 +8953,20 @@
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
+          <t>GPA 요건 없음 · 학생 기숙사 제공 · 공학·건축 특성화</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M111" s="2" t="inlineStr">
+      <c r="N111" s="2" t="inlineStr">
         <is>
           <t>https://www.polimi.it/en/campus-e-servizi/international-mobility/study-abroad</t>
         </is>
       </c>
-      <c r="N111" s="2" t="inlineStr">
+      <c r="O111" s="2" t="inlineStr">
         <is>
           <t>exchange-leonardo@polimi.it</t>
         </is>
@@ -8478,15 +9030,20 @@
       </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · GPA 요건 없음 · Welcome Unit 개별 오리엔테이션 제공 · 700+ 해외 대학과 교환 협약</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M112" s="2" t="inlineStr">
+      <c r="N112" s="2" t="inlineStr">
         <is>
           <t>https://www.unive.it/pag/12574/</t>
         </is>
       </c>
-      <c r="N112" s="2" t="inlineStr">
+      <c r="O112" s="2" t="inlineStr">
         <is>
           <t>incoming.mobility@unive.it</t>
         </is>
@@ -8550,15 +9107,20 @@
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · GPA 요건 없음 · 기숙사 미보장·조기신청 필요 · 국제학생데스크(ISD) 지원 서비스</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M113" s="2" t="inlineStr">
+      <c r="N113" s="2" t="inlineStr">
         <is>
           <t>https://www.unibocconi.it/en/international-students/incoming-exchange-students</t>
         </is>
       </c>
-      <c r="N113" s="2" t="inlineStr">
+      <c r="O113" s="2" t="inlineStr">
         <is>
           <t>inexchange@unibocconi.it</t>
         </is>
@@ -8622,15 +9184,20 @@
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
+          <t>오리엔테이션 제공 · 석사생 수강 제한(일본어·영어 강의만)</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M114" s="2" t="inlineStr">
+      <c r="N114" s="2" t="inlineStr">
         <is>
           <t>https://intl.okayama-u.ac.jp/en/inbound/programs/epok/</t>
         </is>
       </c>
-      <c r="N114" s="2" t="inlineStr">
+      <c r="O114" s="2" t="inlineStr">
         <is>
           <t>epok-inbound1@adm.okayama-u.ac.jp</t>
         </is>
@@ -8694,15 +9261,20 @@
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
+          <t>GPA 요건 없음 · 영어 능력 시험 및 언어 검정 시험 응시료 지원 제도 · 스포츠·건강과학부 운영</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M115" s="2" t="inlineStr">
+      <c r="N115" s="2" t="inlineStr">
         <is>
           <t>https://www.daito.ac.jp/english/admissions/exchange.html</t>
         </is>
       </c>
-      <c r="N115" s="2" t="inlineStr">
+      <c r="O115" s="2" t="inlineStr">
         <is>
           <t>dbuexchange@jm.daito.ac.jp</t>
         </is>
@@ -8766,15 +9338,20 @@
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · GPA 요건 없음 · 일본 국민건강보험(연 3만엔) 및 학생 사고보험(1,340엔) 필수 가입</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M116" s="2" t="inlineStr">
+      <c r="N116" s="2" t="inlineStr">
         <is>
           <t>https://www.nishogakusha-u.ac.jp/international/study_abroad_application.html</t>
         </is>
       </c>
-      <c r="N116" s="2" t="inlineStr">
+      <c r="O116" s="2" t="inlineStr">
         <is>
           <t>icenter1@nishogakusha-u.ac.jp</t>
         </is>
@@ -8838,15 +9415,20 @@
       </c>
       <c r="L117" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · 기숙사·아파트·홈스테이 정보 핸드북 제공 · 35개국 160개 파트너 대학 · 학기당 14학점(10시간 수업) 필수</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M117" s="2" t="inlineStr">
+      <c r="N117" s="2" t="inlineStr">
         <is>
           <t>https://www.aoyama.ac.jp/en/admission/exchange/</t>
         </is>
       </c>
-      <c r="N117" s="2" t="inlineStr">
+      <c r="O117" s="2" t="inlineStr">
         <is>
           <t>exchange@aoyamagakuin.jp</t>
         </is>
@@ -8910,15 +9492,20 @@
       </c>
       <c r="L118" s="2" t="inlineStr">
         <is>
+          <t>GPA 요건 없음 · 교환학생 기숙사 보장 (국제교류회관, 전실 개인실) · 기숙사 비용: 입관비 33,000엔, 월 33,000엔 (광열비 별도)</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:웹 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M118" s="2" t="inlineStr">
+      <c r="N118" s="2" t="inlineStr">
         <is>
           <t>https://www.kokusai.fukuoka-u.ac.jp/inbound/exchange_fgn/</t>
         </is>
       </c>
-      <c r="N118" s="2" t="inlineStr">
+      <c r="O118" s="2" t="inlineStr">
         <is>
           <t>kokusai@adm.fukuoka-u.ac.jp</t>
         </is>
@@ -8982,15 +9569,20 @@
       </c>
       <c r="L119" s="2" t="inlineStr">
         <is>
+          <t>국제학생 기숙사(코다이라) 우선 배정, 1인실 공유형 · 장애 학생 합리적 편의 제공 · 일본 국립 사회과학 특화 대학</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
           <t>GPA:웹 · 어학:웹 · 수업언어:웹 · 전공:웹 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M119" s="2" t="inlineStr">
+      <c r="N119" s="2" t="inlineStr">
         <is>
           <t>https://international.hit-u.ac.jp/en/pros/exchange/</t>
         </is>
       </c>
-      <c r="N119" s="2" t="inlineStr">
+      <c r="O119" s="2" t="inlineStr">
         <is>
           <t>edu-gs.g2@ad.hit-u.ac.jp</t>
         </is>
@@ -9054,15 +9646,20 @@
       </c>
       <c r="L120" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · 기숙사 환영 미팅 제공 · 오리엔테이션 및 은행 계좌 개설 지원 · 마키구치 장학금 및 일본학 센터 장학금 제공</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M120" s="2" t="inlineStr">
+      <c r="N120" s="2" t="inlineStr">
         <is>
           <t>https://www.soka.ac.jp/en/admissions/exchange/</t>
         </is>
       </c>
-      <c r="N120" s="2" t="inlineStr">
+      <c r="O120" s="2" t="inlineStr">
         <is>
           <t>globalmobility@soka.ac.jp</t>
         </is>
@@ -9126,15 +9723,20 @@
       </c>
       <c r="L121" s="2" t="inlineStr">
         <is>
+          <t>주당 최소 10시간 수업 필수, 최대 20학점 등록 가능</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M121" s="2" t="inlineStr">
+      <c r="N121" s="2" t="inlineStr">
         <is>
           <t>https://en.ritsumei.ac.jp/skp/</t>
         </is>
       </c>
-      <c r="N121" s="2" t="inlineStr">
+      <c r="O121" s="2" t="inlineStr">
         <is>
           <t>skp@st.ritsumei.ac.jp</t>
         </is>
@@ -9198,15 +9800,20 @@
       </c>
       <c r="L122" s="2" t="inlineStr">
         <is>
+          <t>GPA 요건 없음 · 기숙사 신청 필요 · 도쿄 버디 프로그램 · 일본어 능력시험 지원금</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:웹 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M122" s="2" t="inlineStr">
+      <c r="N122" s="2" t="inlineStr">
         <is>
           <t>https://www.dokkyo.ac.jp/english/exchange/program/japanese.html</t>
         </is>
       </c>
-      <c r="N122" s="2" t="inlineStr">
+      <c r="O122" s="2" t="inlineStr">
         <is>
           <t>intl-inbound@ml.dokkyo.ac.jp</t>
         </is>
@@ -9270,15 +9877,20 @@
       </c>
       <c r="L123" s="2" t="inlineStr">
         <is>
+          <t>국제 기숙사 제공 · 국제 라운지(G-square) 운영 · 파트너 대학 266개교</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M123" s="2" t="inlineStr">
+      <c r="N123" s="2" t="inlineStr">
         <is>
           <t>https://www.chuo-u.ac.jp/english/admissions/exchange/semester-or-full-year/</t>
         </is>
       </c>
-      <c r="N123" s="2" t="inlineStr">
+      <c r="O123" s="2" t="inlineStr">
         <is>
           <t>exchange-grp@g.chuo-u.ac.jp</t>
         </is>
@@ -9342,15 +9954,20 @@
       </c>
       <c r="L124" s="2" t="inlineStr">
         <is>
+          <t>연 40명 수용 · 재정 증명서 필수</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:이메일문의 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M124" s="2" t="inlineStr">
+      <c r="N124" s="2" t="inlineStr">
         <is>
           <t>https://www.shinshu-u.ac.jp/institution/gec/en/prospective_students/gec_exchange_student_program/</t>
         </is>
       </c>
-      <c r="N124" s="2" t="inlineStr">
+      <c r="O124" s="2" t="inlineStr">
         <is>
           <t>gec_inbound@shinshu-u.ac.jp</t>
         </is>
@@ -9414,15 +10031,20 @@
       </c>
       <c r="L125" s="2" t="inlineStr">
         <is>
+          <t>사전 도착 정보·오리엔테이션 제공</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M125" s="2" t="inlineStr">
+      <c r="N125" s="2" t="inlineStr">
         <is>
           <t>https://nupace.iee.nagoya-u.ac.jp/en/</t>
         </is>
       </c>
-      <c r="N125" s="2" t="inlineStr">
+      <c r="O125" s="2" t="inlineStr">
         <is>
           <t>kusumoto.keiko.h7@f.mail.nagoya-u.ac.jp</t>
         </is>
@@ -9486,15 +10108,20 @@
       </c>
       <c r="L126" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · GPA 요건 없음 · 비학위 과정(특별청강생/특별연구생) 제공</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:이메일문의 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M126" s="2" t="inlineStr">
+      <c r="N126" s="2" t="inlineStr">
         <is>
           <t>https://www.kais.kyoto-u.ac.jp/english/international/exchange-programs/</t>
         </is>
       </c>
-      <c r="N126" s="2" t="inlineStr">
+      <c r="O126" s="2" t="inlineStr">
         <is>
           <t>[1] agri-kyoumu1@mail2.adm.kyoto-u.ac.jp, [2] agri-kyoumu2@mail2.adm.kyoto-u.ac.jp</t>
         </is>
@@ -9558,15 +10185,20 @@
       </c>
       <c r="L127" s="2" t="inlineStr">
         <is>
+          <t>교환학생 기숙사 제공 · 오리엔테이션 및 특별 수업 제공 · ISEP, UMAP 등 국제 교류 프로그램 운영</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:웹 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M127" s="2" t="inlineStr">
+      <c r="N127" s="2" t="inlineStr">
         <is>
           <t>https://www.toyo.ac.jp/academics/international-exchange/prospective/exchange_program/</t>
         </is>
       </c>
-      <c r="N127" s="2" t="inlineStr">
+      <c r="O127" s="2" t="inlineStr">
         <is>
           <t>mlies@toyo.jp</t>
         </is>
@@ -9630,15 +10262,20 @@
       </c>
       <c r="L128" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · 대학 기숙사 배정 · 장학금 신청 가능</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M128" s="2" t="inlineStr">
+      <c r="N128" s="2" t="inlineStr">
         <is>
           <t>https://www.global.hokudai.ac.jp/admissions/exchange-student-admissions/</t>
         </is>
       </c>
-      <c r="N128" s="2" t="inlineStr">
+      <c r="O128" s="2" t="inlineStr">
         <is>
           <t>hustep@oia.hokudai.ac.jp</t>
         </is>
@@ -9702,15 +10339,20 @@
       </c>
       <c r="L129" s="2" t="inlineStr">
         <is>
+          <t>교환학생 기숙사 보장 · 필수 보험 2종 가입 · 공학·자연과학 특성화</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:웹 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M129" s="2" t="inlineStr">
+      <c r="N129" s="2" t="inlineStr">
         <is>
           <t>https://www.insc.tohoku.ac.jp/english/exchange/</t>
         </is>
       </c>
-      <c r="N129" s="2" t="inlineStr">
+      <c r="O129" s="2" t="inlineStr">
         <is>
           <t>studyab@grp.tohoku.ac.jp</t>
         </is>
@@ -9774,15 +10416,20 @@
       </c>
       <c r="L130" s="2" t="inlineStr">
         <is>
+          <t>파트너 대학 협약 체결</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M130" s="2" t="inlineStr">
+      <c r="N130" s="2" t="inlineStr">
         <is>
           <t>https://www.isc.kyushu-u.ac.jp/intlweb/en/admission/exchangetop</t>
         </is>
       </c>
-      <c r="N130" s="2" t="inlineStr">
+      <c r="O130" s="2" t="inlineStr">
         <is>
           <t>exchange@jimu.kyushu-u.ac.jp</t>
         </is>
@@ -9846,15 +10493,20 @@
       </c>
       <c r="L131" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · 공인 어학성적 없이 지원 가능 · 카자흐스탄 최대 영어 강의 대학</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M131" s="2" t="inlineStr">
+      <c r="N131" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N131" s="2" t="inlineStr">
+      <c r="O131" s="2" t="inlineStr">
         <is>
           <t>incoming@kimep.kz</t>
         </is>
@@ -9918,15 +10570,20 @@
       </c>
       <c r="L132" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · VMU 기숙사에서 다른 국제학생과 생활 · VMU 멘토 프로그램 및 오리엔테이션 데이 제공 · 연간 2000명+ 80개국 이상 교환학생 수용</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
           <t>GPA:웹 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M132" s="2" t="inlineStr">
+      <c r="N132" s="2" t="inlineStr">
         <is>
           <t>https://www.vdu.lt/en/international-cooperation/for-students/vmu-bilateral-exchange-studies/incoming-exchange-students/</t>
         </is>
       </c>
-      <c r="N132" s="2" t="inlineStr">
+      <c r="O132" s="2" t="inlineStr">
         <is>
           <t>juste.lenortaviciene@vdu.lt</t>
         </is>
@@ -9990,15 +10647,20 @@
       </c>
       <c r="L133" s="2" t="inlineStr">
         <is>
+          <t>문화·스포츠·특별 관심사 그룹 활동 제공 · QS 세계 사립대 29위</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M133" s="2" t="inlineStr">
+      <c r="N133" s="2" t="inlineStr">
         <is>
           <t>https://studyinmexico.tec.mx/en</t>
         </is>
       </c>
-      <c r="N133" s="2" t="inlineStr">
+      <c r="O133" s="2" t="inlineStr">
         <is>
           <t>maria.alonsoji@tec.mx</t>
         </is>
@@ -10062,15 +10724,20 @@
       </c>
       <c r="L134" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · GPA 요건 없음 · 교내 기숙사 미보장·조기신청 필요 · 파트너 대학 300개교 이상</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M134" s="2" t="inlineStr">
+      <c r="N134" s="2" t="inlineStr">
         <is>
           <t>www.hanze.nl/exchange</t>
         </is>
       </c>
-      <c r="N134" s="2" t="inlineStr">
+      <c r="O134" s="2" t="inlineStr">
         <is>
           <t>exchange@org.hanze.nl</t>
         </is>
@@ -10134,15 +10801,20 @@
       </c>
       <c r="L135" s="2" t="inlineStr">
         <is>
+          <t>오리엔테이션 활동 제공 · 비EEA 학생 비자 지원 및 최소 20 ECTS 수강 필요 · 네덜란드 연구 중심 종합대학</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:웹 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M135" s="2" t="inlineStr">
+      <c r="N135" s="2" t="inlineStr">
         <is>
           <t>https://www.ru.nl/en/education/more-education-and-training/courses-for-exchange-students/for-partner-universities</t>
         </is>
       </c>
-      <c r="N135" s="2" t="inlineStr">
+      <c r="O135" s="2" t="inlineStr">
         <is>
           <t>studentexchange@ru.nl</t>
         </is>
@@ -10206,15 +10878,20 @@
       </c>
       <c r="L136" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · GPA 요건 없음 · 교내 기숙사 미보장·조기신청 필요 · Inclusive Mobility 지원 서비스 제공</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:웹 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M136" s="2" t="inlineStr">
+      <c r="N136" s="2" t="inlineStr">
         <is>
           <t>https://www.tilburguniversity.edu/education/exchange-programs</t>
         </is>
       </c>
-      <c r="N136" s="2" t="inlineStr">
+      <c r="O136" s="2" t="inlineStr">
         <is>
           <t>studyabroad@tilburguniversity.edu</t>
         </is>
@@ -10278,15 +10955,20 @@
       </c>
       <c r="L137" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · 교환학생 전용 오리엔테이션 주 제공 · 홈대학 학점 인정 가능 · 실용적 교육 중심 응용과학대학</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M137" s="2" t="inlineStr">
+      <c r="N137" s="2" t="inlineStr">
         <is>
           <t>https://www.nhlstenden.com/en/why-nhl-stenden/international-opportunities/exchange</t>
         </is>
       </c>
-      <c r="N137" s="2" t="inlineStr">
+      <c r="O137" s="2" t="inlineStr">
         <is>
           <t>io@nhlstenden.com</t>
         </is>
@@ -10350,15 +11032,20 @@
       </c>
       <c r="L138" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · 비영어권이지만 전 과정 영어 수업</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M138" s="2" t="inlineStr">
+      <c r="N138" s="2" t="inlineStr">
         <is>
           <t>Exchange programmes | Fontys</t>
         </is>
       </c>
-      <c r="N138" s="2" t="inlineStr">
+      <c r="O138" s="2" t="inlineStr">
         <is>
           <t>studyabroad@fontys.nl</t>
         </is>
@@ -10425,17 +11112,22 @@
       </c>
       <c r="L139" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · 연 650명+ 교환학생 수용 · 경영 트리플크라운 인증</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M139" s="2" t="inlineStr">
+      <c r="N139" s="2" t="inlineStr">
         <is>
           <t>1. School of Business and Economics: https://www.maastrichtuniversity.nl/education/exchange/sbe
  2. Univeristy College Maastricht: www.ucm.nl/exchange 
  3. Maastricht Science Programme: https://www.maastrichtuniversity.nl/education/exchange/faculty-science-and-engineering/msp-exchange-programme</t>
         </is>
       </c>
-      <c r="N139" s="2" t="inlineStr">
+      <c r="O139" s="2" t="inlineStr">
         <is>
           <t>1. School of Business and Economics: incoming-sbe@maastrichtuniversity.nl
  2. Univeristy College Maastricht: ucm-iro-incoming@maastrichtuniversity.nl
@@ -10501,15 +11193,20 @@
       </c>
       <c r="L140" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · 비영어권이지만 전 과정 영어 수업 · 수강 신청 시 최소/최대 인원 제한으로 캠퍼스·강의 변경 가능성 있음 · 응용과학대학(Holland Applied Sciences)</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M140" s="2" t="inlineStr">
+      <c r="N140" s="2" t="inlineStr">
         <is>
           <t>For this year: https://www.inholland.nl/inhollandcom/exchange/ects-course-guides/course-catalogue-2025-2026/</t>
         </is>
       </c>
-      <c r="N140" s="2" t="inlineStr">
+      <c r="O140" s="2" t="inlineStr">
         <is>
           <t>incoming@inholland.nl</t>
         </is>
@@ -10573,15 +11270,20 @@
       </c>
       <c r="L141" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · 비영어권이지만 전 과정 영어 수업 · 블록제 운영(8주 수업+1주 시험), 1블록 12~16EC 권장 · 경영·경제 특성화 대학</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M141" s="2" t="inlineStr">
+      <c r="N141" s="2" t="inlineStr">
         <is>
           <t>https://www.eur.nl/en/ese/exchange/visiting-students</t>
         </is>
       </c>
-      <c r="N141" s="2" t="inlineStr">
+      <c r="O141" s="2" t="inlineStr">
         <is>
           <t>incoming.exchange@ese.eur.nl</t>
         </is>
@@ -10645,15 +11347,20 @@
       </c>
       <c r="L142" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · 비영어권이지만 전 과정 영어 수업 · 실용학문 중심 대학</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M142" s="2" t="inlineStr">
+      <c r="N142" s="2" t="inlineStr">
         <is>
           <t>https://www.internationalhu.com/programmes#/typeofprogramme=a90b3191-d174-4155-b7c9-7b3e39665cc3</t>
         </is>
       </c>
-      <c r="N142" s="2" t="inlineStr">
+      <c r="O142" s="2" t="inlineStr">
         <is>
           <t>exchange@hu.nl</t>
         </is>
@@ -10717,15 +11424,20 @@
       </c>
       <c r="L143" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · GPA 요건 없음 · 연 1,100개 이상 영어 강의 제공 · 홈 대학 공식 추천 필요</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M143" s="2" t="inlineStr">
+      <c r="N143" s="2" t="inlineStr">
         <is>
           <t>https://vu.nl/en/education/exchange</t>
         </is>
       </c>
-      <c r="N143" s="2" t="inlineStr">
+      <c r="O143" s="2" t="inlineStr">
         <is>
           <t>incoming@vu.nl</t>
         </is>
@@ -10789,15 +11501,20 @@
       </c>
       <c r="L144" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · 국제 교환 코디네이터 지원 · 네덜란드 최상위권 종합대</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M144" s="2" t="inlineStr">
+      <c r="N144" s="2" t="inlineStr">
         <is>
           <t>https://www.student.universiteitleiden.nl/en/vr/incoming-exchange?cf=university&amp;cd=guest</t>
         </is>
       </c>
-      <c r="N144" s="2" t="inlineStr">
+      <c r="O144" s="2" t="inlineStr">
         <is>
           <t>exchange@sea.leidenuniv.nl</t>
         </is>
@@ -10861,15 +11578,20 @@
       </c>
       <c r="L145" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · 비영어권이지만 전 과정 영어 수업 · 교환학생 기숙사 우선 배정 · 가을학기 8월 10일 시작</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M145" s="2" t="inlineStr">
+      <c r="N145" s="2" t="inlineStr">
         <is>
           <t>https://www.uio.no/english/studies/admission/exchange/</t>
         </is>
       </c>
-      <c r="N145" s="2" t="inlineStr">
+      <c r="O145" s="2" t="inlineStr">
         <is>
           <t>studieinfo@mn.uio.no</t>
         </is>
@@ -10933,15 +11655,20 @@
       </c>
       <c r="L146" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · 교환학생 기숙사 보장</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M146" s="2" t="inlineStr">
+      <c r="N146" s="2" t="inlineStr">
         <is>
           <t>https://www4.uib.no/en/studies/for-exchange-students-at-uib/how-to-nominate-students-for-exchange-to-uib</t>
         </is>
       </c>
-      <c r="N146" s="2" t="inlineStr">
+      <c r="O146" s="2" t="inlineStr">
         <is>
           <t>incoming@uib.no.</t>
         </is>
@@ -11005,15 +11732,20 @@
       </c>
       <c r="L147" s="2" t="inlineStr">
         <is>
+          <t>파트너 300개교+ · 교환학생 장학금 제공 · QS 페루 1위 종합대</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M147" s="2" t="inlineStr">
+      <c r="N147" s="2" t="inlineStr">
         <is>
           <t>https://internacionalizacion.pucp.edu.pe/</t>
         </is>
       </c>
-      <c r="N147" s="2" t="inlineStr">
+      <c r="O147" s="2" t="inlineStr">
         <is>
           <t>exchange@pucp.edu.pe</t>
         </is>
@@ -11077,15 +11809,20 @@
       </c>
       <c r="L148" s="2" t="inlineStr">
         <is>
+          <t>GPA 요건 없음 · 오리엔테이션 주간 및 버디 프로그램 제공 · 비파트너 대학생도 1학기 또는 1년 자유수강 가능 · 폴란드 최고 경제·경영 대학</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M148" s="2" t="inlineStr">
+      <c r="N148" s="2" t="inlineStr">
         <is>
           <t>https://www.sgh.waw.pl/en/student/international-programs-incoming-students</t>
         </is>
       </c>
-      <c r="N148" s="2" t="inlineStr">
+      <c r="O148" s="2" t="inlineStr">
         <is>
           <t>mkomore@sgh.waw.pl</t>
         </is>
@@ -11149,15 +11886,20 @@
       </c>
       <c r="L149" s="2" t="inlineStr">
         <is>
+          <t>1학기 30~36 ECTS 권장, 최대 36 ECTS 선택 가능 · 공학·기술 특성화 대학</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M149" s="2" t="inlineStr">
+      <c r="N149" s="2" t="inlineStr">
         <is>
           <t>https://aai.tecnico.ulisboa.pt/en/nucleo-de-mobilidade-e-parcerias-internacionais/do-mundo-para-o-tecnico/candidaturas-in/</t>
         </is>
       </c>
-      <c r="N149" s="2" t="inlineStr">
+      <c r="O149" s="2" t="inlineStr">
         <is>
           <t>outsideeurope@tecnico.ulisboa.pt</t>
         </is>
@@ -11221,15 +11963,20 @@
       </c>
       <c r="L150" s="2" t="inlineStr">
         <is>
+          <t>공인 어학성적 없이 지원 가능 · 교내 기숙사 미보장·조기신청 필요 · 전담 오리엔테이션·학생 지원 서비스 · 연 200명+ 교환학생 수용</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:웹 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M150" s="2" t="inlineStr">
+      <c r="N150" s="2" t="inlineStr">
         <is>
           <t>https://www.sutd.edu.sg/campus-life/global-experience-and-exchange/student-exchange/inbound/inbound-exchange/</t>
         </is>
       </c>
-      <c r="N150" s="2" t="inlineStr">
+      <c r="O150" s="2" t="inlineStr">
         <is>
           <t>global@sutd.edu.sg</t>
         </is>
@@ -11293,16 +12040,21 @@
       </c>
       <c r="L151" s="2" t="inlineStr">
         <is>
+          <t>기숙사 신청 필요 · 교환학생 포털·오리엔테이션 제공 · 파트너 350+개교 · 장학금 미제공</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
           <t>GPA:웹 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M151" s="2" t="inlineStr">
+      <c r="N151" s="2" t="inlineStr">
         <is>
           <t>1. https://gem.ntu.edu.sg/index.cfm?FuseAction=Programs.ViewProgramAngular&amp;id=10006
  2. https://www.ntu.edu.sg/education/student-exchanges/exchange-programmes/inbound-programmes#Content_C113_Col00</t>
         </is>
       </c>
-      <c r="N151" s="2" t="inlineStr">
+      <c r="O151" s="2" t="inlineStr">
         <is>
           <t>GEM-Trailblazer@ntu.edu.sg</t>
         </is>
@@ -11366,15 +12118,20 @@
       </c>
       <c r="L152" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · GPA 요건 없음 · 교내 기숙사 미보장·개인 주거 선택 · 오리엔테이션(리틀 인디아·차이나타운 방문) 및 글로벌 네트워크 기회</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M152" s="2" t="inlineStr">
+      <c r="N152" s="2" t="inlineStr">
         <is>
           <t>https://geo.smu.edu.sg/study-in-smu/international-student-exchange-programme</t>
         </is>
       </c>
-      <c r="N152" s="2" t="inlineStr">
+      <c r="O152" s="2" t="inlineStr">
         <is>
           <t>isep.inbound@smu.edu.sg</t>
         </is>
@@ -11438,15 +12195,20 @@
       </c>
       <c r="L153" s="2" t="inlineStr">
         <is>
+          <t>GPA 요건 없음 · 오리엔테이션 제공 · 스페인어 무료 수강(교재비 €60), 영어 강의 제한적</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M153" s="2" t="inlineStr">
+      <c r="N153" s="2" t="inlineStr">
         <is>
           <t>https://sri.ua.es/en/movilidad/incoming-students.html</t>
         </is>
       </c>
-      <c r="N153" s="2" t="inlineStr">
+      <c r="O153" s="2" t="inlineStr">
         <is>
           <t>globalmobility@ua.es</t>
         </is>
@@ -11510,15 +12272,20 @@
       </c>
       <c r="L154" s="2" t="inlineStr">
         <is>
+          <t>GPA 요건 없음 · 기숙사 미보장·조기신청 필요 · 멘토 프로그램 제공 · 스페인어 필수·스페인어 과정 제공</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M154" s="2" t="inlineStr">
+      <c r="N154" s="2" t="inlineStr">
         <is>
           <t>https://www.upv.es/entidades/OPII/infoweb/pi/info/818854normali.html</t>
         </is>
       </c>
-      <c r="N154" s="2" t="inlineStr">
+      <c r="O154" s="2" t="inlineStr">
         <is>
           <t>macaball@upv.es</t>
         </is>
@@ -11582,15 +12349,20 @@
       </c>
       <c r="L155" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · 교환학생 기숙사 신청 가능 · 연 2,000명+ 교환학생 수용 · €4.02 보험비 납부 필수</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M155" s="2" t="inlineStr">
+      <c r="N155" s="2" t="inlineStr">
         <is>
           <t>https://www.uab.cat/web/mobility-international-exchange/mobility-international-exchange-programmes/erasmus-uab-exchange-in/erasmus-exchange-studies-incoming-1345895725317.html</t>
         </is>
       </c>
-      <c r="N155" s="2" t="inlineStr">
+      <c r="O155" s="2" t="inlineStr">
         <is>
           <t>uab.exchange.programme@uab.cat</t>
         </is>
@@ -11654,15 +12426,20 @@
       </c>
       <c r="L156" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · 공인 어학성적 없이 지원 가능 · 모든 등록 과목 출석 필수 · 경영·법학 분야 트리플크라운 인증</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M156" s="2" t="inlineStr">
+      <c r="N156" s="2" t="inlineStr">
         <is>
           <t>https://www.esade.edu/en</t>
         </is>
       </c>
-      <c r="N156" s="2" t="inlineStr">
+      <c r="O156" s="2" t="inlineStr">
         <is>
           <t>maria.gambin@esade.edu</t>
         </is>
@@ -11726,15 +12503,20 @@
       </c>
       <c r="L157" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · 공인 어학성적 없이 지원 가능 · 스페인 북부 명문 사립대</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M157" s="2" t="inlineStr">
+      <c r="N157" s="2" t="inlineStr">
         <is>
           <t>https://www.deusto.es/es/inicio/internacional/estudiantes-internacionales?_gl=1*oaveu4*_up*MQ..*_ga*NzU1Njg5MzgzLjE3NjU1MzcyNDc.*_ga_ZVJ1XGGKPL*czE3NjU1MzcyNDckbzEkZzEkdDE3NjU1MzcyNDkkajU4JGwwJGgw</t>
         </is>
       </c>
-      <c r="N157" s="2" t="inlineStr">
+      <c r="O157" s="2" t="inlineStr">
         <is>
           <t>incoming@deusto.es</t>
         </is>
@@ -11798,15 +12580,20 @@
       </c>
       <c r="L158" s="2" t="inlineStr">
         <is>
+          <t>버디 프로그램 운영 · 연 수백 명 교환학생 수용 · 무료 스페인어 과정 제공 · 의학·경영·공학 특성화</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M158" s="2" t="inlineStr">
+      <c r="N158" s="2" t="inlineStr">
         <is>
           <t>https://www.unav.edu/estudiantes/programas-de-intercambio/incoming</t>
         </is>
       </c>
-      <c r="N158" s="2" t="inlineStr">
+      <c r="O158" s="2" t="inlineStr">
         <is>
           <t>exchangeunav@unav.es</t>
         </is>
@@ -11870,15 +12657,20 @@
       </c>
       <c r="L159" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · 파트너 200개교 이상 · 2026년 2월 업데이트 예정 · 경영 트리플크라운 인증</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M159" s="2" t="inlineStr">
+      <c r="N159" s="2" t="inlineStr">
         <is>
           <t>https://www.ie.edu/university/ieu-experience/international-experience/</t>
         </is>
       </c>
-      <c r="N159" s="2" t="inlineStr">
+      <c r="O159" s="2" t="inlineStr">
         <is>
           <t>geo.incoming@ie.edu</t>
         </is>
@@ -11942,15 +12734,20 @@
       </c>
       <c r="L160" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · 1학기 30학점 권장, 6개 과목 선호순 신청 · 공학·IT·에너지 기술 특성화</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M160" s="2" t="inlineStr">
+      <c r="N160" s="2" t="inlineStr">
         <is>
           <t>https://www.hh.se/english/education/apply-to-halmstad-university/apply-as-exchange-student.html</t>
         </is>
       </c>
-      <c r="N160" s="2" t="inlineStr">
+      <c r="O160" s="2" t="inlineStr">
         <is>
           <t>helpdesk.exchange@hh.se</t>
         </is>
@@ -12014,15 +12811,20 @@
       </c>
       <c r="L161" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · GPA 요건 없음 · 트라이메스터제 운영(학기당 15주 내외)</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M161" s="2" t="inlineStr">
+      <c r="N161" s="2" t="inlineStr">
         <is>
           <t>https://liu.se/en/article/application-procedure-faculty-of-arts-and-sciences</t>
         </is>
       </c>
-      <c r="N161" s="2" t="inlineStr">
+      <c r="O161" s="2" t="inlineStr">
         <is>
           <t>international@ffk.liu.se</t>
         </is>
@@ -12086,15 +12888,20 @@
       </c>
       <c r="L162" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · GPA 요건 없음 · 드롭인 서비스 및 온라인 상담 제공 · 900개 이상 교환학생 과정 제공</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M162" s="2" t="inlineStr">
+      <c r="N162" s="2" t="inlineStr">
         <is>
           <t>https://www.uu.se/en/study/exchange-studies</t>
         </is>
       </c>
-      <c r="N162" s="2" t="inlineStr">
+      <c r="O162" s="2" t="inlineStr">
         <is>
           <t>mobility@uu.se</t>
         </is>
@@ -12158,15 +12965,20 @@
       </c>
       <c r="L163" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · 트라이메스터제 운영</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M163" s="2" t="inlineStr">
+      <c r="N163" s="2" t="inlineStr">
         <is>
           <t>https://lnu.se/en/education/exchange-studies/</t>
         </is>
       </c>
-      <c r="N163" s="2" t="inlineStr">
+      <c r="O163" s="2" t="inlineStr">
         <is>
           <t>inexchange@lnu.se</t>
         </is>
@@ -12230,15 +13042,20 @@
       </c>
       <c r="L164" s="2" t="inlineStr">
         <is>
+          <t>ESN FHNW 학생 조직 지원 · 다양한 캠퍼스·전공 과목 선택 가능 · 응용과학·예술 분야 특성화 대학</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M164" s="2" t="inlineStr">
+      <c r="N164" s="2" t="inlineStr">
         <is>
           <t>https://www.fhnw.ch/en/degree-programmes/business/international-experience/offers-for-incoming-students</t>
         </is>
       </c>
-      <c r="N164" s="2" t="inlineStr">
+      <c r="O164" s="2" t="inlineStr">
         <is>
           <t>io.business@fhnw.ch</t>
         </is>
@@ -12302,15 +13119,20 @@
       </c>
       <c r="L165" s="2" t="inlineStr">
         <is>
+          <t>국제학생 전담 학업 지원 코디네이터 및 오리엔테이션 주 제공 · 교통카드(할프탁스·세븐25) 구매 권장 및 ECTS 초과 신청 권장 · 경영 트리플크라운 인증(AACSB·EQUIS·AMBA)</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M165" s="2" t="inlineStr">
+      <c r="N165" s="2" t="inlineStr">
         <is>
           <t>https://www.zhaw.ch/en/sml/study/international/incoming-students</t>
         </is>
       </c>
-      <c r="N165" s="2" t="inlineStr">
+      <c r="O165" s="2" t="inlineStr">
         <is>
           <t>incoming.area1.sml@zhaw.ch</t>
         </is>
@@ -12374,15 +13196,20 @@
       </c>
       <c r="L166" s="2" t="inlineStr">
         <is>
+          <t>교환학생 권장 학점 20-25 ECTS</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:시트 · 수업언어:웹 · 전공:웹 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M166" s="2" t="inlineStr">
+      <c r="N166" s="2" t="inlineStr">
         <is>
           <t>https://www.unibe.ch/studies/mobility/incoming/worldwide/worldwide_exchange/application/index_eng.html; incoming.unibe.ch</t>
         </is>
       </c>
-      <c r="N166" s="2" t="inlineStr">
+      <c r="O166" s="2" t="inlineStr">
         <is>
           <t>worldwide.int@unibe.ch</t>
         </is>
@@ -12446,15 +13273,20 @@
       </c>
       <c r="L167" s="2" t="inlineStr">
         <is>
+          <t>공학·경영 특성화</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M167" s="2" t="inlineStr">
+      <c r="N167" s="2" t="inlineStr">
         <is>
           <t>https://oia.fcu.edu.tw/overseas-students/inbound_international/</t>
         </is>
       </c>
-      <c r="N167" s="2" t="inlineStr">
+      <c r="O167" s="2" t="inlineStr">
         <is>
           <t>oia_in@o365.fcu.edu.tw</t>
         </is>
@@ -12518,15 +13350,20 @@
       </c>
       <c r="L168" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · GPA 요건 없음 · 교내 기숙사 미보장·자체 주거 확보 필요</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M168" s="2" t="inlineStr">
+      <c r="N168" s="2" t="inlineStr">
         <is>
           <t>https://oia.nsysu.edu.tw/p/412-1308-20581.php?Lang=en</t>
         </is>
       </c>
-      <c r="N168" s="2" t="inlineStr">
+      <c r="O168" s="2" t="inlineStr">
         <is>
           <t>oia.exchange@mail.nsysu.edu.tw</t>
         </is>
@@ -12590,15 +13427,20 @@
       </c>
       <c r="L169" s="2" t="inlineStr">
         <is>
+          <t>공학·반도체 분야 특성화</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M169" s="2" t="inlineStr">
+      <c r="N169" s="2" t="inlineStr">
         <is>
           <t>https://oga.site.nthu.edu.tw/p/412-1524-18681.php?Lang=en</t>
         </is>
       </c>
-      <c r="N169" s="2" t="inlineStr">
+      <c r="O169" s="2" t="inlineStr">
         <is>
           <t>cyuliu@mx.nthu.edu.tw</t>
         </is>
@@ -12662,15 +13504,20 @@
       </c>
       <c r="L170" s="2" t="inlineStr">
         <is>
+          <t>9학점(학부)/2과목(대학원) 최소 수강, 전체 대학 과목 선택 가능 · 공학·컴퓨터과학 특성화</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M170" s="2" t="inlineStr">
+      <c r="N170" s="2" t="inlineStr">
         <is>
           <t>https://oia.nycu.edu.tw/oia/en/app/artwebsite/view?module=artwebsite&amp;id=821&amp;serno=a277c341-8d25-4a51-8495-58d1d58bbc5d</t>
         </is>
       </c>
-      <c r="N170" s="2" t="inlineStr">
+      <c r="O170" s="2" t="inlineStr">
         <is>
           <t>ex-in@nycu.edu.tw</t>
         </is>
@@ -12734,15 +13581,20 @@
       </c>
       <c r="L171" s="2" t="inlineStr">
         <is>
+          <t>Buddy Program (학우 멘토링) 운영 · 교환학생 장학금 다수 운영 (傑出交換生獎學金 등)</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M171" s="2" t="inlineStr">
+      <c r="N171" s="2" t="inlineStr">
         <is>
           <t>https://oic.nccu.edu.tw/</t>
         </is>
       </c>
-      <c r="N171" s="2" t="inlineStr">
+      <c r="O171" s="2" t="inlineStr">
         <is>
           <t>ykuo088@g.nccu.edu.tw</t>
         </is>
@@ -12806,15 +13658,20 @@
       </c>
       <c r="L172" s="2" t="inlineStr">
         <is>
+          <t>국제학생 자원봉사자(버디) 지원 · 환영 활동 필수 참석(결석 시 입학 취소) · QS 세계대학랭킹 50위권 종합대</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M172" s="2" t="inlineStr">
+      <c r="N172" s="2" t="inlineStr">
         <is>
           <t>https://isss.ntu.edu.tw/exchange-visiting-students/overview/</t>
         </is>
       </c>
-      <c r="N172" s="2" t="inlineStr">
+      <c r="O172" s="2" t="inlineStr">
         <is>
           <t>intstudent@ntu.edu.tw</t>
         </is>
@@ -12878,15 +13735,20 @@
       </c>
       <c r="L173" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · GPA 요건 없음 · 기숙사 시설 제공 · 영어 강의 제공</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:웹 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M173" s="2" t="inlineStr">
+      <c r="N173" s="2" t="inlineStr">
         <is>
           <t>https://en.mfu.ac.th/en-mfu-links/mfu-student-exchange-programme-inbound-students.html</t>
         </is>
       </c>
-      <c r="N173" s="2" t="inlineStr">
+      <c r="O173" s="2" t="inlineStr">
         <is>
           <t>global@mfu.ac.th</t>
         </is>
@@ -12950,15 +13812,20 @@
       </c>
       <c r="L174" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · Chula Link 장학금(2026학년도 1학기 국제학생 대상) · 태국 최고 명문 종합대학</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M174" s="2" t="inlineStr">
+      <c r="N174" s="2" t="inlineStr">
         <is>
           <t>https://www.inter.chula.ac.th/exchange/</t>
         </is>
       </c>
-      <c r="N174" s="2" t="inlineStr">
+      <c r="O174" s="2" t="inlineStr">
         <is>
           <t>cuexchange.inbound@chula.ac.th</t>
         </is>
@@ -13022,15 +13889,20 @@
       </c>
       <c r="L175" s="2" t="inlineStr">
         <is>
+          <t>공학 및 과학기술 특성화</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M175" s="2" t="inlineStr">
+      <c r="N175" s="2" t="inlineStr">
         <is>
           <t>https://eds.kmutt.ac.th/curriculum/courses-offered/fsci/</t>
         </is>
       </c>
-      <c r="N175" s="2" t="inlineStr">
+      <c r="O175" s="2" t="inlineStr">
         <is>
           <t>nitchakarn.jer@mail.kmutt.ac.th</t>
         </is>
@@ -13094,15 +13966,20 @@
       </c>
       <c r="L176" s="2" t="inlineStr">
         <is>
+          <t>GPA 요건 없음 · 교환학생 기숙사 예약 가능 · UNI 101 오리엔테이션·터키어 지원·국제우정의 날 행사 · UNI 101 9월·10월 세션 필수 참여</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M176" s="2" t="inlineStr">
+      <c r="N176" s="2" t="inlineStr">
         <is>
           <t>https://www.hacettepe.edu.tr/international/international_students</t>
         </is>
       </c>
-      <c r="N176" s="2" t="inlineStr">
+      <c r="O176" s="2" t="inlineStr">
         <is>
           <t>uob@hacettepe.edu.tr</t>
         </is>
@@ -13166,15 +14043,20 @@
       </c>
       <c r="L177" s="2" t="inlineStr">
         <is>
+          <t>교환학생 오리엔테이션 및 버디 프로그램 운영 · 니가타대 여름 프로그램 무료 수강 가능 · 터키 최초·최대 국립 종합대학</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M177" s="2" t="inlineStr">
+      <c r="N177" s="2" t="inlineStr">
         <is>
           <t>https://iso.ankara.edu.tr/</t>
         </is>
       </c>
-      <c r="N177" s="2" t="inlineStr">
+      <c r="O177" s="2" t="inlineStr">
         <is>
           <t>iso@ankara.edu.tr</t>
         </is>
@@ -13238,15 +14120,20 @@
       </c>
       <c r="L178" s="2" t="inlineStr">
         <is>
+          <t>공인 어학성적 없이 지원 가능 · 공학 특성화</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M178" s="2" t="inlineStr">
+      <c r="N178" s="2" t="inlineStr">
         <is>
           <t>https://global.itu.edu.tr/students/international-programs/global-exchange-students</t>
         </is>
       </c>
-      <c r="N178" s="2" t="inlineStr">
+      <c r="O178" s="2" t="inlineStr">
         <is>
           <t>globalexchange@itu.edu.tr</t>
         </is>
@@ -13310,15 +14197,20 @@
       </c>
       <c r="L179" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · 터키 최고 명문 종합대</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:이메일문의 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M179" s="2" t="inlineStr">
+      <c r="N179" s="2" t="inlineStr">
         <is>
           <t>https://intl.bogazici.edu.tr</t>
         </is>
       </c>
-      <c r="N179" s="2" t="inlineStr">
+      <c r="O179" s="2" t="inlineStr">
         <is>
           <t>exchange-incoming@bogazici.edu.tr</t>
         </is>
@@ -13382,15 +14274,20 @@
       </c>
       <c r="L180" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · 기숙사 신청 가능(풀년·학기별 옵션) · 오리엔테이션 주 제공(학기별 1주) · 연 200명+ 교환학생 수용(학기별 100명+)</t>
+        </is>
+      </c>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M180" s="2" t="inlineStr">
+      <c r="N180" s="2" t="inlineStr">
         <is>
           <t>https://www.soas.ac.uk/study/study-abroad-and-exchange/inbound-students-study-abroad</t>
         </is>
       </c>
-      <c r="N180" s="2" t="inlineStr">
+      <c r="O180" s="2" t="inlineStr">
         <is>
           <t>studyabroad@soas.ac.uk</t>
         </is>
@@ -13454,15 +14351,20 @@
       </c>
       <c r="L181" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · 기숙사 제공·신청 절차 안내 · 비자 신청 시 CAS 발급 필요 · 영국 연구 중심 종합대학</t>
+        </is>
+      </c>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
           <t>GPA:웹 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M181" s="2" t="inlineStr">
+      <c r="N181" s="2" t="inlineStr">
         <is>
           <t>https://le.ac.uk/cite/study-abroad-unit/incoming</t>
         </is>
       </c>
-      <c r="N181" s="2" t="inlineStr">
+      <c r="O181" s="2" t="inlineStr">
         <is>
           <t>studyabroad@le.ac.uk</t>
         </is>
@@ -13526,15 +14428,20 @@
       </c>
       <c r="L182" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · 여름학기 프로그램 운영 · 러셀 그룹 소속 종합대</t>
+        </is>
+      </c>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M182" s="2" t="inlineStr">
+      <c r="N182" s="2" t="inlineStr">
         <is>
           <t>https://sheffield.ac.uk/globalopps</t>
         </is>
       </c>
-      <c r="N182" s="2" t="inlineStr">
+      <c r="O182" s="2" t="inlineStr">
         <is>
           <t>globalopps@sheffield.ac.uk</t>
         </is>
@@ -13598,15 +14505,20 @@
       </c>
       <c r="L183" s="2" t="inlineStr">
         <is>
+          <t>교내 기숙사 제공 · 학업·행정·복지 지원 제공 · 1학기만 수강 시 시험 대체 과제 가능 · QS 2025 세계 200위권 종합대</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M183" s="2" t="inlineStr">
+      <c r="N183" s="2" t="inlineStr">
         <is>
           <t>https://studyabroad.reading.ac.uk/incoming/</t>
         </is>
       </c>
-      <c r="N183" s="2" t="inlineStr">
+      <c r="O183" s="2" t="inlineStr">
         <is>
           <t>studyabroad@reading.ac.uk</t>
         </is>
@@ -13670,15 +14582,20 @@
       </c>
       <c r="L184" s="2" t="inlineStr">
         <is>
+          <t>기숙사 보장·조기신청 필요 · 전담 인바운드 팀·온라인 상담 · 30+ 학과 모듈 선택 가능 · 러셀 그룹 소속·경영 트리플크라운 인증</t>
+        </is>
+      </c>
+      <c r="M184" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M184" s="2" t="inlineStr">
+      <c r="N184" s="2" t="inlineStr">
         <is>
           <t>https://www.exeter.ac.uk/study/studyabroadprogrammes/</t>
         </is>
       </c>
-      <c r="N184" s="2" t="inlineStr">
+      <c r="O184" s="2" t="inlineStr">
         <is>
           <t>inbound@exeter.ac.uk</t>
         </is>
@@ -13742,15 +14659,20 @@
       </c>
       <c r="L185" s="2" t="inlineStr">
         <is>
+          <t>GPA 요건 없음 · 기숙사 계약 시 전체 학년 기간 의무 · 트라이메스터제 운영(9월-6월), 여름학기 단독 수강 불가 · 영국 연구 중심 공립대</t>
+        </is>
+      </c>
+      <c r="M185" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M185" s="2" t="inlineStr">
+      <c r="N185" s="2" t="inlineStr">
         <is>
           <t>https://www.essex.ac.uk/study-abroad/incoming-students/exchange-programme</t>
         </is>
       </c>
-      <c r="N185" s="2" t="inlineStr">
+      <c r="O185" s="2" t="inlineStr">
         <is>
           <t>incomingexchange@essex.ac.uk</t>
         </is>
@@ -13814,15 +14736,20 @@
       </c>
       <c r="L186" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · 국제 기회 팀 지원 · 150개국 이상 교환 프로그램 · 28일 이상 해외 인턴십 필수</t>
+        </is>
+      </c>
+      <c r="M186" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M186" s="2" t="inlineStr">
+      <c r="N186" s="2" t="inlineStr">
         <is>
           <t>https://www.bradford.ac.uk/study/abroad/</t>
         </is>
       </c>
-      <c r="N186" s="2" t="inlineStr">
+      <c r="O186" s="2" t="inlineStr">
         <is>
           <t>studyabroad@bradford.ac.uk</t>
         </is>
@@ -13886,15 +14813,20 @@
       </c>
       <c r="L187" s="2" t="inlineStr">
         <is>
+          <t>트라이메스터제(9월·1월 입학 가능) · QS 최상위권 종합대</t>
+        </is>
+      </c>
+      <c r="M187" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M187" s="2" t="inlineStr">
+      <c r="N187" s="2" t="inlineStr">
         <is>
           <t>https://www.bristol.ac.uk/centre-for-study-abroad/inbound/study-abroad-programmes-at-bristol/study-abroad-general-pathway/</t>
         </is>
       </c>
-      <c r="N187" s="2" t="inlineStr">
+      <c r="O187" s="2" t="inlineStr">
         <is>
           <t>cfsa-inbound@bristol.ac.uk</t>
         </is>
@@ -13958,15 +14890,20 @@
       </c>
       <c r="L188" s="2" t="inlineStr">
         <is>
+          <t>연 200명+ 교환학생 수용 · 1학기 또는 2학기(1년) 선택 가능</t>
+        </is>
+      </c>
+      <c r="M188" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M188" s="2" t="inlineStr">
+      <c r="N188" s="2" t="inlineStr">
         <is>
           <t>https://www.yorksj.ac.uk/international/study-abroad-and-exchange/study-abroad-at-york-st-john</t>
         </is>
       </c>
-      <c r="N188" s="2" t="inlineStr">
+      <c r="O188" s="2" t="inlineStr">
         <is>
           <t>studyabroad@yorksj.ac.uk</t>
         </is>
@@ -14030,15 +14967,20 @@
       </c>
       <c r="L189" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · 교환학생 기숙사 보장 · 학기제(1학기/1년) 선택 가능 · QS 세계 100위권 종합대</t>
+        </is>
+      </c>
+      <c r="M189" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M189" s="2" t="inlineStr">
+      <c r="N189" s="2" t="inlineStr">
         <is>
           <t>https://www.leeds.ac.uk/international-exchange-and-study-abroad</t>
         </is>
       </c>
-      <c r="N189" s="2" t="inlineStr">
+      <c r="O189" s="2" t="inlineStr">
         <is>
           <t>studyabroad@leeds.ac.uk</t>
         </is>
@@ -14102,15 +15044,20 @@
       </c>
       <c r="L190" s="2" t="inlineStr">
         <is>
+          <t>공인 어학성적 없이 지원 가능 · 공항 환영 서비스·국제학생 오리엔테이션 제공 · 영국 남서부 브리스톨 소재 종합대</t>
+        </is>
+      </c>
+      <c r="M190" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M190" s="2" t="inlineStr">
+      <c r="N190" s="2" t="inlineStr">
         <is>
           <t>https://www.uwe.ac.uk/study/international-study-exchange/apply-for-an-exchange</t>
         </is>
       </c>
-      <c r="N190" s="2" t="inlineStr">
+      <c r="O190" s="2" t="inlineStr">
         <is>
           <t>studyabroad@uwe.ac.uk</t>
         </is>
@@ -14174,15 +15121,20 @@
       </c>
       <c r="L191" s="2" t="inlineStr">
         <is>
+          <t>교환학생 기숙사 보장 · 전담 글로벌 기회 팀·개인 칼리지 튜터 지원 · 비유럽 13개국 50+ 대학 파트너 · 120학점(6과목) 이수, 최대 3개 학과 선택</t>
+        </is>
+      </c>
+      <c r="M191" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:웹 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M191" s="2" t="inlineStr">
+      <c r="N191" s="2" t="inlineStr">
         <is>
           <t>https://www.durham.ac.uk/global-durham/global-opportunities/incoming-opportunities/non-european-incoming-exchange/</t>
         </is>
       </c>
-      <c r="N191" s="2" t="inlineStr">
+      <c r="O191" s="2" t="inlineStr">
         <is>
           <t>incoming.exchange@durham.ac.uk</t>
         </is>
@@ -14246,15 +15198,20 @@
       </c>
       <c r="L192" s="2" t="inlineStr">
         <is>
+          <t>교내 기숙사 옵션 제공 · 전 세계 100개 대학 파트너십 · 의학·치의학·조산학 등 일부 전공 제외</t>
+        </is>
+      </c>
+      <c r="M192" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:시트 · 수업언어:확인필요 · 전공:웹 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M192" s="2" t="inlineStr">
+      <c r="N192" s="2" t="inlineStr">
         <is>
           <t>https://www.lancashire.ac.uk/study/global-opportunities/international-exchange-students</t>
         </is>
       </c>
-      <c r="N192" s="2" t="inlineStr">
+      <c r="O192" s="2" t="inlineStr">
         <is>
           <t>globalopportunities@lancashire.ac.uk</t>
         </is>
@@ -14318,15 +15275,20 @@
       </c>
       <c r="L193" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · 1~2학기 선택 가능, 홈교 학점 인정 · 영국 내 현대·국제적 대학</t>
+        </is>
+      </c>
+      <c r="M193" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M193" s="2" t="inlineStr">
+      <c r="N193" s="2" t="inlineStr">
         <is>
           <t>https://www.bcu.ac.uk/international/go-abroad-at-bcu</t>
         </is>
       </c>
-      <c r="N193" s="2" t="inlineStr">
+      <c r="O193" s="2" t="inlineStr">
         <is>
           <t>goabroad@bcu.ac.uk</t>
         </is>
@@ -14390,15 +15352,20 @@
       </c>
       <c r="L194" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · QS 세계 100위권 종합대</t>
+        </is>
+      </c>
+      <c r="M194" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M194" s="2" t="inlineStr">
+      <c r="N194" s="2" t="inlineStr">
         <is>
           <t>https://sway.cloud.microsoft/crKH1ECjA0trPUqY</t>
         </is>
       </c>
-      <c r="N194" s="2" t="inlineStr">
+      <c r="O194" s="2" t="inlineStr">
         <is>
           <t>studyabroad@soton.ac.uk</t>
         </is>
@@ -14462,11 +15429,16 @@
       </c>
       <c r="L195" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · 뉴욕주립대 시스템 소속 공립 종합대</t>
+        </is>
+      </c>
+      <c r="M195" s="2" t="inlineStr">
+        <is>
           <t>GPA:확인필요 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M195" s="2" t="inlineStr"/>
       <c r="N195" s="2" t="inlineStr"/>
+      <c r="O195" s="2" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -14526,15 +15498,20 @@
       </c>
       <c r="L196" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · 파트너 30개국 40개교 이상</t>
+        </is>
+      </c>
+      <c r="M196" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:웹 · 수업언어:시트 · 전공:웹 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M196" s="2" t="inlineStr">
+      <c r="N196" s="2" t="inlineStr">
         <is>
           <t>https://www.hpu.edu/study-abroad/incoming-exchange.html</t>
         </is>
       </c>
-      <c r="N196" s="2" t="inlineStr">
+      <c r="O196" s="2" t="inlineStr">
         <is>
           <t>incomingexchange@hpu.edu</t>
         </is>
@@ -14598,15 +15575,20 @@
       </c>
       <c r="L197" s="2" t="inlineStr">
         <is>
+          <t>교환학생 기숙사 보장, 아파트형 기숙사 배정 · 공학·경영·예술과학 분야 강점</t>
+        </is>
+      </c>
+      <c r="M197" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M197" s="2" t="inlineStr">
+      <c r="N197" s="2" t="inlineStr">
         <is>
           <t>https://www.clarkson.edu/international-center/international-students-and-scholars/inbound-exchange</t>
         </is>
       </c>
-      <c r="N197" s="2" t="inlineStr">
+      <c r="O197" s="2" t="inlineStr">
         <is>
           <t>cbailey@clarkson.edu</t>
         </is>
@@ -14670,15 +15652,20 @@
       </c>
       <c r="L198" s="2" t="inlineStr">
         <is>
+          <t>교내 기숙사 신청 가능 (F1 비자 학생 대상, $250 보증금) · 국제학생 지원 (Office of International Affairs)</t>
+        </is>
+      </c>
+      <c r="M198" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M198" s="2" t="inlineStr">
+      <c r="N198" s="2" t="inlineStr">
         <is>
           <t>www.northpark.edu/international</t>
         </is>
       </c>
-      <c r="N198" s="2" t="inlineStr">
+      <c r="O198" s="2" t="inlineStr">
         <is>
           <t>medrake@northpark.edu</t>
         </is>
@@ -14742,15 +15729,20 @@
       </c>
       <c r="L199" s="2" t="inlineStr">
         <is>
+          <t>기숙사 보장·조기신청 권장, 아파트 신청 가능 · 기숙사 계약 1개월 전 해지 가능, 식사 플랜 권장 · 공립 연구중심 종합대</t>
+        </is>
+      </c>
+      <c r="M199" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M199" s="2" t="inlineStr">
+      <c r="N199" s="2" t="inlineStr">
         <is>
           <t>https://ip.wsu.edu/education-abroad/program-types/inbound-exchange/</t>
         </is>
       </c>
-      <c r="N199" s="2" t="inlineStr">
+      <c r="O199" s="2" t="inlineStr">
         <is>
           <t>ip.exchange@wsu.edu</t>
         </is>
@@ -14814,15 +15806,20 @@
       </c>
       <c r="L200" s="2" t="inlineStr">
         <is>
+          <t>국제학생 오리엔테이션·크로스컬처 활동 제공 · 수강 과목 홈교 학점 인정 필수 확인 · 연구 중심 공학·응용과학 특성화</t>
+        </is>
+      </c>
+      <c r="M200" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M200" s="2" t="inlineStr">
+      <c r="N200" s="2" t="inlineStr">
         <is>
           <t>https://ie.utdallas.edu/go-abroad/incoming-exchange/</t>
         </is>
       </c>
-      <c r="N200" s="2" t="inlineStr">
+      <c r="O200" s="2" t="inlineStr">
         <is>
           <t>oie@utdallas.edu</t>
         </is>
@@ -14886,15 +15883,20 @@
       </c>
       <c r="L201" s="2" t="inlineStr">
         <is>
+          <t>교내 기숙사 미보장·조기신청 필요 · 교환학생 전용 오리엔테이션 제공 · 필수 보험·교통비·기숙사 신청비 발생</t>
+        </is>
+      </c>
+      <c r="M201" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:웹 · 수업언어:시트 · 전공:웹 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M201" s="2" t="inlineStr">
+      <c r="N201" s="2" t="inlineStr">
         <is>
           <t>https://www.umb.edu/academics/global-programs/international-exchange-students/</t>
         </is>
       </c>
-      <c r="N201" s="2" t="inlineStr">
+      <c r="O201" s="2" t="inlineStr">
         <is>
           <t>studyabroad@umb.edu</t>
         </is>
@@ -14958,15 +15960,20 @@
       </c>
       <c r="L202" s="2" t="inlineStr">
         <is>
+          <t>교내 기숙사 필수 · 파트너 7개국 대학 · 1학기 생활비 6,500달러</t>
+        </is>
+      </c>
+      <c r="M202" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M202" s="2" t="inlineStr">
+      <c r="N202" s="2" t="inlineStr">
         <is>
           <t>https://www.uis.edu/study-away/exchange-students</t>
         </is>
       </c>
-      <c r="N202" s="2" t="inlineStr">
+      <c r="O202" s="2" t="inlineStr">
         <is>
           <t>blute2@uis.edu; sap@uis.edu</t>
         </is>
@@ -15030,15 +16037,20 @@
       </c>
       <c r="L203" s="2" t="inlineStr">
         <is>
+          <t>파트너 15개교 이상 운영 · 홈교 학비 납부·제한적 수수료</t>
+        </is>
+      </c>
+      <c r="M203" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:웹 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M203" s="2" t="inlineStr">
+      <c r="N203" s="2" t="inlineStr">
         <is>
           <t>https://uh.edu/learningabroad/find-a-program/exchange-programs/#incoming</t>
         </is>
       </c>
-      <c r="N203" s="2" t="inlineStr">
+      <c r="O203" s="2" t="inlineStr">
         <is>
           <t>acarruth@central.uh.edu</t>
         </is>
@@ -15102,15 +16114,20 @@
       </c>
       <c r="L204" s="2" t="inlineStr">
         <is>
+          <t>기숙사 보장 · 국제 교환학생 전용 오리엔테이션 · 필수 보험·여행 지원 서비스</t>
+        </is>
+      </c>
+      <c r="M204" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M204" s="2" t="inlineStr">
+      <c r="N204" s="2" t="inlineStr">
         <is>
           <t>https://www.brandeis.edu/abroad/study-at-brandeis/incoming-exchange/index.html</t>
         </is>
       </c>
-      <c r="N204" s="2" t="inlineStr">
+      <c r="O204" s="2" t="inlineStr">
         <is>
           <t>arikramer@brandeis.edu</t>
         </is>
@@ -15174,15 +16191,20 @@
       </c>
       <c r="L205" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · 미국 아이다호 주 보이시 소재 공립대</t>
+        </is>
+      </c>
+      <c r="M205" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M205" s="2" t="inlineStr">
+      <c r="N205" s="2" t="inlineStr">
         <is>
           <t>On fact sheet</t>
         </is>
       </c>
-      <c r="N205" s="2" t="inlineStr">
+      <c r="O205" s="2" t="inlineStr">
         <is>
           <t>internationalinfo@boisestate.edu</t>
         </is>
@@ -15246,15 +16268,20 @@
       </c>
       <c r="L206" s="2" t="inlineStr">
         <is>
+          <t>GPA 요건 없음 · 교내 기숙사 미보장·조기신청 필요 · 연 150명+ 교환학생 수용 · 필수 건강 보험 가입</t>
+        </is>
+      </c>
+      <c r="M206" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M206" s="2" t="inlineStr">
+      <c r="N206" s="2" t="inlineStr">
         <is>
           <t>https://goglobal.asu.edu/international/application</t>
         </is>
       </c>
-      <c r="N206" s="2" t="inlineStr">
+      <c r="O206" s="2" t="inlineStr">
         <is>
           <t>ASUExchangeStudent@asu.edu</t>
         </is>
@@ -15318,15 +16345,20 @@
       </c>
       <c r="L207" s="2" t="inlineStr">
         <is>
+          <t>기숙사 입주 가능 · 오리엔테이션 제공 · 필수 보험 가입 필요 · R1 연구 중심 대학</t>
+        </is>
+      </c>
+      <c r="M207" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M207" s="2" t="inlineStr">
+      <c r="N207" s="2" t="inlineStr">
         <is>
           <t>https://www.uwyo.edu/uwyoabroad/incoming-students/incoming-exchange-and-study-abroad-students/index.html</t>
         </is>
       </c>
-      <c r="N207" s="2" t="inlineStr">
+      <c r="O207" s="2" t="inlineStr">
         <is>
           <t>salt@uwyo.edu</t>
         </is>
@@ -15390,15 +16422,20 @@
       </c>
       <c r="L208" s="2" t="inlineStr">
         <is>
+          <t>장학금 및 재정 지원 가능, 주외 학생 수수료 면제 혜택 · 플로리다 주립대 시스템 소속 공립 연구중심대</t>
+        </is>
+      </c>
+      <c r="M208" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M208" s="2" t="inlineStr">
+      <c r="N208" s="2" t="inlineStr">
         <is>
           <t>https://www.usf.edu/world/education-abroad/applying-going/incoming-exchange.aspx</t>
         </is>
       </c>
-      <c r="N208" s="2" t="inlineStr">
+      <c r="O208" s="2" t="inlineStr">
         <is>
           <t>ea-exchanges@usf.edu</t>
         </is>
@@ -15462,15 +16499,20 @@
       </c>
       <c r="L209" s="2" t="inlineStr">
         <is>
+          <t>기숙사 신청 가능·교내 외 숙소 광고 포털 제공 · 교환학생 전담 담당자(Quynh Luong) 및 오리엔테이션 제공 · 학기 시작 전 주 도착 필요·12-18학점 필수 등록 · 경영학부(Kelley School of Business) 특성화</t>
+        </is>
+      </c>
+      <c r="M209" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M209" s="2" t="inlineStr">
+      <c r="N209" s="2" t="inlineStr">
         <is>
           <t>https://kelley.iu.edu/undergraduate/academics/study-abroad/international-exchange-students.html</t>
         </is>
       </c>
-      <c r="N209" s="2" t="inlineStr">
+      <c r="O209" s="2" t="inlineStr">
         <is>
           <t>ksbexch@iu.edu</t>
         </is>
@@ -15534,15 +16576,20 @@
       </c>
       <c r="L210" s="2" t="inlineStr">
         <is>
+          <t>국제학생 지원 및 글로벌 학습 경험 강화</t>
+        </is>
+      </c>
+      <c r="M210" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M210" s="2" t="inlineStr">
+      <c r="N210" s="2" t="inlineStr">
         <is>
           <t>global.uncg.edu</t>
         </is>
       </c>
-      <c r="N210" s="2" t="inlineStr">
+      <c r="O210" s="2" t="inlineStr">
         <is>
           <t>dmbrown2@uncg.edu</t>
         </is>
@@ -15606,15 +16653,20 @@
       </c>
       <c r="L211" s="2" t="inlineStr">
         <is>
+          <t>교환학생 기숙사 보장·조기신청 필요 · 50개 이상 대학 파트너십 · 특정 과목 수강 제한 · 뉴욕주립대 시스템 소속 종합대</t>
+        </is>
+      </c>
+      <c r="M211" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M211" s="2" t="inlineStr">
+      <c r="N211" s="2" t="inlineStr">
         <is>
           <t>https://www.buffalo.edu/educationabroad/incomingexchangeandvisitingstudents.html</t>
         </is>
       </c>
-      <c r="N211" s="2" t="inlineStr">
+      <c r="O211" s="2" t="inlineStr">
         <is>
           <t>keo@buffalo.edu</t>
         </is>
@@ -15678,15 +16730,20 @@
       </c>
       <c r="L212" s="2" t="inlineStr">
         <is>
+          <t>교내 기숙사 및 식사 제공 · 기숙사 거주 시 예방접종 필수 · 펜실베이니아 주립대, 미국 최대 공립대 중 하나</t>
+        </is>
+      </c>
+      <c r="M212" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M212" s="2" t="inlineStr">
+      <c r="N212" s="2" t="inlineStr">
         <is>
           <t>https://global.psu.edu/landing/incoming-exchange-students</t>
         </is>
       </c>
-      <c r="N212" s="2" t="inlineStr">
+      <c r="O212" s="2" t="inlineStr">
         <is>
           <t>eaexchanges@psu.edu</t>
         </is>
@@ -15750,15 +16807,20 @@
       </c>
       <c r="L213" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · 기숙사 미보장·조기신청 필요 · 전담 매니저 지원 · 연 200명+ 교환학생 수용</t>
+        </is>
+      </c>
+      <c r="M213" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M213" s="2" t="inlineStr">
+      <c r="N213" s="2" t="inlineStr">
         <is>
           <t>https://uwm.edu/cie/partner/exchange-partners/incoming-exchange-students/</t>
         </is>
       </c>
-      <c r="N213" s="2" t="inlineStr">
+      <c r="O213" s="2" t="inlineStr">
         <is>
           <t>conways@uwm.edu</t>
         </is>
@@ -15822,15 +16884,20 @@
       </c>
       <c r="L214" s="2" t="inlineStr">
         <is>
+          <t>교내 기숙사 신청 가능 · J-1 비자 필수, DS-2019 발급 · 경영·금융 특성화 대학</t>
+        </is>
+      </c>
+      <c r="M214" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M214" s="2" t="inlineStr">
+      <c r="N214" s="2" t="inlineStr">
         <is>
           <t>https://www.bentley.edu/offices/international-education/exchange-program</t>
         </is>
       </c>
-      <c r="N214" s="2" t="inlineStr">
+      <c r="O214" s="2" t="inlineStr">
         <is>
           <t>cdeichmann@bentley.edu</t>
         </is>
@@ -15894,15 +16961,20 @@
       </c>
       <c r="L215" s="2" t="inlineStr">
         <is>
+          <t>교환학생 전용 오리엔테이션 및 앰배서더 지원 · 미국 최대 규모의 종합대학 중 하나</t>
+        </is>
+      </c>
+      <c r="M215" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M215" s="2" t="inlineStr">
+      <c r="N215" s="2" t="inlineStr">
         <is>
           <t>https://americansemester.isp.msu.edu/</t>
         </is>
       </c>
-      <c r="N215" s="2" t="inlineStr">
+      <c r="O215" s="2" t="inlineStr">
         <is>
           <t>msuex@msu.edu</t>
         </is>
@@ -15966,15 +17038,20 @@
       </c>
       <c r="L216" s="2" t="inlineStr">
         <is>
+          <t>기숙사 조기 신청 필요 · 교환학생 전용 오리엔테이션 · 파트너 30여 개국 50+ 대학 · 트라이메스터제 학사일정</t>
+        </is>
+      </c>
+      <c r="M216" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M216" s="2" t="inlineStr">
+      <c r="N216" s="2" t="inlineStr">
         <is>
           <t>https://issp.ucsc.edu/students/exchange/</t>
         </is>
       </c>
-      <c r="N216" s="2" t="inlineStr">
+      <c r="O216" s="2" t="inlineStr">
         <is>
           <t>istudent@ucsc.edu</t>
         </is>
@@ -16038,15 +17115,20 @@
       </c>
       <c r="L217" s="2" t="inlineStr">
         <is>
+          <t>연 130개교 이상 파트너 대학 · 세계 40위권 종합대</t>
+        </is>
+      </c>
+      <c r="M217" s="2" t="inlineStr">
+        <is>
           <t>GPA:이메일문의 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M217" s="2" t="inlineStr">
+      <c r="N217" s="2" t="inlineStr">
         <is>
           <t>https://global.utexas.edu/isss/advising-services/student-exchange-program</t>
         </is>
       </c>
-      <c r="N217" s="2" t="inlineStr">
+      <c r="O217" s="2" t="inlineStr">
         <is>
           <t>inbound-exchange@austin.utexas.edu</t>
         </is>
@@ -16110,15 +17192,20 @@
       </c>
       <c r="L218" s="2" t="inlineStr">
         <is>
+          <t>도심 도보권 캠퍼스 · 공학 특성화</t>
+        </is>
+      </c>
+      <c r="M218" s="2" t="inlineStr">
+        <is>
           <t>GPA:웹 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M218" s="2" t="inlineStr">
+      <c r="N218" s="2" t="inlineStr">
         <is>
           <t>https://www.sjsu.edu/isss/scholars/exchange/</t>
         </is>
       </c>
-      <c r="N218" s="2" t="inlineStr">
+      <c r="O218" s="2" t="inlineStr">
         <is>
           <t>suzanne.pendergrass@sjsu.edu</t>
         </is>
@@ -16182,15 +17269,20 @@
       </c>
       <c r="L219" s="2" t="inlineStr">
         <is>
+          <t>DS-2019 발급 후 J-1 비자 신청 필요</t>
+        </is>
+      </c>
+      <c r="M219" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M219" s="2" t="inlineStr">
+      <c r="N219" s="2" t="inlineStr">
         <is>
           <t>https://charleston.edu/international/international-students/incoming-exchange-students.php</t>
         </is>
       </c>
-      <c r="N219" s="2" t="inlineStr">
+      <c r="O219" s="2" t="inlineStr">
         <is>
           <t>intlstudents@cofc.edu</t>
         </is>
@@ -16254,15 +17346,20 @@
       </c>
       <c r="L220" s="2" t="inlineStr">
         <is>
+          <t>미국 최고 역사 공립대</t>
+        </is>
+      </c>
+      <c r="M220" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M220" s="2" t="inlineStr">
+      <c r="N220" s="2" t="inlineStr">
         <is>
           <t>https://studyabroad.unc.edu/incoming-exchange/program-overview/</t>
         </is>
       </c>
-      <c r="N220" s="2" t="inlineStr">
+      <c r="O220" s="2" t="inlineStr">
         <is>
           <t>incoming_exchange@unc.edu</t>
         </is>
@@ -16326,15 +17423,20 @@
       </c>
       <c r="L221" s="2" t="inlineStr">
         <is>
+          <t>필수 건강 보험 정책 · FAMU-FSU 공학대 운영</t>
+        </is>
+      </c>
+      <c r="M221" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M221" s="2" t="inlineStr">
+      <c r="N221" s="2" t="inlineStr">
         <is>
           <t>https://globalexchanges.fsu.edu/index.cfm?FuseAction=Programs.ViewProgramAngular&amp;id=27974</t>
         </is>
       </c>
-      <c r="N221" s="2" t="inlineStr">
+      <c r="O221" s="2" t="inlineStr">
         <is>
           <t>inboundexchange@fsu.edu</t>
         </is>
@@ -16398,15 +17500,20 @@
       </c>
       <c r="L222" s="2" t="inlineStr">
         <is>
+          <t>비영어권이지만 전 과정 영어 수업 · 기숙사 미보장·조기신청 필요 · I-GESA 장학금 지원 · I-GESA 장학금(400만 VND) 제공</t>
+        </is>
+      </c>
+      <c r="M222" s="2" t="inlineStr">
+        <is>
           <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
-      <c r="M222" s="2" t="inlineStr">
+      <c r="N222" s="2" t="inlineStr">
         <is>
           <t>https://vinuni.edu.vn/global_exchange/home/</t>
         </is>
       </c>
-      <c r="N222" s="2" t="inlineStr">
+      <c r="O222" s="2" t="inlineStr">
         <is>
           <t>incomingexchange@vinuni.edu.vn</t>
         </is>

--- a/out/universities.xlsx
+++ b/out/universities.xlsx
@@ -658,7 +658,11 @@
           <t>IELTS 6.0점 이상 (전 밴드 6.0) 또는 TOEFL iBT 64점 이상 또는 Duolingo 110점 이상 또는 PTE 50점 이상 (학부 기준)</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>교내 기숙사 미보장 (경쟁적, 조기 신청 권장) · 캠퍼스 간 무료 셔틀버스 운행 · Welcome Week·국제학생 전담 지원팀 운영</t>
+        </is>
+      </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
           <t>GPA:이메일문의 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>

--- a/out/universities.xlsx
+++ b/out/universities.xlsx
@@ -1011,7 +1011,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>2학기 이상 (1년/60 ECTS 완료)</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>프랑스어, 영어</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>프랑스어, 영어</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>네덜란드어, 영어</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>GPA:이메일문의 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:이메일문의 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>IELTS 6.5점 이상 또는 TOEFL iBT 80점 이상 또는 CAEL 60점 이상</t>
+          <t>IELTS 6.5점 이상 또는 TOEFL iBT 86점 이상 (영역별 20) 또는 CAEL 60점 이상</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>중국어, 영어</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>GPA:이메일문의 · 어학:이메일문의 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:이메일문의 · 어학:이메일문의 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>크로아티아어, 영어</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>스페인어, 영어</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>프랑스어, 영어</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 79점 이상 또는 IELTS 6.5점 이상 또는 TOEIC 785점 이상</t>
+          <t>TOEFL iBT 80점 이상 또는 IELTS 6.5점 이상 또는 TOEIC 785점 이상 또는 Duolingo 90점 이상</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>GPA:이메일문의 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:이메일문의 · 어학:웹 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7407,7 +7407,7 @@
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>독일어, 영어</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -8793,7 +8793,7 @@
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>인도네시아어, 영어</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8808,7 +8808,7 @@
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -9024,7 +9024,7 @@
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>이탈리아어, 영어</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>GPA:시트 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:시트 · 어학:웹 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>일본어, 영어</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -9655,7 +9655,7 @@
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:시트 · 어학:시트 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>일본어, 영어</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -16344,7 +16344,7 @@
       </c>
       <c r="K207" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 71점 이상 또는 IELTS 6.0점 이상 또는 CET-4 (학부)/CET-6 (대학원)</t>
+          <t>TOEFL iBT 71점 이상 또는 IELTS 6.0점 이상 또는 CET-4/6 (중국어권 지원자용)</t>
         </is>
       </c>
       <c r="L207" s="2" t="inlineStr">

--- a/out/universities.xlsx
+++ b/out/universities.xlsx
@@ -1083,7 +1083,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>담당자 이메일 문의</t>
+          <t>제한 없음 (홈교 기준 적용)</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>GPA:이메일문의 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:웹 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>18 units (감축 승인 시; 표준 24)</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>24 units</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>담당자 이메일 문의</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -2479,12 +2479,12 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>12 credits (학부; 대학원 6)</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>15 credits (학부; 대학원 9)</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>담당자 이메일 문의</t>
+          <t>프랑스어 CEFR B2 이상</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>GPA:이메일문의 · 어학:이메일문의 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:웹 · 어학:웹 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>담당자 이메일 문의</t>
+          <t>제한 없음 (홈교 선발 신뢰)</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>담당자 이메일 문의</t>
+          <t>IELTS 6.5점 이상 (밴드 6.0) 또는 영어매체 재학 증명 인정</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>GPA:이메일문의 · 어학:이메일문의 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:웹 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>담당자 이메일 문의</t>
+          <t>3.0/4.0 (B 또는 70%)</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>명시 없음 (통상 9~15 credits)</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>15 credits</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>담당자 이메일 문의</t>
+          <t>TOEFL iBT 90점 이상 또는 IELTS 6.5점 이상 (밴드 6.0) 또는 Duolingo 125점 이상 또는 PTE 65점 이상 (협정에 따라 면제 가능)</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>GPA:이메일문의 · 어학:이메일문의 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:웹 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>담당자 이메일 문의</t>
+          <t>2.7/4.0 (학부; 대학원 3.0/4.0)</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>2.5 UofT credits (5과목, 풀타임)</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>GPA:이메일문의 · 어학:웹 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:웹 · 어학:웹 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -4007,17 +4007,17 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>제한 없음</t>
+          <t>2학기 이상 (60 ECTS)</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>30 ECTS (풀타임 기준)</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>30 ECTS</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>담당자 이메일 문의</t>
+          <t>영어 CEFR B2 (증빙 필요)</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>GPA:이메일문의 · 어학:이메일문의 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:이메일문의 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr"/>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>담당자 이메일 문의</t>
+          <t>공인성적 불요 (영어 B2 수준 기대)</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>GPA:이메일문의 · 어학:이메일문의 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:이메일문의 · 어학:웹 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>담당자 이메일 문의</t>
+          <t>3.0/4.0</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -5548,12 +5548,12 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>담당자 이메일 문의</t>
+          <t>명시 없음 (표준 30 ECTS)</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>담당자 이메일 문의</t>
+          <t>30 ECTS (표준)</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>GPA:이메일문의 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:웹 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>명시 없음 (통상 30 ECTS)</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>명시 없음 (통상 30 ECTS)</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
@@ -9953,7 +9953,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>담당자 이메일 문의</t>
+          <t>명시 없음 (일본어 배치시험; 전공과목은 일본어 필요)</t>
         </is>
       </c>
       <c r="L124" s="2" t="inlineStr">
@@ -9963,7 +9963,7 @@
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>GPA:이메일문의 · 어학:이메일문의 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:이메일문의 · 어학:웹 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -10087,12 +10087,12 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>담당자 이메일 문의</t>
+          <t>7과목 (KUINEP·GEA 학부; 대학원 4과목)</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>담당자 이메일 문의</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>담당자 이메일 문의</t>
+          <t>TOEFL iBT 72점 이상 (신척도 4) 또는 IELTS 6.5점 이상 (KUINEP 기준)</t>
         </is>
       </c>
       <c r="L126" s="2" t="inlineStr">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>GPA:시트 · 어학:이메일문의 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:시트 · 어학:웹 · 수업언어:웹 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -11639,7 +11639,7 @@
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>제한 없음 (통상 30 ECTS)</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
@@ -13945,12 +13945,12 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>30 ECTS (표준 부하)</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>30 ECTS (표준 부하)</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
@@ -14166,7 +14166,7 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>담당자 이메일 문의</t>
+          <t>명시 없음</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr">
@@ -14181,7 +14181,7 @@
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>명시 없음 (통상 4~6과목)</t>
         </is>
       </c>
       <c r="I179" s="2" t="inlineStr">
@@ -14196,7 +14196,7 @@
       </c>
       <c r="K179" s="2" t="inlineStr">
         <is>
-          <t>담당자 이메일 문의</t>
+          <t>TOEFL iBT 79점 이상 (TWE 24) 또는 홈교 B2 확인서 (IELTS 인정)</t>
         </is>
       </c>
       <c r="L179" s="2" t="inlineStr">
@@ -14206,7 +14206,7 @@
       </c>
       <c r="M179" s="2" t="inlineStr">
         <is>
-          <t>GPA:이메일문의 · 어학:이메일문의 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:웹 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N179" s="2" t="inlineStr">
@@ -16170,12 +16170,12 @@
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>담당자 이메일 문의</t>
+          <t>12 US credits</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
-          <t>담당자 이메일 문의</t>
+          <t>15 US credits (초과 시 추가 비용)</t>
         </is>
       </c>
       <c r="I205" s="2" t="inlineStr">
@@ -17084,7 +17084,7 @@
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>담당자 이메일 문의</t>
+          <t>명시 없음 (Good standing, 프로그램별 상이)</t>
         </is>
       </c>
       <c r="F217" s="2" t="inlineStr">
@@ -17124,7 +17124,7 @@
       </c>
       <c r="M217" s="2" t="inlineStr">
         <is>
-          <t>GPA:이메일문의 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:웹 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N217" s="2" t="inlineStr">

--- a/out/universities.xlsx
+++ b/out/universities.xlsx
@@ -8336,7 +8336,7 @@
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>TOEFL iBT 80점 이상 또는 TOEFL PBT 550점 이상 또는 IELTS 6.0점 이상</t>
+          <t>TOEFL iBT 80점 이상 (신척도 4.5) 또는 TOEFL PBT 550점 이상 또는 IELTS 6.0점 이상 (대학원 6.5)</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>GPA:시트 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:시트 · 어학:웹 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -8460,7 +8460,7 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>담당자 이메일 문의</t>
+          <t>명시 없음 (법대만 3.0/4.3)</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
@@ -8500,7 +8500,7 @@
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>GPA:이메일문의 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
+          <t>GPA:웹 · 어학:시트 · 수업언어:시트 · 전공:시트 · 위치:AI추정</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">

--- a/out/universities.xlsx
+++ b/out/universities.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · GPA 요건 없음 · QS 최상위권 종합대</t>
+          <t>예술·디자인 산업 중심지로서의 도시 인프라 · 다양한 국제학생 커뮤니티 활성화 · 남반구 최대 규모의 대학 도서관 보유</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>교내 기숙사 미보장 (경쟁적, 조기 신청 권장) · 캠퍼스 간 무료 셔틀버스 운행 · Welcome Week·국제학생 전담 지원팀 운영</t>
+          <t>교내 기숙사 미보장 (경쟁적, 조기 신청 권장) · 시드니 접근성 좋은 해변 도시 · 휴양지 분위기 캠퍼스·자연 경관</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>GPA 요건 없음 · ELICOS 및 준비 과정 제공 · 공학 및 기술 특성화</t>
+          <t>멜버른 미식·카페 문화 체험 가능 · 도심 접근성 좋은 조용한 주거지</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>160+ 학생 클럽 보유 · QS 세계 77위 종합대</t>
+          <t>인도양 접한 해변 도시 휴양지 매력 · 캠퍼스 내 호주 원주민 문화 체험 가능</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>트라이메스터제 학사일정 · QS 세계대학랭킹 19위 종합대</t>
+          <t>바다와 가까운 휴양 도시 분위기 · 미식과 카페 문화로 유명한 도시</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · 호주 내 실용적 교육 강점</t>
+          <t>강변 카페·레스토랑 밀집해 분위기 좋음 · 브리즈번 강 유람선 타고 도시 경관 즐기기 · 현대적 아트 갤러리·박물관 접근성 우수</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · 150+ 학생 동아리 및 과외 프로그램 · 호주 1위 젊은 대학(2024 THE)</t>
+          <t>시드니 오페라하우스 근접 문화 체험 · 디자인·IT 분야 호주 최고 수준 교육 · 다국적 푸드마켓·해변 카페 문화</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>트라이메스터제 운영(2월-6월, 7월-11월)</t>
+          <t>해양 스포츠·자연 탐방 기회 풍부 · 브리즈번 접근성 좋은 소도시 휴양지 · 캠퍼스 주변 자연 경관 활용한 휴식 공간</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>OSHC(해외학생 건강보험) 필수 가입</t>
+          <t>호주 국립대 명성으로 글로벌 네트워크 강점 · 정치·행정 중심지 도시 특유의 차분한 분위기 · 자연사 박물관·전쟁 기념관 등 문화시설 접근성 우수</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · GPA 요건 없음 · 버디 프로그램 운영 · 교환학생 필수 오리엔테이션 및 교환페어 참석</t>
+          <t>알프스 근접 자연 경관·아웃도어 활동 천국 · 티롤 지역 전통 문화·독일어권 생활 체험 · 인스브루크 접근성 좋은 소도시 생활</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · GPA 요건 없음 · 기숙사 미보장·조기신청 필요 · 전담 오리엔테이션·멘토링</t>
+          <t>기숙사 미보장·조기신청 필요 · 유럽 문화 중심지·박물관·오페라 접근성 우수 · 빈 특유 커피하우스 문화 체험 가능 · 알프스·동유럽 배낭여행 거점 도시</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · GPA 요건 없음 · Welcome Week 제공 · 18~30 ECTS 학점 선택 가능</t>
+          <t>알프스 근접 자연 경관·아웃도어 활동 천국 · 소규모 도시 한적함·유럽 전통 마을 분위기</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · 공인 어학성적 없이 지원 가능 · 오리엔테이션 프로그램 제공 · 연 400명+ 교환학생 수용</t>
+          <t>알프스 접근성 최고, 겨울 스포츠 천국 · 중세풍 구시가지와 현대적 인프라 조화</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · 공인 어학성적 없이 지원 가능 · 공학·경영 특성화</t>
+          <t>알프스 근접 자연 탐험·휴양 최적 · 소도시 정취 속 유럽 전통 건축 감상 · 린츠 문화생활 접근성 우수</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>GPA 요건 없음 · 연 200명+ 교환학생 수용 · 유럽연합 학생 무료 건강보험 적용 · 경영·경영관리 특성화</t>
+          <t>유럽 연합 기관 밀집한 정치·비즈니스 중심지 · 벨기에 전통 와플·초콜릿 문화 체험 가능</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · GPA 요건 없음 · 학생 클럽 Cercle Solvay가 교환학생 대상 사회·커리어 이벤트 주최 · 경영 트리플크라운 인증(AACSB·AMBA·EQUIS) 보유</t>
+          <t>유럽 연합 기관 밀집한 국제적 도시 분위기 · 벨기에 전통 와플·초콜릿 문화 체험 가능 · 브뤼셀 도심 접근성 좋은 교통 인프라</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · 비영어권이지만 전 과정 영어 수업 · HEC 캠퍼스 근처 사설 기숙사 · 버디 프로그램 및 국제학생 전용 클럽 운영</t>
+          <t>HEC 캠퍼스 근처 사설 기숙사 · 벨기에 전통 맥주·와플 체험 가능한 미식 도시 · 아르덴 숲·독일 국경 근접 자연 탐험 적합 · 유럽 중세 건축물과 현대적 캠퍼스 조화</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · 오리엔테이션 &amp; 버디 프로그램 · 캠퍼스별 전공 특성 차이 (안트베르펜·브뤼셀-경영 실무, 루벤-경제·금융 분석) · 벨기에 최대 종합대</t>
+          <t>유럽 한복판 주말 배낭여행 거점 · 고즈넉한 유럽 대학도시 낭만 · 미식과 카페 문화로 유명한 도시</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>공인 어학성적 없이 지원 가능 · 100% 온라인 수업 옵션 제공 · 50년 전통 종합대학</t>
+          <t>포르투알레그리 접근성 좋은 소도시 분위기 · 남미의 독특한 포르투갈어 문화 체험 · 대학가 중심 소규모 카페·식당 밀집</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>학점 인정 가이드라인 및 성적 환산 기준 제공 · 브라질 최대 국립 종합대학</t>
+          <t>남미 최대 규모의 종합대학 연구 인프라 · 상파울루 미식·카페 문화 체험 가능 · 대도시 접근성·인턴십 기회 풍부</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>학부 과정 무료(등록금·월비 없음) · 공학·의학·자연과학 강점</t>
+          <t>열대 식물원·호수로 자연 속 캠퍼스 분위기 · 상파울루 접근성 좋은 교통 허브 도시</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · 교내 기숙사·홈스테이·개인 숙소 선택 가능 · 국제교육팀 지원 및 오리엔테이션 제공 · 의료보험 필수·교통비 월 $65~$208</t>
+          <t>교내 기숙사·홈스테이·개인 숙소 선택 가능 · 와인 산업 중심지로 미식·와이너리 체험 가능 · 로키 산맥 근접해 자연 탐험·아웃도어 활동 적합 · 소도시라 한적하지만 밴쿠버 접근성 좋은 균형</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · 비영어권이지만 전 과정 영어 수업 · 기숙사 미보장·조기신청 필요 · 전담 Academic Coordinator 지원</t>
+          <t>기숙사 미보장·조기신청 필요 · 대도시 인턴십·아르바이트 기회 풍부 · 다문화 도시 음식·카페 탐방 매력적 · 나이아가라 폭포 등 근교 여행 접근성</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>65세 이상 수강생 $100 행정 수수료 · 영어·프랑스어 이중 언어 교육</t>
+          <t>토론토 도심 접근성 좋은 교통 인프라 · 다문화 도시 환경에서 글로벌 경험 가능 · 현대적 캠퍼스 시설 및 연구 자원 풍부</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · 비영어권이지만 전 과정 영어 수업 · 교내 기숙사 미보장 · 국제학생지원센터(ISSAC) 운영</t>
+          <t>교내 기숙사 미보장 · 대평원 풍경과 오로라 체험 가능한 자연 경관 · 캐나다 대표 곡창지대 농업 연구 중심지</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · 트라이메스터제 운영(겨울 2027 지원 접수) · 경영 트리플크라운 인증(AACSB, EQUIS, AMBA 보유)</t>
+          <t>프랑스어권 문화 체험 가능한 이중언어 도시 · 몬트리올 재즈 페스티벌 등 문화행사 활발 · 북미에서 유럽풍 거리 분위기 느껴지는 도시</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · 일부 파트너국 저비용 숙소 · 전체 과정 지원 · 65+ 영어 사용 파트너교</t>
+          <t>대평원 접한 자연 경관과 도시 접근성 조화 · 프랑스계 문화 영향받은 독특한 도시 분위기</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · 필수 보험(Guard.Me) 및 교통비(U-Pass) 납부 · 캐나다 밴쿠버 소재 종합대</t>
+          <t>밴쿠버 근교 자연 경관과 도시 생활 균형 · 다양한 국제학생 커뮤니티와 문화 행사</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · 캐나다 북대서양 연안에 위치한 종합대학</t>
+          <t>바다와 인접한 휴양지 분위기 · 소도시라 생활비 부담 적은 편 · 유럽풍 건축물과 역사적 명소 산재</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · 교내 기숙사 신청 가능·수요 높음·조기신청 필요 · 도착 체크리스트·학생 서비스 제공 · QS 세계 40위권 종합대</t>
+          <t>교내 기숙사 신청 가능·수요 높음·조기신청 필요 · 바다와 가까운 휴양 도시 분위기 · 미식과 카페 문화로 유명한 도시 · 시내로 나가는 대중교통 편리</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · 비영어권이지만 전 과정 영어 수업 · 기숙사 미보장·경쟁적 신청 필요 · 여름 학기 기숙사 보장</t>
+          <t>기숙사 미보장·경쟁적 신청 필요 · 여름 학기 기숙사 보장 · 한국인 인지도 높은 캐나다 최고 명문대 · 다양한 문화·음식 체험 가능한 글로벌 도시 · 온타리오 호수 인접 자연 경관 접근성 우수</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>연 1000명+ 교환학생 수용 · 프랑스어 B2 이상 필수 · 캐나다 프랑스어권 종합대</t>
+          <t>프랑스어권 문화 체험에 최적화된 도시 · 유럽풍 건축물과 활기찬 예술 현장 · 겨울 카니발 등 독특한 계절 행사</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>연 4,000명+ 국제학생 수용 · 최소 12학점(4과목) 필수 등록, 최대 15학점(5과목)+언어 3학점 · 경영 트리플크라운 인증</t>
+          <t>프랑스어·영어 이중언어 도시 문화 체험 · 몬트리올 재즈페스티벌 등 세계적 축제 다수 · 북미에서 유럽풍 도시 분위기 독특</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>미디어·커뮤니케이션 분야 특성화 국립대</t>
+          <t>베이징 도심 접근성 좋은 교통 인프라 · 미디어 시설 집약된 첨단 캠퍼스 환경 · 전통과 현대 조화되는 도시 문화 체험</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
@@ -3193,7 +3193,7 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>교내 기숙사 700-1400 CNY/월 · 보험 800 CNY/년 필수 · 공학·의학 특성화 국립대</t>
+          <t>교내 기숙사 700-1400 CNY/월 · 공학·의학 분야 세계적 연구 인프라 · 우한 특색 있는 후이쿠이 거리 미식 체험 · 장강 유람·황허궁 등 역사 명소 접근성</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · 글로벌 파트너 200개교 이상</t>
+          <t>산둥반도 역사 유적과 현대 도시 조화 · 실크로드 경제벨트 중심 도시 접근성</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · 경영 트리플크라운 인증</t>
+          <t>베이징 중심가 접근성·역사문화 탐방 용이 · 경영 분야 글로벌 네트워크 형성 기회</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>기숙사 제공 및 공항 픽업 서비스 · 오리엔테이션 및 심리 상담 서비스</t>
+          <t>기숙사 제공 및 공항 픽업 서비스 · 베이징 역사·문화 유적 접근성 우수 · 미식과 전통 시장 체험 기회 풍부</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>일부 과목 수강 경쟁률 높음 · 공학·경영 특성화</t>
+          <t>상하이 미식·카페 문화 체험 가능 · 도심 접근성 좋은 첨단 캠퍼스 환경 · 한국인에게 인지도 높은 명문 공학·경영대</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · 비영어권이지만 전 과정 영어 수업 · 석사 과정 수강 시 180 ECTS 이상 필요 · 크로아티아 최대 경제·경영 단과대학</t>
+          <t>아드리아해 접근 용이한 유럽 배낭여행 거점 · 중세 건축물과 현대적 도시 풍경 조화</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · 비영어권이지만 전 과정 영어 수업 · 기숙사 신청 가능 · 버디 시스템·오리엔테이션 주 운영</t>
+          <t>기숙사 신청 가능 · 유럽 중부 교통 허브로 주말 여행 편리 · 역사적 건축물과 현대적 도시 풍경 조화 · 체코 전통 음식과 와인 문화 체험</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · 비영어권이지만 전 과정 영어 수업 · 교환학생 기숙사 보장 (Větrník, Hvězda, Kajetánka) · 버디 프로그램 운영</t>
+          <t>교환학생 기숙사 보장 (Větrník, Hvězda, Kajetánka) · 유럽 역사 중심지에서의 문화 체험 · 중세 건축물과 현대적 도시 풍경 조화 · 체코 전통 음식과 맥주 문화 체험</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · 학생 기숙사 제공 (에스비에르, 콜딩, 오덴세, 쇠네르보르, 베일레) · 게스트 학생 학비 부과 · 영어 강의 제공 국제 대학</t>
+          <t>학생 기숙사 제공 (에스비에르, 콜딩, 오덴세, 쇠네르보르, 베일레) · 유럽 한복판 주말 배낭여행 거점 · 고즈넉한 유럽 대학도시 낭만 · 바다와 가까운 휴양 도시 분위기</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · 국제학생서비스 지원 · 연 900명+ 교환학생 수용 · 영어 B2 이상 요구</t>
+          <t>코펜하겐 접근성 좋은 소도시 생활 · 북유럽 첨단기술 연구 인프라 체험 · 자전거 친화적 도시 환경</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · 비영어권이지만 전 과정 영어 수업 · 교환학생 기숙사 신청 보장 · 연 2000+ 과목 제공</t>
+          <t>교환학생 기숙사 신청 보장 · 유럽 배낭여행 거점으로 주말 여행 편리 · 북유럽 미식·디자인 문화 체험 가능 · 한적한 운하·공원 도시 낭만적 분위기</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · 덴마크 유일의 학제간 프로젝트 기반 교육</t>
+          <t>코펜하겐 접근성 좋은 소도시 생활 · 자연과 어우러진 현대적 캠퍼스</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · 코펜하겐 캠퍼스 기숙사 구하기 어려움 · 버디 프로그램 및 국제 사무실 지원 · 덴마크어 A레벨 요구(북유럽 교환생)</t>
+          <t>코펜하겐 캠퍼스 기숙사 구하기 어려움 · 프로젝트 기반 학습 방식 독창적 · 북유럽 산업단지 인접 취업 기회 · 한적한 항구 도시 여유로운 분위기</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · 공인 어학성적 없이 지원 가능 · 갈라파고스 학기제 운영</t>
+          <t>갈라파고스 근접 생태 탐험 기회 · 안데스 산악 지형과 열대 우림 접한 자연 경관 · 에콰도르 전통 문화 체험 가능한 소도시 분위기</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · GPA 요건 없음 · 기숙사 미보장·조기신청 필요 · 학생 버디 프로그램·국제학생 오리엔테이션</t>
+          <t>기숙사 미보장·조기신청 필요 · 발트해 접한 중세풍 항구 도시 · 유럽 배낭여행 거점 접근성 우수 · 북유럽식 현대적 학습 공간</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · GPA 요건 없음 · ESN(Erasmus Student Network) 활동 · 연 200명+ 교환학생 수용</t>
+          <t>헬싱키 근교 소도시라 유럽 여행 접근성 우수 · 숲과 호수 많은 자연 친화적 환경 · 디자인·테크 산업 중심지 도시 분위기</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · 공인 어학성적 없이 지원 가능 · 기숙사 사실 미제공 · 교환학생 전용 튜터 배정</t>
+          <t>기숙사 사실 미제공 · 핀란드 서부 해안가 휴양 도시 분위기 · 소규모 캠퍼스·친근한 학풍 · 헬싱키 접근성 좋은 소도시 생활</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · 교환학생 오리엔테이션(8월 18-21일) 및 전담 인바운드 팀 지원 · 캠퍼스 내 5명 중 1명 국제학생 비율 · 유럽연합 최북단 종합대학(과학·예술 분야)</t>
+          <t>북극권 오로라 체험 가능한 겨울 풍경 · 산타클로스 마을과 크리스마스 테마 관광지 인접 · 한적한 북유럽 자연 속 캠퍼스 분위기</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · GPA 요건 없음 · Clinical Medicine 지원자는 3-4월 신청 시 우선권 부여</t>
+          <t>호수와 숲으로 둘러싸인 자연 친화적 환경 · 소도시라 한적하고 여유로운 생활 리듬 · 핀란드 전통 사우나 문화 체험 가능</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · 비영어권이지만 전 과정 영어 수업 · 다학제 연구 중심 국립대</t>
+          <t>북유럽 디자인·테크놀로지 융합 연구 선도 · 호수와 숲으로 둘러싸인 자연 친화적 도시 · 핀란드 제2의 도시로 문화·예술 인프라 풍부</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · GPA 요건 없음 · 오리엔테이션 3일 제공 · EU 외 학생 필수 건강보험 가입</t>
+          <t>북극권 근처 자연 경관 접근성 우수 · 소도시 한적한 유럽 생활 체험 · 오울루 대비 저렴한 생활비</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · 비영어권이지만 전 과정 영어 수업 · 기숙사 정보 링크 제공 · 튜터 픽업 서비스 및 필수 오리엔테이션 제공</t>
+          <t>기숙사 정보 링크 제공 · 북유럽 비즈니스 명문대 명성 · 발트해 접한 항구 도시 전망 · 디자인·북유럽 라이프스타일 체험</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · 비영어권이지만 전 과정 영어 수업 · 교환학생 기숙사 보장 · 학생 튜터·오리엔테이션·개인 학습 상담 지원</t>
+          <t>교환학생 기숙사 보장 · 북유럽 디자인·창업 생태계 체험 가능 · 발트해 접한 항구 도시 휴양지 분위기</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · GPA 요건 없음 · Housing for exchange students · Mandatory orientation</t>
+          <t>헬싱키 근교 자연·호수 접근성 우수 · 북유럽 디자인·테크 혁신 중심지 · 유럽 배낭여행 거점 도시 연결성</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · 비영어권이지만 전 과정 영어 수업 · 의학·심리학 수강 시 2년 이상 학업 요건, 생명과학은 2년 전공 이수 필요</t>
+          <t>북유럽 최대 도시 헬싱키의 활기찬 문화생활 · 발트해 접한 해양 휴양지 분위기 · 유럽 내 배낭여행 거점 도시 접근성</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · 교내 기숙사 미보장·조기신청 필요 · 학생 튜터 배정(오리엔테이션·실용 문제 지원) · 연 300명+ 교환학생 수용</t>
+          <t>교내 기숙사 미보장·조기신청 필요 · 북유럽 디자인·공예 체험 가능한 문화 도시 · 헬싱키 접근성 좋은 소도시 여유로움 · 발트해 접한 항구 도시의 자연 경관</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · GPA 요건 없음 · 필수 예방접종 증명(파상풍·B형 간염) 필요 · 생명공학 특성화 사립대</t>
+          <t>생명공학 특화 교육 인프라 집약 · 파리 접근성 좋은 교외 생활권 · 프랑스어 없이도 영어 수업 가능</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>공인 어학성적 없이 지원 가능 · GPA 요건 없음 · 교환학생 브로슈어 제공 · 경영 트리플크라운 인증</t>
+          <t>경영 트리플크라운 인증의 글로벌 명성 · 파리 접근성 좋은 준도시 생활 편의성 · 유럽 배낭여행 거점으로 최적</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · 비영어권이지만 전 과정 영어 수업 · 기숙사 미보장·조기신청 필요 · 버디 프로그램·학생협회 지원</t>
+          <t>기숙사 미보장·조기신청 필요 · 유럽 한복판 주말 배낭여행 거점 · 미식·카페 문화 체험 가능한 도시 · 대도시 인턴·문화생활 기회 풍부</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
@@ -5419,7 +5419,7 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · GPA 요건 없음 · 경영 트리플크라운 인증</t>
+          <t>낭시 시내 미식·카페 문화 체험 가능 · 파리 접근성 좋은 유럽 여행 거점 · 낭만적인 소도시 분위기·역사적 건축물</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · 정보 세션 및 튜터 지원 · 비자 신청용 입학허가서 발급</t>
+          <t>리옹의 미식·와인 문화와 어우러진 도시 생활 · 유럽 교통 허브로 주말 여행 접근성 우수 · 역사적 건축물과 현대적 도시 풍경 공존</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
@@ -5573,7 +5573,7 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · 프랑스어 레벨 테스트 필수 · 경영 트리플크라운 인증</t>
+          <t>유럽 배낭여행 거점으로 접근성 우수 · 프랑스 전통 미식·카페 문화 체험 가능 · 고즈넉한 유럽 소도시 낭만 분위기</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · 파트너 230개교 · 학기당 25~35 ECTS 수강 · 경영 트리플크라운 인증</t>
+          <t>유럽 한복판 주말 배낭여행 거점 · 리옹 미식·와인 문화 체험 · 경영 명문 인증받은 글로벌 교육</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · Grande Ecole 21ECTS/학기, BBA 30ECTS/학기 · 경영 트리플크라운 인증</t>
+          <t>유럽 북부 교통 허브로 주말 여행 편리 · 프랑스 전통 건축과 현대적 캠퍼스 조화 · 릴의 번화한 도심 문화 체험 가능</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>GPA 요건 없음 · 교내 기숙사 미보장·조기신청 필요 · 프랑스어 B1-B2 또는 영어 B2 권장 · 공학·자연과학·인문학 강점 종합대</t>
+          <t>교내 기숙사 미보장·조기신청 필요 · 알프스 접근성 좋은 산악 휴양지 · 프랑스어·영어 병행 수업 가능 · 미식 도시 그르노블의 카페 문화</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>프랑스어/영어 집중 세미나 및 언어 강좌 제공 · 전 세계 수백 개 대학과 교환 협약 체결 · 최대 30 ECTS(프랑스어 세미나 수강 시 33 ECTS) 수강 가능 · 경영·경제·수학·컴퓨터과학 분야 특성화 대학</t>
+          <t>파리 도심 접근성 좋은 교통 인프라 · 미식·예술 도시 문화 체험 가능 · 유럽 배낭여행 거점 도시 입지</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>연 1000명+ 교환학생 수용 · 프랑스어·영어 병행 수업 선택 가능 · 경영 트리플크라운 인증</t>
+          <t>와인 산업 중심지 미식·와이너리 체험 가능 · 보르도 강변 휴양지 분위기·유럽풍 도시 경관 · 프랑스 남서부 여행 거점(기차 2시간 내 대서양·산악지대)</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · GPA 요건 없음 · 교내·외 기숙사 지원 · 버디 시스템·국제 클럽·프랑스어 수업</t>
+          <t>교내·외 기숙사 지원 · 파리 접근성 좋은 준도시 생활 · 프랑스어 수업 병행한 문화 체험 · 유럽 배낭여행 거점 도시</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · 프랑스어 불필요(교환 지원 시) · 공학 특성화</t>
+          <t>유럽 한복판 주말 배낭여행 거점 · 미식·카페 문화 도시 매력</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · GPA 요건 없음 · 파트너 300개교+ · 인문학·사회과학 특성화</t>
+          <t>유럽 역사 중심지·예술적 분위기 체험 · 미식·카페 문화 풍부한 도시 생활 · 한국인에게 인지도 높은 명문 대학</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>가톨릭 계열 종합대</t>
+          <t>유럽 배낭여행 거점으로 접근성 우수 · 프랑스 북부 미식·카페 문화 체험 가능</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>GPA 요건 없음 · 국제학생 오리엔테이션 필수 참석 · 160개 파트너 대학, 100+ 국적 학생 · 무료 프랑스어 수업(5 ECTS), 필수 출석</t>
+          <t>지중해 휴양지 니스의 해변·기후 매력 · 릴의 유럽풍 구시가지·카페 문화 · 프랑스 남부·북부 두 도시 경험 가능</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · 국제학생 대상 연중 행사 운영 · 모든 캠퍼스 교환 프로그램 가능 · 스페인어 집중 코스(8월 말 시작)</t>
+          <t>유럽 배낭여행 거점으로 접근성 우수 · 로즈 와인·남프랑스 미식 체험 가능 · 우주산업 중심지 첨단 기술 분위기</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>GPA 요건 없음 · 외부 기숙사 협력 (월 €450-700), 보장 불가 · 프랑스어 시험 필수 (도착 전), 학기별 시험 기간 2주 · 아시아·아프리카·중동 언어·문명 연구 특화 국립대</t>
+          <t>외부 기숙사 협력 (월 €450-700), 보장 불가 · 아시아·아프리카·중동 문화 체험 기회 풍부 · 파리 접근성 좋은 준도시 생활 · 프랑스어 집중 학습 환경</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>GPA 요건 없음 · 공학 특성화</t>
+          <t>파리 도심 접근성 좋은 교통 인프라 · 도시 공학 특화 실습 프로젝트 풍부 · 프랑스 전통 건축과 현대적 캠퍼스 조화</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>GPA 요건 없음 · HUB를 통한 전 과정 지원 · 연 2100명+ 교환학생 수용 · 프랑스어 B2 이상 필수</t>
+          <t>샴페인 본고장 미식·와인 문화 체험 · 파리 접근성 좋은 유럽 여행 거점 · 역사적 건축물 가득한 고풍스러운 도시</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · 교내 기숙사 미보장·조기신청 필요 · 버디 프로그램·학생협회 지원 · 월 평균 1200~1900유로 생활비</t>
+          <t>교내 기숙사 미보장·조기신청 필요 · 미식과 카페 문화로 유명한 도시 · 유럽 한복판이라 주말 배낭여행 거점으로 최적</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>교환학생 기숙사 일부 보장·조기신청 필요 · 버디 프로그램·국제학생팀 지원 · 연 23,000명+ 학생·100개국 이상 국제학생 · 학기별 360유로 기여금(교통권 포함)</t>
+          <t>교환학생 기숙사 일부 보장·조기신청 필요 · 유럽 내 접근성 좋은 교통 허브 도시 · 자연과 도시가 조화된 산악 지형 경관 · 독일 전통 시장과 현대적 문화 공존</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
@@ -6882,7 +6882,7 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · 경영·경제 분야 강세</t>
+          <t>라인강변 산책로·강가 카페 문화 · 독일 남서부 교통 허브로 유럽 여행 편리 · 바덴뷔르템베르크 주 경제 중심지</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
@@ -6955,7 +6955,7 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · GPA 요건 없음 · 교환학생 상담 서비스 제공 · 영어 강의 수강 가능</t>
+          <t>루르 공업지대 중심 도시 산업 현장 체험 기회 · 독일 전통 맥주 문화 체험 가능한 도시</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · GPA 요건 없음 · 독일어 과정·기업 방문·소셜 활동 제공 · 경영·디지털 기술·AI 분야 특화</t>
+          <t>라인 강변 산책로·강변 카페 문화 · 쾰른 대성당·역사적 명소 접근성 · 유럽 주요 도시 간 교통 허브</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -7109,7 +7109,7 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · 기숙사 신청 필수·조기신청 필요 · 오리엔테이션 주·버디 프로그램 · 영어 강의·과정 제공</t>
+          <t>기숙사 신청 필수·조기신청 필요 · 발트해 접한 항구 도시 휴양지 분위기 · 북독일 전통 건축물과 현대적 캠퍼스 조화</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>공인 어학성적 없이 지원 가능 · GPA 요건 없음 · 보험 미제공, B2 어학 권장 · 공학·IT 특성화</t>
+          <t>라이프치히 접근성 좋은 유럽 배낭여행 거점 · 공학 특화 대학도시 고즈넉한 분위기</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>버디 프로그램 운영 · 모듈 핸드북 온라인 제공</t>
+          <t>중세 도시 풍경과 현대적 캠퍼스 조화 · 함부르크 접근성 좋은 소도시 생활 · 북독일 전통 음식과 카페 문화</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>교환학생 전용 오리엔테이션 및 온라인 상담 제공 · 파트너 대학 대상 GStEP 프로그램 운영 · 학기 시작 전 3개 트랙의 예비 수업 제공 · 프랑크푸르트 학파 이론 연구 중심 대학</t>
+          <t>유럽 금융 중심지 인턴십 기회 풍부 · 프랑크푸르트 학파 사회과학 명성 · 마인 강변 산책로·근교 자연경관</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · 비영어권이지만 전 과정 영어 수업</t>
+          <t>라인 강변 낭만적인 도시 풍경 · 쾰른 대성당 등 역사적 명소 접근성 · 유럽 내 교통 허브로 주말 여행 편리</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>GPA 요건 없음</t>
+          <t>유럽 한복판이라 주말 배낭여행 거점으로 최적 · 바다와 가까운 휴양 도시 분위기</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>기숙사 엘리베이터 미설치·버디 지원 · 버디 프로그램 운영 · 다국적 학생 교류 활발 · 저렴한 생활비·짧은 통학 거리</t>
+          <t>기숙사 엘리베이터 미설치·버디 지원 · 하노버 접근성 좋은 조용한 대학 도시 · 독일 전통 건축물과 현대적 캠퍼스 조화</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>GPA 요건 없음 · 120개 이상 대학 파트너십 · 비EU 국적자 거주허가 필요 · 독일 명문 종합대</t>
+          <t>유럽 한복판이라 주말 배낭여행 거점으로 최적 · 대도시라 인턴·문화생활 기회 풍부</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · 기숙사 및 민간 숙소 지원 · 버디 프로그램 운영 · 비자·보험·등록 지원</t>
+          <t>기숙사 및 민간 숙소 지원 · 유럽 한복판 주말 배낭여행 거점 · 미식·맥주 문화 중심 도시 · 알프스 접근성 좋은 대도시</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
@@ -7802,7 +7802,7 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>기숙사 비용 월 280~470유로, 1인 아파트 350유로 · 버디 프로그램 운영</t>
+          <t>기숙사 비용 월 280~470유로, 1인 아파트 350유로 · 프라이부르크 접근성 좋은 소도시 생활 · 독일 블랙포레스트 휴양지 근접 · 실용적 공학 교육 중심 대학</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
@@ -7879,7 +7879,7 @@
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>버디 프로그램 운영</t>
+          <t>유럽 주요 도시 접근성 뛰어난 교통 허브 · 프랑크푸르트 금융 중심지 인턴십 기회 풍부 · 현대적 캠퍼스·실용적 교육 환경</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
@@ -7956,7 +7956,7 @@
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · 비영어권이지만 전 과정 영어 수업 · 교환학생 전담 지원 서비스 · 여름/겨울 학교 프로그램 운영</t>
+          <t>유럽 금융허브 도시에서의 인턴십 기회 풍부 · 프랑크푸르트 공항 접근성 우수한 교통 요충지 · 마인강변 산책로와 현대적 도시 풍경 조화</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
@@ -8033,7 +8033,7 @@
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · 비영어권이지만 전 과정 영어 수업 · 기숙사 미보장·조기신청 필요 · 버디 프로그램·독일어 집중 코스</t>
+          <t>기숙사 미보장·조기신청 필요 · 유럽 중심지로 주말 여행·인턴십 기회 다수 · 예술·역사 유적지 밀집한 문화 도시</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
@@ -8110,7 +8110,7 @@
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · 선택적 기숙사 제공 · 국제 사무실 지원 · 전 세계 40개 파트너 대학</t>
+          <t>선택적 기숙사 제공 · 유럽 한복판 주말 배낭여행 거점 · 라인강변 고즈넉한 대학도시 낭만 · 미식과 카페 문화 발달한 도시</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
@@ -8187,7 +8187,7 @@
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · GPA 요건 없음 · 교내 기숙사 미보장·조기신청 필요 · 버디 프로그램(BeBuddy), 웰컴 위크, 전담 교환학생 서비스</t>
+          <t>교내 기숙사 미보장·조기신청 필요 · 유럽 내 교통 허브로 주말 여행 편리 · 독일 전통 건축물과 현대적 캠퍼스 조화 · 미식과 맥주 문화로 유명한 도시</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
@@ -8264,7 +8264,7 @@
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>기숙사 사실 미보장·개별 신청 필요 · 월 생활비 992-1250유로·학기당 72유로 필수 납부 · 공학·의학·자연과학 강점 국립대</t>
+          <t>기숙사 사실 미보장·개별 신청 필요 · 뉘른베르크 접근성 좋은 소도시 낭만 · 공학·의학 연구 인프라 우수 · 바이에른 전통 음식과 맥주 문화 체험</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
@@ -8341,7 +8341,7 @@
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>홍콩 최상위권 종합대</t>
+          <t>홍콩 섬과 가까운 자연 경관·트레킹 명소 · 미식·쇼핑·야경 즐길 수 있는 글로벌 도시 · 대학 내 중영 이중언어 환경·국제적 분위기</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>봄학기 기숙사 가용성 높음 · 오리엔테이션 및 활동 제공 · 학점 24-30학점 권장, 법학 전공자 비법학 과목 제한 · 아시아 최상위권 종합대</t>
+          <t>봄학기 기숙사 가용성 높음 · 아시아 금융허브 도시에서의 글로벌 인턴십 기회 · 미식과 야경 명소로 유명한 활기찬 도시 생활 · 홍콩 도심 접근성 좋은 현대적 캠퍼스 환경</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
@@ -8495,7 +8495,7 @@
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>QS 세계대학랭킹 100위권 종합대</t>
+          <t>미식과 카페 문화로 유명한 도시 · 시내로 나가는 대중교통 편리 · 대도시라 인턴·문화생활 기회 풍부</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>공학·비즈니스·건설환경 분야 강세</t>
+          <t>미식과 카페 문화로 유명한 도시 · 대도시라 인턴·문화생활 기회 풍부</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
@@ -8649,7 +8649,7 @@
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>ESN Pécs 지원 · 유럽 300만 명 이상 교환학생 참여 · 헝가리 최대 규모 종합대학</t>
+          <t>유럽 전통 건축물과 현대적 캠퍼스 조화 · 부다페스트 접근성 좋은 소도시 생활 · 헝가리 전통 온천 문화 체험 가능</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>저렴한 생활비, 친절한 지역사회, 활발한 학술분위기 · 인도네시아 최상위권 종합대</t>
+          <t>유네스코 문화유산과 전통 시장 접근성 우수 · 열대 정원형 캠퍼스와 역사적 건축물 조화</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · 오리엔테이션 프로그램·사전 출발 세션 제공 · 인도네시아 국립 종합대</t>
+          <t>자카르타 접근성 좋은 휴양형 대학도시 · 열대 자연 속 현대적 캠퍼스 시설 · 인도네시아 전통문화 체험 기회 풍부</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>월 €450 공유 학생 아파트 · 학기 초 오리엔테이션 데이 · 연간 500명+ 교환학생 수용 · 월 생활비 €1,000 (식비 €450 포함)</t>
+          <t>로미오와 줄리엣 배경지·오페라 하우스 등 문화 자원 풍부 · 밀라노·베네치아 접근성 좋은 유럽 여행 거점 · 이탈리아 전통 미식 체험하기 좋은 소도시 분위기</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
@@ -8957,7 +8957,7 @@
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>GPA 요건 없음 · 학생 기숙사 제공 · 공학·건축 특성화</t>
+          <t>학생 기숙사 제공 · 밀라노 패션·디자인 산업 중심지 · 알프스·호수 접근성 좋은 여행 거점 · 유럽 최대 역사 중심가와 현대적 스카이라인 공존</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · GPA 요건 없음 · Welcome Unit 개별 오리엔테이션 제공 · 700+ 해외 대학과 교환 협약</t>
+          <t>운하 도시 베네치아에서 낭만적인 유럽 생활 · 이탈리아 미식 문화 체험에 최적화된 도시 · 유럽 배낭여행 거점으로 접근성 우수</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
@@ -9111,7 +9111,7 @@
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · GPA 요건 없음 · 기숙사 미보장·조기신청 필요 · 국제학생데스크(ISD) 지원 서비스</t>
+          <t>기숙사 미보장·조기신청 필요 · 유럽 패션·금융 중심지 인턴십 기회 풍부 · 밀라노 명소 두오모·나빌리오 거리 접근성 우수 · 이탈리아 미식·카페 문화 체험 가능</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>오리엔테이션 제공 · 석사생 수강 제한(일본어·영어 강의만)</t>
+          <t>오카야마 성·코라쿠엔 정원 등 역사 명소 접근성 · 조용한 소도시 분위기로 학업 집중 환경 · 세토 내해 인접 휴양지 분위기</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
@@ -9265,7 +9265,7 @@
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>GPA 요건 없음 · 영어 능력 시험 및 언어 검정 시험 응시료 지원 제도 · 스포츠·건강과학부 운영</t>
+          <t>전통과 현대가 공존하는 독특한 캠퍼스 분위기 · 자연 속 조용한 학습 환경 · 도쿄 근교 접근성 좋은 휴양지</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
@@ -9342,7 +9342,7 @@
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · GPA 요건 없음 · 일본 국민건강보험(연 3만엔) 및 학생 사고보험(1,340엔) 필수 가입</t>
+          <t>도쿄 중심가 접근성 우수한 교통 인프라 · 일본 전통문화 체험 가능한 신주쿠 인접</t>
         </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
@@ -9419,7 +9419,7 @@
       </c>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · 기숙사·아파트·홈스테이 정보 핸드북 제공 · 35개국 160개 파트너 대학 · 학기당 14학점(10시간 수업) 필수</t>
+          <t>기숙사·아파트·홈스테이 정보 핸드북 제공 · 도쿄 패션 중심지 신주쿠·하라주쿠 접근성 우수 · 일본 전통문화·현대문화 공존한 도시 분위기 · 미식·카페 문화 발달한 글로벌 도시</t>
         </is>
       </c>
       <c r="M117" s="2" t="inlineStr">
@@ -9496,7 +9496,7 @@
       </c>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>GPA 요건 없음 · 교환학생 기숙사 보장 (국제교류회관, 전실 개인실) · 기숙사 비용: 입관비 33,000엔, 월 33,000엔 (광열비 별도)</t>
+          <t>교환학생 기숙사 보장 (국제교류회관, 전실 개인실) · 기숙사 비용: 입관비 33,000엔, 월 33,000엔 (광열비 별도) · 후쿠오카 미식·카페 문화 체험 가능 · 온천·자연 휴양지 접근성 우수 · 한국인에게 친근한 관광 도시 분위기</t>
         </is>
       </c>
       <c r="M118" s="2" t="inlineStr">
@@ -9573,7 +9573,7 @@
       </c>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>국제학생 기숙사(코다이라) 우선 배정, 1인실 공유형 · 장애 학생 합리적 편의 제공 · 일본 국립 사회과학 특화 대학</t>
+          <t>국제학생 기숙사(코다이라) 우선 배정, 1인실 공유형 · 사회과학 특화 도서관·연구 시설 우수 · 도쿄 접근성 좋은 조용한 자연 환경</t>
         </is>
       </c>
       <c r="M119" s="2" t="inlineStr">
@@ -9650,7 +9650,7 @@
       </c>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · 기숙사 환영 미팅 제공 · 오리엔테이션 및 은행 계좌 개설 지원 · 마키구치 장학금 및 일본학 센터 장학금 제공</t>
+          <t>기숙사 환영 미팅 제공 · 소카대학교 평화 철학 반영한 캠퍼스 분위기 · 도쿄 근교 접근성 좋은 조용한 소도시 생활 · 일본 전통 문화 체험 가능한 지역 환경</t>
         </is>
       </c>
       <c r="M120" s="2" t="inlineStr">
@@ -9727,7 +9727,7 @@
       </c>
       <c r="L121" s="2" t="inlineStr">
         <is>
-          <t>주당 최소 10시간 수업 필수, 최대 20학점 등록 가능</t>
+          <t>교토 전통 문화 체험 가능한 역사 도시 · 대학 내 일본식 정원·전통 건축물 보유 · 교토 시내 접근성 좋은 교통 인프라</t>
         </is>
       </c>
       <c r="M121" s="2" t="inlineStr">
@@ -9804,7 +9804,7 @@
       </c>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>GPA 요건 없음 · 기숙사 신청 필요 · 도쿄 버디 프로그램 · 일본어 능력시험 지원금</t>
+          <t>기숙사 신청 필요 · 도쿄 접근성 좋은 조용한 소도시 생활 · 일본 전통문화 체험 가능한 지역 축제</t>
         </is>
       </c>
       <c r="M122" s="2" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>국제 기숙사 제공 · 국제 라운지(G-square) 운영 · 파트너 대학 266개교</t>
+          <t>국제 기숙사 제공 · 도쿄 도심 접근성 좋은 준도시 생활 · 일본 전통·현대 문화 공존하는 도시 분위기 · 미식·카페 문화 풍부한 글로벌 도시</t>
         </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="L124" s="2" t="inlineStr">
         <is>
-          <t>연 40명 수용 · 재정 증명서 필수</t>
+          <t>알프스 접근성 좋은 휴양 도시 · 전통과 현대가 공존하는 고풍스러운 도시 · 일본 내 한국인 인지도 높은 국립대</t>
         </is>
       </c>
       <c r="M124" s="2" t="inlineStr">
@@ -10035,7 +10035,7 @@
       </c>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>사전 도착 정보·오리엔테이션 제공</t>
+          <t>일본 전통 공예 체험 가능한 문화 도시 · 나고야성·도요타 박물관 등 역사·산업 명소 · 혼마쿠·오아시스 등 현지 맛집 밀집</t>
         </is>
       </c>
       <c r="M125" s="2" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · GPA 요건 없음 · 비학위 과정(특별청강생/특별연구생) 제공</t>
+          <t>전통과 현대가 공존하는 역사적 도시 분위기 · 일본 전통 문화 체험 기회 풍부</t>
         </is>
       </c>
       <c r="M126" s="2" t="inlineStr">
@@ -10189,7 +10189,7 @@
       </c>
       <c r="L127" s="2" t="inlineStr">
         <is>
-          <t>교환학생 기숙사 제공 · 오리엔테이션 및 특별 수업 제공 · ISEP, UMAP 등 국제 교류 프로그램 운영</t>
+          <t>교환학생 기숙사 제공 · 도쿄 근교 접근성 좋은 조용한 소도시 · 전통과 현대 조화되는 사와타 시내 분위기</t>
         </is>
       </c>
       <c r="M127" s="2" t="inlineStr">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="L128" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · 대학 기숙사 배정 · 장학금 신청 가능</t>
+          <t>대학 기숙사 배정 · 미식과 카페 문화로 유명한 도시 · 유럽 한복판이라 주말 배낭여행 거점으로 최적</t>
         </is>
       </c>
       <c r="M128" s="2" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="L129" s="2" t="inlineStr">
         <is>
-          <t>교환학생 기숙사 보장 · 필수 보험 2종 가입 · 공학·자연과학 특성화</t>
+          <t>교환학생 기숙사 보장 · 일본 동북부 역사·문화 중심지 센다이 도심 접근성 · 공학·IT 분야 연구 인프라 우수 · 미야기현 특산물 활용한 지역 음식 문화 체험</t>
         </is>
       </c>
       <c r="M129" s="2" t="inlineStr">
@@ -10420,7 +10420,7 @@
       </c>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>파트너 대학 협약 체결</t>
+          <t>후쿠오카 미식·카페 문화 체험 가능 · 규슈 지역 역사 유적 탐방 접근성 우수 · 후쿠오카 도심 접근성 좋은 준도시 생활</t>
         </is>
       </c>
       <c r="M130" s="2" t="inlineStr">
@@ -10497,7 +10497,7 @@
       </c>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · 공인 어학성적 없이 지원 가능 · 카자흐스탄 최대 영어 강의 대학</t>
+          <t>중앙아시아 최대 도시 알마티 접근성 우수 · 유럽풍 건축물과 산악 지형 어우러진 도시 경관 · 카자흐스탄 경제 중심지 인턴십 기회 다수</t>
         </is>
       </c>
       <c r="M131" s="2" t="inlineStr">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · VMU 기숙사에서 다른 국제학생과 생활 · VMU 멘토 프로그램 및 오리엔테이션 데이 제공 · 연간 2000명+ 80개국 이상 교환학생 수용</t>
+          <t>VMU 기숙사에서 다른 국제학생과 생활 · 유럽 배낭여행 거점으로 접근성 좋은 위치 · 발트 3국 전통 건축물과 현대적 도시 풍경 공존 · 카우나스 강변 산책로와 유럽풍 카페 문화</t>
         </is>
       </c>
       <c r="M132" s="2" t="inlineStr">
@@ -10651,7 +10651,7 @@
       </c>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>문화·스포츠·특별 관심사 그룹 활동 제공 · QS 세계 사립대 29위</t>
+          <t>멕시코 최대 산업단지 인접해 인턴십 기회 풍부 · 미국 국경 인접해 주말 여행·쇼핑 편리 · 현대적 캠퍼스 내 첨단 연구 시설 보유</t>
         </is>
       </c>
       <c r="M133" s="2" t="inlineStr">
@@ -10728,7 +10728,7 @@
       </c>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · GPA 요건 없음 · 교내 기숙사 미보장·조기신청 필요 · 파트너 대학 300개교 이상</t>
+          <t>교내 기숙사 미보장·조기신청 필요 · 유럽 한복판 주말 배낭여행 거점 · 고즈넉한 유럽 대학도시 낭만 · 미식과 카페 문화 유명 도시</t>
         </is>
       </c>
       <c r="M134" s="2" t="inlineStr">
@@ -10805,7 +10805,7 @@
       </c>
       <c r="L135" s="2" t="inlineStr">
         <is>
-          <t>오리엔테이션 활동 제공 · 비EEA 학생 비자 지원 및 최소 20 ECTS 수강 필요 · 네덜란드 연구 중심 종합대학</t>
+          <t>유럽 한복판 주말 배낭여행 거점 · 고즈넉한 유럽 대학도시 낭만 · 미식과 카페 문화 유명 도시</t>
         </is>
       </c>
       <c r="M135" s="2" t="inlineStr">
@@ -10882,7 +10882,7 @@
       </c>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · GPA 요건 없음 · 교내 기숙사 미보장·조기신청 필요 · Inclusive Mobility 지원 서비스 제공</t>
+          <t>교내 기숙사 미보장·조기신청 필요 · 유럽 내륙 교통 허브로 주말 여행 편리 · 조용한 대학도시에서 집중적 학업 가능 · 로테르담 접근성 좋은 문화·쇼핑 기회</t>
         </is>
       </c>
       <c r="M136" s="2" t="inlineStr">
@@ -10959,7 +10959,7 @@
       </c>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · 교환학생 전용 오리엔테이션 주 제공 · 홈대학 학점 인정 가능 · 실용적 교육 중심 응용과학대학</t>
+          <t>유럽 한복판 주말 배낭여행 거점 · 휴양 도시 분위기 바다 접근성 · 소도시 낭만 고즈넉한 유럽 생활</t>
         </is>
       </c>
       <c r="M137" s="2" t="inlineStr">
@@ -11036,7 +11036,7 @@
       </c>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · 비영어권이지만 전 과정 영어 수업</t>
+          <t>유럽 한복판 주말 배낭여행 거점 · 미식·카페 문화 발달한 첨단 도시</t>
         </is>
       </c>
       <c r="M138" s="2" t="inlineStr">
@@ -11116,7 +11116,7 @@
       </c>
       <c r="L139" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · 연 650명+ 교환학생 수용 · 경영 트리플크라운 인증</t>
+          <t>유럽 교통 허브로 주말 여행 편리 · 역사적 건축물 가득한 중세 도시 분위기 · 네덜란드에서 가장 오래된 대학 도시</t>
         </is>
       </c>
       <c r="M139" s="2" t="inlineStr">
@@ -11197,7 +11197,7 @@
       </c>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · 비영어권이지만 전 과정 영어 수업 · 수강 신청 시 최소/최대 인원 제한으로 캠퍼스·강의 변경 가능성 있음 · 응용과학대학(Holland Applied Sciences)</t>
+          <t>유럽 배낭여행 거점으로 접근성 우수 · 미식·카페 문화 풍부한 도시 분위기</t>
         </is>
       </c>
       <c r="M140" s="2" t="inlineStr">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · 비영어권이지만 전 과정 영어 수업 · 블록제 운영(8주 수업+1주 시험), 1블록 12~16EC 권장 · 경영·경제 특성화 대학</t>
+          <t>유럽 물류 중심지 도시 경제 체험 · 현대적 항구 도시 문화·예술 활기 · 네덜란드 제2의 도시 글로벌 분위기</t>
         </is>
       </c>
       <c r="M141" s="2" t="inlineStr">
@@ -11351,7 +11351,7 @@
       </c>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · 비영어권이지만 전 과정 영어 수업 · 실용학문 중심 대학</t>
+          <t>유럽 내 교통 허브로 주말 여행 편리 · 운하·자전거 문화 중심의 친환경 도시</t>
         </is>
       </c>
       <c r="M142" s="2" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · GPA 요건 없음 · 연 1,100개 이상 영어 강의 제공 · 홈 대학 공식 추천 필요</t>
+          <t>유럽 배낭여행 거점으로 접근성 우수 · 미식·카페 문화 풍부한 도시 분위기 · 현대적 학습 시설 갖춘 대학 캠퍼스</t>
         </is>
       </c>
       <c r="M143" s="2" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · 국제 교환 코디네이터 지원 · 네덜란드 최상위권 종합대</t>
+          <t>유럽 한복판 주말 배낭여행 거점 · 고즈넉한 유럽 대학도시 낭만 · 미식과 카페 문화 유명 도시</t>
         </is>
       </c>
       <c r="M144" s="2" t="inlineStr">
@@ -11582,7 +11582,7 @@
       </c>
       <c r="L145" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · 비영어권이지만 전 과정 영어 수업 · 교환학생 기숙사 우선 배정 · 가을학기 8월 10일 시작</t>
+          <t>교환학생 기숙사 우선 배정 · 피오르드 접한 자연 경관과 도시 조화 · 북유럽 디자인의 현대적 학습 공간</t>
         </is>
       </c>
       <c r="M145" s="2" t="inlineStr">
@@ -11659,7 +11659,7 @@
       </c>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · 교환학생 기숙사 보장</t>
+          <t>교환학생 기숙사 보장 · 피오르드와 어우러진 자연 경관 · 북유럽 특유의 고풍스러운 도시 분위기 · 유럽 내 배낭여행 접근성 우수</t>
         </is>
       </c>
       <c r="M146" s="2" t="inlineStr">
@@ -11736,7 +11736,7 @@
       </c>
       <c r="L147" s="2" t="inlineStr">
         <is>
-          <t>파트너 300개교+ · 교환학생 장학금 제공 · QS 페루 1위 종합대</t>
+          <t>잉카 문명 유적과 현대 도시 공존하는 독특한 분위기 · 페루 전통 시장과 미식 체험 가능한 문화 중심지</t>
         </is>
       </c>
       <c r="M147" s="2" t="inlineStr">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>GPA 요건 없음 · 오리엔테이션 주간 및 버디 프로그램 제공 · 비파트너 대학생도 1학기 또는 1년 자유수강 가능 · 폴란드 최고 경제·경영 대학</t>
+          <t>유럽 중심 위치 주말 여행 편리 · 폴란드 전통 건축물과 현대적 도시 풍경 조화 · 저렴한 물가로 경제적 생활 가능</t>
         </is>
       </c>
       <c r="M148" s="2" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>1학기 30~36 ECTS 권장, 최대 36 ECTS 선택 가능 · 공학·기술 특성화 대학</t>
+          <t>유럽 배낭여행 거점인 대서양 연안 도시 · 공학 특화 대학 내 첨단 연구 시설 · 리스본 미식·카페 문화 체험 가능</t>
         </is>
       </c>
       <c r="M149" s="2" t="inlineStr">
@@ -11967,7 +11967,7 @@
       </c>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>공인 어학성적 없이 지원 가능 · 교내 기숙사 미보장·조기신청 필요 · 전담 오리엔테이션·학생 지원 서비스 · 연 200명+ 교환학생 수용</t>
+          <t>교내 기숙사 미보장·조기신청 필요 · 디자인 중심 교육·창의적 캠퍼스 환경 · 싱가포르 도심 접근성·국제적 생활 경험 · 다국적 학생 교류·글로벌 네트워크 형성</t>
         </is>
       </c>
       <c r="M150" s="2" t="inlineStr">
@@ -12044,7 +12044,7 @@
       </c>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t>기숙사 신청 필요 · 교환학생 포털·오리엔테이션 제공 · 파트너 350+개교 · 장학금 미제공</t>
+          <t>기숙사 신청 필요 · 현대적 첨단 연구 시설·스마트 캠퍼스 · 열대 정원·호수가 어우러진 자연 친화적 환경 · 미식·쇼핑·관광 명소 접근성 우수</t>
         </is>
       </c>
       <c r="M151" s="2" t="inlineStr">
@@ -12122,7 +12122,7 @@
       </c>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · GPA 요건 없음 · 교내 기숙사 미보장·개인 주거 선택 · 오리엔테이션(리틀 인디아·차이나타운 방문) 및 글로벌 네트워크 기회</t>
+          <t>교내 기숙사 미보장·개인 주거 선택 · 미식과 카페 문화로 유명한 도시 · 대도시라 인턴·문화생활 기회 풍부</t>
         </is>
       </c>
       <c r="M152" s="2" t="inlineStr">
@@ -12199,7 +12199,7 @@
       </c>
       <c r="L153" s="2" t="inlineStr">
         <is>
-          <t>GPA 요건 없음 · 오리엔테이션 제공 · 스페인어 무료 수강(교재비 €60), 영어 강의 제한적</t>
+          <t>지중해 휴양지 근접·해변 여가 활동 · 스페인 전통 건축물과 현대적 캠퍼스 조화 · 유럽 배낭여행 거점·주말 여행 편리</t>
         </is>
       </c>
       <c r="M153" s="2" t="inlineStr">
@@ -12276,7 +12276,7 @@
       </c>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>GPA 요건 없음 · 기숙사 미보장·조기신청 필요 · 멘토 프로그램 제공 · 스페인어 필수·스페인어 과정 제공</t>
+          <t>기숙사 미보장·조기신청 필요 · 지중해 휴양지 근접·해변 여가 활동 가능 · 발렌시아 파에야·오렌지 문화 체험 가능</t>
         </is>
       </c>
       <c r="M154" s="2" t="inlineStr">
@@ -12353,7 +12353,7 @@
       </c>
       <c r="L155" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · 교환학생 기숙사 신청 가능 · 연 2,000명+ 교환학생 수용 · €4.02 보험비 납부 필수</t>
+          <t>교환학생 기숙사 신청 가능 · 지중해 휴양지 근접해 주말 해변 휴식 가능 · 카탈루냐 전통 시장·타파스 문화 체험 · 바르셀로나 접근성 좋은 소도시 생활</t>
         </is>
       </c>
       <c r="M155" s="2" t="inlineStr">
@@ -12430,7 +12430,7 @@
       </c>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · 공인 어학성적 없이 지원 가능 · 모든 등록 과목 출석 필수 · 경영·법학 분야 트리플크라운 인증</t>
+          <t>바르셀로나 접근성 좋은 소도시 생활 · 유럽 배낭여행 거점 도시 분위기 · 미식·카페 문화 풍부한 도시</t>
         </is>
       </c>
       <c r="M156" s="2" t="inlineStr">
@@ -12507,7 +12507,7 @@
       </c>
       <c r="L157" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · 공인 어학성적 없이 지원 가능 · 스페인 북부 명문 사립대</t>
+          <t>구겐하임 미술관 등 문화 인프라 우수 · 바스크 전통 음식과 와인 문화 체험 · 산악·해안 경관과 도시 접근성 겸비</t>
         </is>
       </c>
       <c r="M157" s="2" t="inlineStr">
@@ -12584,7 +12584,7 @@
       </c>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>버디 프로그램 운영 · 연 수백 명 교환학생 수용 · 무료 스페인어 과정 제공 · 의학·경영·공학 특성화</t>
+          <t>산페르민 축제 등 전통 문화 체험 가능 · 소도시라 한국인 적고 현지인 교류 용이 · 피레네 산맥 근접 자연 경관 활용</t>
         </is>
       </c>
       <c r="M158" s="2" t="inlineStr">
@@ -12661,7 +12661,7 @@
       </c>
       <c r="L159" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · 파트너 200개교 이상 · 2026년 2월 업데이트 예정 · 경영 트리플크라운 인증</t>
+          <t>중세 성곽 도시 낭만적인 분위기 · 마드리드 접근성 좋은 소도시 생활 · 스페인 전통 미식 체험 가능</t>
         </is>
       </c>
       <c r="M159" s="2" t="inlineStr">
@@ -12738,7 +12738,7 @@
       </c>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · 1학기 30학점 권장, 6개 과목 선호순 신청 · 공학·IT·에너지 기술 특성화</t>
+          <t>예테보리 접근성 좋은 소도시 생활 · 공학 특화 대학·실험 시설 우수 · 스웨덴 서해안의 한적한 자연 경관</t>
         </is>
       </c>
       <c r="M160" s="2" t="inlineStr">
@@ -12815,7 +12815,7 @@
       </c>
       <c r="L161" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · GPA 요건 없음 · 트라이메스터제 운영(학기당 15주 내외)</t>
+          <t>스칸디나비아 디자인 체험 가능한 현대적 캠퍼스 · 호반 도시 자연 경관과 자전거 생활 문화 · 스톡홀름 접근성 좋은 유럽 여행 거점</t>
         </is>
       </c>
       <c r="M161" s="2" t="inlineStr">
@@ -12892,7 +12892,7 @@
       </c>
       <c r="L162" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · GPA 요건 없음 · 드롭인 서비스 및 온라인 상담 제공 · 900개 이상 교환학생 과정 제공</t>
+          <t>스칸디나비아 최대·최고(最古) 대학 역사 · 중세 유적과 현대적 캠퍼스 조화</t>
         </is>
       </c>
       <c r="M162" s="2" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="L163" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · 트라이메스터제 운영</t>
+          <t>바다와 가까운 휴양 도시 분위기 · 고즈넉한 유럽 대학도시 낭만 · 유럽 한복판이라 주말 배낭여행 거점으로 최적</t>
         </is>
       </c>
       <c r="M163" s="2" t="inlineStr">
@@ -13046,7 +13046,7 @@
       </c>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t>ESN FHNW 학생 조직 지원 · 다양한 캠퍼스·전공 과목 선택 가능 · 응용과학·예술 분야 특성화 대학</t>
+          <t>알프스 근접 자연 경관 접근성 우수 · 취리히 근교 교통 편리성 겸비 · 예술·공학 융합 교육 환경</t>
         </is>
       </c>
       <c r="M164" s="2" t="inlineStr">
@@ -13123,7 +13123,7 @@
       </c>
       <c r="L165" s="2" t="inlineStr">
         <is>
-          <t>국제학생 전담 학업 지원 코디네이터 및 오리엔테이션 주 제공 · 교통카드(할프탁스·세븐25) 구매 권장 및 ECTS 초과 신청 권장 · 경영 트리플크라운 인증(AACSB·EQUIS·AMBA)</t>
+          <t>취리히 접근성 좋은 소도시 생활 · 알프스·유럽 여행 거점 도시 · 스위스 실용주의 교육 환경</t>
         </is>
       </c>
       <c r="M165" s="2" t="inlineStr">
@@ -13200,7 +13200,7 @@
       </c>
       <c r="L166" s="2" t="inlineStr">
         <is>
-          <t>교환학생 권장 학점 20-25 ECTS</t>
+          <t>알프스 접근성 좋은 유럽 대학도시 · 유네스코 지정 구시가지 역사 분위기</t>
         </is>
       </c>
       <c r="M166" s="2" t="inlineStr">
@@ -13277,7 +13277,7 @@
       </c>
       <c r="L167" s="2" t="inlineStr">
         <is>
-          <t>공학·경영 특성화</t>
+          <t>타이중 미식·야시장 문화 체험 가능 · 대만과 대륙 간 교류 중심지 역사성 · 중부 타이완 교통 허브 접근성</t>
         </is>
       </c>
       <c r="M167" s="2" t="inlineStr">
@@ -13354,7 +13354,7 @@
       </c>
       <c r="L168" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · GPA 요건 없음 · 교내 기숙사 미보장·자체 주거 확보 필요</t>
+          <t>교내 기숙사 미보장·자체 주거 확보 필요 · 가오슝 항구·야경 조망 가능한 캠퍼스 · 대만 남부 미식·야시장 체험 용이 · 휴양지 근처로 주말 여행 편리</t>
         </is>
       </c>
       <c r="M168" s="2" t="inlineStr">
@@ -13431,7 +13431,7 @@
       </c>
       <c r="L169" s="2" t="inlineStr">
         <is>
-          <t>공학·반도체 분야 특성화</t>
+          <t>반도체 산업단지 인접 현장 학습 기회 · 신주 도심 접근성 좋은 교통 인프라 · 대만 대표 과학 기술 명문 대학 명성</t>
         </is>
       </c>
       <c r="M169" s="2" t="inlineStr">
@@ -13508,7 +13508,7 @@
       </c>
       <c r="L170" s="2" t="inlineStr">
         <is>
-          <t>9학점(학부)/2과목(대학원) 최소 수강, 전체 대학 과목 선택 가능 · 공학·컴퓨터과학 특성화</t>
+          <t>공학·컴퓨터과학 분야 세계적 명성 · 신베이시 접근성 좋은 교통 인프라 · 대만 전통시장·야시장 문화 체험</t>
         </is>
       </c>
       <c r="M170" s="2" t="inlineStr">
@@ -13585,7 +13585,7 @@
       </c>
       <c r="L171" s="2" t="inlineStr">
         <is>
-          <t>Buddy Program (학우 멘토링) 운영 · 교환학생 장학금 다수 운영 (傑出交換生獎學金 등)</t>
+          <t>타이베이 미식·야시장 문화 체험 가능 · 대학로 인근 조용한 주거 환경 · 대만 정치·국제관계 특화 교육 강점</t>
         </is>
       </c>
       <c r="M171" s="2" t="inlineStr">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="L172" s="2" t="inlineStr">
         <is>
-          <t>국제학생 자원봉사자(버디) 지원 · 환영 활동 필수 참석(결석 시 입학 취소) · QS 세계대학랭킹 50위권 종합대</t>
+          <t>타이베이 도심 접근성 좋은 교통 인프라 · 대만 전통 시장과 현대 문화 공존한 도시 · 한국인에게 친숙한 동아시아 문화 환경</t>
         </is>
       </c>
       <c r="M172" s="2" t="inlineStr">
@@ -13739,7 +13739,7 @@
       </c>
       <c r="L173" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · GPA 요건 없음 · 기숙사 시설 제공 · 영어 강의 제공</t>
+          <t>기숙사 시설 제공 · 치앙라이의 고즈넉한 산악 도시 분위기 · 태국 북부 전통 문화 체험 기회 풍부 · 저렴한 물가로 배낭여행 겸 생활 가능</t>
         </is>
       </c>
       <c r="M173" s="2" t="inlineStr">
@@ -13816,7 +13816,7 @@
       </c>
       <c r="L174" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · Chula Link 장학금(2026학년도 1학기 국제학생 대상) · 태국 최고 명문 종합대학</t>
+          <t>태국 전통 시장과 현대적 쇼핑 거리 공존 · 열대 정원형 캠퍼스로 휴식 공간 풍부 · 미식과 스트리트 푸드 천국 도시</t>
         </is>
       </c>
       <c r="M174" s="2" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="L175" s="2" t="inlineStr">
         <is>
-          <t>공학 및 과학기술 특성화</t>
+          <t>방콕 미식·야시장 체험 기회 풍부 · 열대 휴양지 접근성 좋은 대도시</t>
         </is>
       </c>
       <c r="M175" s="2" t="inlineStr">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="L176" s="2" t="inlineStr">
         <is>
-          <t>GPA 요건 없음 · 교환학생 기숙사 예약 가능 · UNI 101 오리엔테이션·터키어 지원·국제우정의 날 행사 · UNI 101 9월·10월 세션 필수 참여</t>
+          <t>교환학생 기숙사 예약 가능 · 터키 전통 시장과 현대 상권 공존하는 활기찬 도시 · 유럽-아시아 연결점으로 주말 여행 접근성 우수 · 역사적 유적지와 현대적 인프라가 공존하는 수도</t>
         </is>
       </c>
       <c r="M176" s="2" t="inlineStr">
@@ -14047,7 +14047,7 @@
       </c>
       <c r="L177" s="2" t="inlineStr">
         <is>
-          <t>교환학생 오리엔테이션 및 버디 프로그램 운영 · 니가타대 여름 프로그램 무료 수강 가능 · 터키 최초·최대 국립 종합대학</t>
+          <t>터키 전통 시장과 현대식 쇼핑몰 공존 · 유럽-아시아 문화 교류 중심지</t>
         </is>
       </c>
       <c r="M177" s="2" t="inlineStr">
@@ -14124,7 +14124,7 @@
       </c>
       <c r="L178" s="2" t="inlineStr">
         <is>
-          <t>공인 어학성적 없이 지원 가능 · 공학 특성화</t>
+          <t>보스포루스 해협 접한 도시 전망과 역사 유적 공존 · 유럽-아시아 문화 융합한 미식·야시장 체험 · 공학 특화 연구 시설·실험 장비 우수</t>
         </is>
       </c>
       <c r="M178" s="2" t="inlineStr">
@@ -14201,7 +14201,7 @@
       </c>
       <c r="L179" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · 터키 최고 명문 종합대</t>
+          <t>보스포루스 해협 조망 캠퍼스 뷰 · 유럽-아시아 문화 교차 도시 생활 · 이스탄불 역사 유적지 접근성 우수</t>
         </is>
       </c>
       <c r="M179" s="2" t="inlineStr">
@@ -14278,7 +14278,7 @@
       </c>
       <c r="L180" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · 기숙사 신청 가능(풀년·학기별 옵션) · 오리엔테이션 주 제공(학기별 1주) · 연 200명+ 교환학생 수용(학기별 100명+)</t>
+          <t>기숙사 신청 가능(풀년·학기별 옵션) · 아시아·아프리카 연구 특화 세계적 명성 · 런던 중심가 문화·예술 자원 접근성 · 다양한 국제 학생 커뮤니티 형성</t>
         </is>
       </c>
       <c r="M180" s="2" t="inlineStr">
@@ -14355,7 +14355,7 @@
       </c>
       <c r="L181" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · 기숙사 제공·신청 절차 안내 · 비자 신청 시 CAS 발급 필요 · 영국 연구 중심 종합대학</t>
+          <t>기숙사 제공·신청 절차 안내 · 영국 중부의 역사적 유적과 현대적 도시 문화 공존 · 유럽 내 주요 도시 접근성 좋은 교통 허브</t>
         </is>
       </c>
       <c r="M181" s="2" t="inlineStr">
@@ -14432,7 +14432,7 @@
       </c>
       <c r="L182" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · 여름학기 프로그램 운영 · 러셀 그룹 소속 종합대</t>
+          <t>러셀 그룹 소속 연구 중심 명문대 · 영국 내 저렴한 물가와 활기찬 도시 생활 · 피크 디스트릭트 국립공원 접근성 좋은 자연 경관</t>
         </is>
       </c>
       <c r="M182" s="2" t="inlineStr">
@@ -14509,7 +14509,7 @@
       </c>
       <c r="L183" s="2" t="inlineStr">
         <is>
-          <t>교내 기숙사 제공 · 학업·행정·복지 지원 제공 · 1학기만 수강 시 시험 대체 과제 가능 · QS 2025 세계 200위권 종합대</t>
+          <t>교내 기숙사 제공 · 런던 접근성 좋은 소도시 생활 · 영국 전통 건축물과 현대적 캠퍼스 조화 · 테임즈강 근처 자연 경관 활용 가능</t>
         </is>
       </c>
       <c r="M183" s="2" t="inlineStr">
@@ -14586,7 +14586,7 @@
       </c>
       <c r="L184" s="2" t="inlineStr">
         <is>
-          <t>기숙사 보장·조기신청 필요 · 전담 인바운드 팀·온라인 상담 · 30+ 학과 모듈 선택 가능 · 러셀 그룹 소속·경영 트리플크라운 인증</t>
+          <t>기숙사 보장·조기신청 필요 · 러셀 그룹 소속 명문 대학 명성 · 바다와 가까운 휴양 도시 분위기 · 유럽 배낭여행 거점 접근성 우수</t>
         </is>
       </c>
       <c r="M184" s="2" t="inlineStr">
@@ -14663,7 +14663,7 @@
       </c>
       <c r="L185" s="2" t="inlineStr">
         <is>
-          <t>GPA 요건 없음 · 기숙사 계약 시 전체 학년 기간 의무 · 트라이메스터제 운영(9월-6월), 여름학기 단독 수강 불가 · 영국 연구 중심 공립대</t>
+          <t>기숙사 계약 시 전체 학년 기간 의무 · 런던 접근성 좋은 영국 역사 도시 · 기숙사 1인실 위주 쾌적한 환경 · 유럽 배낭여행 거점 도시</t>
         </is>
       </c>
       <c r="M185" s="2" t="inlineStr">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="L186" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · 국제 기회 팀 지원 · 150개국 이상 교환 프로그램 · 28일 이상 해외 인턴십 필수</t>
+          <t>영국 내 저렴한 물가로 생활비 절약 가능 · 유럽 주요 도시 접근성 좋은 교통 허브 · 다양한 문화 체험 가능한 다문화 도시</t>
         </is>
       </c>
       <c r="M186" s="2" t="inlineStr">
@@ -14817,7 +14817,7 @@
       </c>
       <c r="L187" s="2" t="inlineStr">
         <is>
-          <t>트라이메스터제(9월·1월 입학 가능) · QS 최상위권 종합대</t>
+          <t>영국 남서부의 문화·예술 중심지 · 강변 산책로와 공원 자연경관 우수 · 브리스틀 항구의 독특한 스트리트 아트</t>
         </is>
       </c>
       <c r="M187" s="2" t="inlineStr">
@@ -14894,7 +14894,7 @@
       </c>
       <c r="L188" s="2" t="inlineStr">
         <is>
-          <t>연 200명+ 교환학생 수용 · 1학기 또는 2학기(1년) 선택 가능</t>
+          <t>고즈넉한 유럽 대학도시 낭만 · 미식과 카페 문화로 유명한 도시 · 유럽 한복판이라 주말 배낭여행 거점으로 최적</t>
         </is>
       </c>
       <c r="M188" s="2" t="inlineStr">
@@ -14971,7 +14971,7 @@
       </c>
       <c r="L189" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · 교환학생 기숙사 보장 · 학기제(1학기/1년) 선택 가능 · QS 세계 100위권 종합대</t>
+          <t>교환학생 기숙사 보장 · 영국 북부의 활기찬 문화·예술 도시 분위기 · 유럽 배낭여행 거점으로 교통 편리</t>
         </is>
       </c>
       <c r="M189" s="2" t="inlineStr">
@@ -15048,7 +15048,7 @@
       </c>
       <c r="L190" s="2" t="inlineStr">
         <is>
-          <t>공인 어학성적 없이 지원 가능 · 공항 환영 서비스·국제학생 오리엔테이션 제공 · 영국 남서부 브리스톨 소재 종합대</t>
+          <t>브리스틀 강변 산책로와 공원 자연경관 · 창의적인 예술·문화 행사 활발한 도시 · 영국 남서부 교통 허브로 유럽 여행 편리</t>
         </is>
       </c>
       <c r="M190" s="2" t="inlineStr">
@@ -15125,7 +15125,7 @@
       </c>
       <c r="L191" s="2" t="inlineStr">
         <is>
-          <t>교환학생 기숙사 보장 · 전담 글로벌 기회 팀·개인 칼리지 튜터 지원 · 비유럽 13개국 50+ 대학 파트너 · 120학점(6과목) 이수, 최대 3개 학과 선택</t>
+          <t>교환학생 기숙사 보장 · 중세 성당·성곽이 어우러진 고풍스러운 도시 풍경 · 뉴캐슬·에든버러 등 근교 도시 접근성 우수 · 영국 전통 칼리지 시스템 체험 가능</t>
         </is>
       </c>
       <c r="M191" s="2" t="inlineStr">
@@ -15202,7 +15202,7 @@
       </c>
       <c r="L192" s="2" t="inlineStr">
         <is>
-          <t>교내 기숙사 옵션 제공 · 전 세계 100개 대학 파트너십 · 의학·치의학·조산학 등 일부 전공 제외</t>
+          <t>교내 기숙사 옵션 제공 · 맨체스터 접근성 좋은 소도시 생활 · 영국 내 저렴한 물가·생활비 · 유럽 배낭여행 거점 도시</t>
         </is>
       </c>
       <c r="M192" s="2" t="inlineStr">
@@ -15279,7 +15279,7 @@
       </c>
       <c r="L193" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · 1~2학기 선택 가능, 홈교 학점 인정 · 영국 내 현대·국제적 대학</t>
+          <t>영국 제2의 도시 버밍엄의 활기찬 도시 생활 · 현대적 디자인·미디어 시설로 창의적 학습 환경</t>
         </is>
       </c>
       <c r="M193" s="2" t="inlineStr">
@@ -15356,7 +15356,7 @@
       </c>
       <c r="L194" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · QS 세계 100위권 종합대</t>
+          <t>남해안 항구 도시 휴양지 분위기 · 영국 남부 교통 허브 유럽 여행 편리 · 해양공학·로봇공학 연구 강점</t>
         </is>
       </c>
       <c r="M194" s="2" t="inlineStr">
@@ -15433,7 +15433,7 @@
       </c>
       <c r="L195" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · 뉴욕주립대 시스템 소속 공립 종합대</t>
+          <t>뉴욕주 주도 올버니 역사·문화 자원 접근성 · 뉴욕시·캐나다 국경 근접 주말 여행 적합 · 미국 공립대 중 합리적 학비와 생활비</t>
         </is>
       </c>
       <c r="M195" s="2" t="inlineStr">
@@ -15502,7 +15502,7 @@
       </c>
       <c r="L196" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · 파트너 30개국 40개교 이상</t>
+          <t>호놀룰루 해변과 야시장 접근성 우수 · 다국적 학생 구성으로 글로벌 교류 활발</t>
         </is>
       </c>
       <c r="M196" s="2" t="inlineStr">
@@ -15579,7 +15579,7 @@
       </c>
       <c r="L197" s="2" t="inlineStr">
         <is>
-          <t>교환학생 기숙사 보장, 아파트형 기숙사 배정 · 공학·경영·예술과학 분야 강점</t>
+          <t>교환학생 기숙사 보장, 아파트형 기숙사 배정 · 시러큐스보다 한적한 자연 속 캠퍼스 · 겨울 스포츠·아웃도어 활동 활발 · 북미 원주민 문화 체험 가능</t>
         </is>
       </c>
       <c r="M197" s="2" t="inlineStr">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="L198" s="2" t="inlineStr">
         <is>
-          <t>교내 기숙사 신청 가능 (F1 비자 학생 대상, $250 보증금) · 국제학생 지원 (Office of International Affairs)</t>
+          <t>교내 기숙사 신청 가능 (F1 비자 학생 대상, $250 보증금) · 시카고 도심 접근성 좋은 교통 인프라 · 미식·카페 문화 체험 가능한 대도시</t>
         </is>
       </c>
       <c r="M198" s="2" t="inlineStr">
@@ -15733,7 +15733,7 @@
       </c>
       <c r="L199" s="2" t="inlineStr">
         <is>
-          <t>기숙사 보장·조기신청 권장, 아파트 신청 가능 · 기숙사 계약 1개월 전 해지 가능, 식사 플랜 권장 · 공립 연구중심 종합대</t>
+          <t>기숙사 보장·조기신청 권장, 아파트 신청 가능 · 기숙사 계약 1개월 전 해지 가능, 식사 플랜 권장 · 미국 서북부 자연 경관과 어우러진 고즈넉한 캠퍼스 · 스포캔·시애틀 접근성 좋은 소도시 생활</t>
         </is>
       </c>
       <c r="M199" s="2" t="inlineStr">
@@ -15810,7 +15810,7 @@
       </c>
       <c r="L200" s="2" t="inlineStr">
         <is>
-          <t>국제학생 오리엔테이션·크로스컬처 활동 제공 · 수강 과목 홈교 학점 인정 필수 확인 · 연구 중심 공학·응용과학 특성화</t>
+          <t>댈러스 근교 첨단 산업단지 접근성 우수 · 현대적 캠퍼스·첨단 연구 시설 보유 · 텍사스주 내 비교적 안전한 소도시 환경</t>
         </is>
       </c>
       <c r="M200" s="2" t="inlineStr">
@@ -15887,7 +15887,7 @@
       </c>
       <c r="L201" s="2" t="inlineStr">
         <is>
-          <t>교내 기숙사 미보장·조기신청 필요 · 교환학생 전용 오리엔테이션 제공 · 필수 보험·교통비·기숙사 신청비 발생</t>
+          <t>교내 기숙사 미보장·조기신청 필요 · 필수 보험·교통비·기숙사 신청비 발생 · 보스턴 도심 접근성 좋은 해안가 캠퍼스 · 다양한 문화·예술 행사 활발한 도시</t>
         </is>
       </c>
       <c r="M201" s="2" t="inlineStr">
@@ -15964,7 +15964,7 @@
       </c>
       <c r="L202" s="2" t="inlineStr">
         <is>
-          <t>교내 기숙사 필수 · 파트너 7개국 대학 · 1학기 생활비 6,500달러</t>
+          <t>교내 기숙사 필수 · 미국 정치 역사 중심지 링컨 홈·박물관 인접 · 소도시라 생활비·물가 전국 평균보다 저렴 · 시카고 접근성 좋은 조용한 대학 도시</t>
         </is>
       </c>
       <c r="M202" s="2" t="inlineStr">
@@ -16041,7 +16041,7 @@
       </c>
       <c r="L203" s="2" t="inlineStr">
         <is>
-          <t>파트너 15개교 이상 운영 · 홈교 학비 납부·제한적 수수료</t>
+          <t>휴스턴 우주센터와 NASA 연계 프로그램 · 멕시코만 인접 휴양지 접근성 우수 · 다문화 도시 음식·쇼핑 다양성</t>
         </is>
       </c>
       <c r="M203" s="2" t="inlineStr">
@@ -16118,7 +16118,7 @@
       </c>
       <c r="L204" s="2" t="inlineStr">
         <is>
-          <t>기숙사 보장 · 국제 교환학생 전용 오리엔테이션 · 필수 보험·여행 지원 서비스</t>
+          <t>기숙사 보장 · 보스턴 근교 접근성 좋은 문화·교육 도시 · 한적하고 안전한 소도시 분위기 · 미국 동부 명문대 간 교류 활발</t>
         </is>
       </c>
       <c r="M204" s="2" t="inlineStr">
@@ -16195,7 +16195,7 @@
       </c>
       <c r="L205" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · 미국 아이다호 주 보이시 소재 공립대</t>
+          <t>미국 서부 산악 지형과 현대적 캠퍼스 조화 · 인근 보이시 강·산악 액티비티 접근성 우수 · 미국 내 저렴한 생활비·치안 좋은 소도시</t>
         </is>
       </c>
       <c r="M205" s="2" t="inlineStr">
@@ -16272,7 +16272,7 @@
       </c>
       <c r="L206" s="2" t="inlineStr">
         <is>
-          <t>GPA 요건 없음 · 교내 기숙사 미보장·조기신청 필요 · 연 150명+ 교환학생 수용 · 필수 건강 보험 가입</t>
+          <t>교내 기숙사 미보장·조기신청 필요 · 미국 남서부 최대 도시권 접근성·다양한 문화 체험 · 사막 기후 속 현대적 캠퍼스·야외 활동 인프라 우수</t>
         </is>
       </c>
       <c r="M206" s="2" t="inlineStr">
@@ -16349,7 +16349,7 @@
       </c>
       <c r="L207" s="2" t="inlineStr">
         <is>
-          <t>기숙사 입주 가능 · 오리엔테이션 제공 · 필수 보험 가입 필요 · R1 연구 중심 대학</t>
+          <t>기숙사 입주 가능 · 로키 산맥 근접 자연 탐험·아웃도어 활동 천국 · 소도시 여유로운 분위기·현지 문화 체험 적합</t>
         </is>
       </c>
       <c r="M207" s="2" t="inlineStr">
@@ -16426,7 +16426,7 @@
       </c>
       <c r="L208" s="2" t="inlineStr">
         <is>
-          <t>장학금 및 재정 지원 가능, 주외 학생 수수료 면제 혜택 · 플로리다 주립대 시스템 소속 공립 연구중심대</t>
+          <t>멕시코만 접한 휴양지 접근성 우수 · 대도시 인프라 활용한 인턴십 기회</t>
         </is>
       </c>
       <c r="M208" s="2" t="inlineStr">
@@ -16503,7 +16503,7 @@
       </c>
       <c r="L209" s="2" t="inlineStr">
         <is>
-          <t>기숙사 신청 가능·교내 외 숙소 광고 포털 제공 · 교환학생 전담 담당자(Quynh Luong) 및 오리엔테이션 제공 · 학기 시작 전 주 도착 필요·12-18학점 필수 등록 · 경영학부(Kelley School of Business) 특성화</t>
+          <t>기숙사 신청 가능·교내 외 숙소 광고 포털 제공 · 켈리 경영대학 명성·실무 중심 교육 · 인디애나폴리스 접근성·자연 경관 조화 · 소도시 분위기 속 캠퍼스 중심 생활</t>
         </is>
       </c>
       <c r="M209" s="2" t="inlineStr">
@@ -16580,7 +16580,7 @@
       </c>
       <c r="L210" s="2" t="inlineStr">
         <is>
-          <t>국제학생 지원 및 글로벌 학습 경험 강화</t>
+          <t>샬럿 접근성 좋은 소도시 생활 · 남부 미국 전통 문화 체험 가능</t>
         </is>
       </c>
       <c r="M210" s="2" t="inlineStr">
@@ -16657,7 +16657,7 @@
       </c>
       <c r="L211" s="2" t="inlineStr">
         <is>
-          <t>교환학생 기숙사 보장·조기신청 필요 · 50개 이상 대학 파트너십 · 특정 과목 수강 제한 · 뉴욕주립대 시스템 소속 종합대</t>
+          <t>교환학생 기숙사 보장·조기신청 필요 · 뉴욕주 제2의 도시 접근성·다양한 문화생활 · 나이아가라 폭포 근접·주말 여행 명소</t>
         </is>
       </c>
       <c r="M211" s="2" t="inlineStr">
@@ -16734,7 +16734,7 @@
       </c>
       <c r="L212" s="2" t="inlineStr">
         <is>
-          <t>교내 기숙사 및 식사 제공 · 기숙사 거주 시 예방접종 필수 · 펜실베이니아 주립대, 미국 최대 공립대 중 하나</t>
+          <t>교내 기숙사 및 식사 제공 · 기숙사 거주 시 예방접종 필수 · 미국 최대 규모 공립대 중 하나로 다양한 전공 선택 가능 · 필라델피아·뉴욕 접근성 좋은 교통 요충지</t>
         </is>
       </c>
       <c r="M212" s="2" t="inlineStr">
@@ -16811,7 +16811,7 @@
       </c>
       <c r="L213" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · 기숙사 미보장·조기신청 필요 · 전담 매니저 지원 · 연 200명+ 교환학생 수용</t>
+          <t>기숙사 미보장·조기신청 필요 · 미식·맥주 문화로 유명한 도시 · 대호 인접 휴양·레저 활동 가능</t>
         </is>
       </c>
       <c r="M213" s="2" t="inlineStr">
@@ -16888,7 +16888,7 @@
       </c>
       <c r="L214" s="2" t="inlineStr">
         <is>
-          <t>교내 기숙사 신청 가능 · J-1 비자 필수, DS-2019 발급 · 경영·금융 특성화 대학</t>
+          <t>교내 기숙사 신청 가능 · 보스턴 접근성 좋은 소도시 생활 · 경영·금융 특화 커리큘럼 강점</t>
         </is>
       </c>
       <c r="M214" s="2" t="inlineStr">
@@ -16965,7 +16965,7 @@
       </c>
       <c r="L215" s="2" t="inlineStr">
         <is>
-          <t>교환학생 전용 오리엔테이션 및 앰배서더 지원 · 미국 최대 규모의 종합대학 중 하나</t>
+          <t>미국 중서부 최대 규모 캠퍼스·다양한 시설 · 디트로이트·시카고 접근성 좋은 교통 허브 · 계절별 축제·스포츠 문화 활발한 대학 도시</t>
         </is>
       </c>
       <c r="M215" s="2" t="inlineStr">
@@ -17042,7 +17042,7 @@
       </c>
       <c r="L216" s="2" t="inlineStr">
         <is>
-          <t>기숙사 조기 신청 필요 · 교환학생 전용 오리엔테이션 · 파트너 30여 개국 50+ 대학 · 트라이메스터제 학사일정</t>
+          <t>기숙사 조기 신청 필요 · 바다와 인접한 자연 경관이 아름다운 휴양지 · 샌프란시스코 접근성 좋은 소도시 생활</t>
         </is>
       </c>
       <c r="M216" s="2" t="inlineStr">
@@ -17119,7 +17119,7 @@
       </c>
       <c r="L217" s="2" t="inlineStr">
         <is>
-          <t>연 130개교 이상 파트너 대학 · 세계 40위권 종합대</t>
+          <t>미식과 라이브 음악으로 유명한 활기찬 도시 · 텍사스 주의회 의사당 등 역사적 건축물 다수 · 대도시 인프라 속 자연 공원 접근성 우수</t>
         </is>
       </c>
       <c r="M217" s="2" t="inlineStr">
@@ -17196,7 +17196,7 @@
       </c>
       <c r="L218" s="2" t="inlineStr">
         <is>
-          <t>도심 도보권 캠퍼스 · 공학 특성화</t>
+          <t>실리콘밸리 중심지로 IT 기업 인턴십 기회 풍부 · 다양한 문화·음식점 밀집한 글로벌 도시</t>
         </is>
       </c>
       <c r="M218" s="2" t="inlineStr">
@@ -17273,7 +17273,7 @@
       </c>
       <c r="L219" s="2" t="inlineStr">
         <is>
-          <t>DS-2019 발급 후 J-1 비자 신청 필요</t>
+          <t>남부의 역사적 건축물·아름다운 해안가 캠퍼스 · 미식·카페 문화 발달한 관광 도시 분위기 · 물가 저렴해 생활비 부담 적은 편</t>
         </is>
       </c>
       <c r="M219" s="2" t="inlineStr">
@@ -17350,7 +17350,7 @@
       </c>
       <c r="L220" s="2" t="inlineStr">
         <is>
-          <t>미국 최고 역사 공립대</t>
+          <t>롤리-더럼 연구단지 인접해 첨단 산업 인턴십 기회 · 남부 특유의 고풍스러운 대학가 분위기</t>
         </is>
       </c>
       <c r="M220" s="2" t="inlineStr">
@@ -17427,7 +17427,7 @@
       </c>
       <c r="L221" s="2" t="inlineStr">
         <is>
-          <t>필수 건강 보험 정책 · FAMU-FSU 공학대 운영</t>
+          <t>올랜도·플로리다 해변 접근성 좋은 휴양지 · 미국 남부 특유의 활기찬 대학 타운 분위기</t>
         </is>
       </c>
       <c r="M221" s="2" t="inlineStr">
@@ -17504,7 +17504,7 @@
       </c>
       <c r="L222" s="2" t="inlineStr">
         <is>
-          <t>비영어권이지만 전 과정 영어 수업 · 기숙사 미보장·조기신청 필요 · I-GESA 장학금 지원 · I-GESA 장학금(400만 VND) 제공</t>
+          <t>기숙사 미보장·조기신청 필요 · 하노이 미식·카페 문화 체험 가능 · 베트남 신흥 명문 대학 명성 · 도심 접근성 좋은 준도시 환경</t>
         </is>
       </c>
       <c r="M222" s="2" t="inlineStr">
